--- a/신고신저가_20260901.xlsx
+++ b/신고신저가_20260901.xlsx
@@ -33,7 +33,7 @@
     <numFmt numFmtId="164" formatCode="+0.00&quot;%&quot;;-0.00&quot;%&quot;"/>
     <numFmt numFmtId="165" formatCode="0.0&quot;%&quot;"/>
   </numFmts>
-  <fonts count="4">
+  <fonts count="5">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -44,6 +44,7 @@
     <font>
       <b val="1"/>
     </font>
+    <font/>
     <font>
       <color rgb="000000C0"/>
     </font>
@@ -76,15 +77,19 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="164" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment wrapText="1"/>
     </xf>
@@ -453,7 +458,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G7"/>
+  <dimension ref="A1:G23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -611,7 +616,84 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" t="inlineStr">
+      <c r="A7" s="2" t="inlineStr">
+        <is>
+          <t>💬 ■ 결론: 오늘은 미국 유틸리티의 급락과 중국·홍콩 은행의 재평가가 동시에 나타난 정책 디테일 장세였다. 원유 강세는 미국과 일본 에너지주를 밀어 올렸지만, 미국은 신고가 30종보다 신저가 79종이 훨씬 많아 위험 선호가 넓게 퍼진 장은 아니었다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="3" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" s="3" t="inlineStr">
+        <is>
+          <t>■ 美(8/31): 하나만 기억하면 에너지 강세보다 유틸리티 신저가 확산이 더 컸다. 에너지 순강도는 6이었고 XLE는 2.7% 올랐다. 반면 유틸리티 순강도는 -21까지 밀렸고, 산불 책임상한이 법안에서 빠지자 에디슨인터내셔널과 PG&amp;E가 각각 20% 넘게 급락했다. 크라우드스트라이크는 분기 호실적 뒤 매수세가 이어져 5.8% 올랐다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="3" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" s="3" t="inlineStr">
+        <is>
+          <t>■ 日(9/1): 장중 핵심은 원유가격 상승이 정유·상사·전력 신고가를 함께 밀어 올린 점이다. 신고가 16종에 신저가는 2종뿐이었다. 에너지 ETF는 2.1%, 전력·가스 ETF는 3.3% 올라 인펙스와 에네오스의 신고가를 뒷받침했다. 간사이전력은 증권사 목표가 상향까지 겹쳤다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="3" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="3" t="inlineStr">
+        <is>
+          <t>■ 홍콩(8/31): 지수는 보합권이었지만 대형은행과 항공의 방향이 선명하게 갈렸다. 금융은 신고가 8종으로 순강도 7을 기록했다. 반기 순익과 배당 확대 기대가 중국우정저축은행·중국은행을 밀어 올렸지만, 중국 3대 항공사는 적자 확대와 연료비 상승으로 함께 신저가에 들어갔다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="3" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="3" t="inlineStr">
+        <is>
+          <t>■ 中(8/31): 은행과 우주산업이 시장의 중심이었다. 금융 순강도는 6이었고 은행 ETF는 1.5% 올랐다. 중국은행과 중국우정저축은행은 반기 이익과 배당 기대에 신고가를 냈고, 레이트론은 위성통신 기대에 14.4% 급등했다. 반대로 선그로우는 상반기 매출과 순이익 감소가 확인되며 6.3% 내렸다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="3" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" s="3" t="inlineStr">
+        <is>
+          <t>■ 체크: ① 캘리포니아 산불 법안의 책임상한이 다시 협상되는지 확인해야 유틸리티의 추가 하락 범위를 가늠할 수 있다. ② 중국 대형은행의 중간배당 확대가 실제 주당 배당으로 이어지는지 봐야 이번 재평가가 지속될 수 있다. ③ 일본 에너지 강세는 장중 수치이므로 원유가격과 종가에서 다시 확인해야 한다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="3" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" s="3" t="inlineStr">
+        <is>
+          <t>■ 배울점: 같은 정책 뉴스라도 예상 현금흐름의 방향이 주가를 갈랐다. 중국 대형은행은 반기 이익 성장과 배당 확대 기대가 주주에게 돌아갈 현금을 늘려 멀티플을 끌어올렸다. 반대로 캘리포니아 전력회사는 산불 책임상한이 빠지면서 미래 소송 현금유출과 꼬리위험이 함께 커져 이익 기대와 멀티플이 동시에 낮아졌다. 다음에는 은행의 실제 배당 공시와 산불 법안 수정안을 보면 이 로직의 지속 여부를 확인할 수 있다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="3" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" s="3" t="inlineStr">
+        <is>
+          <t>■ 참고: 미국·중국A·홍콩은 2026년 8월 31일 마감분이다. 일본은 2026년 9월 1일 오전 10시 22분 KST 장중 스냅샷이므로 종가가 아니다. ETF 44종과 지수 8종은 모두 수집됐다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
         <is>
           <t>※ 60일 컬럼은 TradingView 3개월(약 63거래일) 고저가 기준. 신고/신저 판정: 당일 고가(저가)가 해당 기간 최고(최저)가 도달.</t>
         </is>
@@ -709,19 +791,19 @@
       <c r="C2" t="n">
         <v>7686.14</v>
       </c>
-      <c r="D2" s="2" t="n">
+      <c r="D2" s="4" t="n">
         <v>-0.58</v>
       </c>
-      <c r="E2" s="3" t="n">
+      <c r="E2" s="5" t="n">
         <v>0.15</v>
       </c>
-      <c r="F2" s="3" t="n">
+      <c r="F2" s="5" t="n">
         <v>3.34</v>
       </c>
-      <c r="G2" s="3" t="n">
+      <c r="G2" s="5" t="n">
         <v>1.4</v>
       </c>
-      <c r="H2" s="3" t="n">
+      <c r="H2" s="5" t="n">
         <v>12.28</v>
       </c>
       <c r="I2" t="n">
@@ -747,19 +829,19 @@
       <c r="C3" t="n">
         <v>26370.89</v>
       </c>
-      <c r="D3" s="2" t="n">
+      <c r="D3" s="4" t="n">
         <v>-0.64</v>
       </c>
-      <c r="E3" s="3" t="n">
+      <c r="E3" s="5" t="n">
         <v>0.73</v>
       </c>
-      <c r="F3" s="3" t="n">
+      <c r="F3" s="5" t="n">
         <v>4.97</v>
       </c>
-      <c r="G3" s="2" t="n">
+      <c r="G3" s="4" t="n">
         <v>-2.23</v>
       </c>
-      <c r="H3" s="3" t="n">
+      <c r="H3" s="5" t="n">
         <v>13.46</v>
       </c>
       <c r="I3" t="n">
@@ -785,19 +867,19 @@
       <c r="C4" t="n">
         <v>6843.45</v>
       </c>
-      <c r="D4" s="2" t="n">
+      <c r="D4" s="4" t="n">
         <v>-1</v>
       </c>
-      <c r="E4" s="2" t="n">
+      <c r="E4" s="4" t="n">
         <v>-1.01</v>
       </c>
-      <c r="F4" s="3" t="n">
+      <c r="F4" s="5" t="n">
         <v>20.84</v>
       </c>
-      <c r="G4" s="2" t="n">
+      <c r="G4" s="4" t="n">
         <v>-16.39</v>
       </c>
-      <c r="H4" s="3" t="n">
+      <c r="H4" s="5" t="n">
         <v>62.39</v>
       </c>
       <c r="I4" t="n">
@@ -823,19 +905,19 @@
       <c r="C5" t="n">
         <v>66157.3</v>
       </c>
-      <c r="D5" s="3" t="n">
+      <c r="D5" s="5" t="n">
         <v>0.04</v>
       </c>
-      <c r="E5" s="3" t="n">
+      <c r="E5" s="5" t="n">
         <v>0.21</v>
       </c>
-      <c r="F5" s="3" t="n">
+      <c r="F5" s="5" t="n">
         <v>7.69</v>
       </c>
-      <c r="G5" s="2" t="n">
+      <c r="G5" s="4" t="n">
         <v>-0.26</v>
       </c>
-      <c r="H5" s="3" t="n">
+      <c r="H5" s="5" t="n">
         <v>31.42</v>
       </c>
       <c r="I5" t="n">
@@ -861,19 +943,19 @@
       <c r="C6" t="n">
         <v>3986.3</v>
       </c>
-      <c r="D6" s="3" t="n">
+      <c r="D6" s="5" t="n">
         <v>0.86</v>
       </c>
-      <c r="E6" s="3" t="n">
+      <c r="E6" s="5" t="n">
         <v>2.69</v>
       </c>
-      <c r="F6" s="3" t="n">
+      <c r="F6" s="5" t="n">
         <v>4.02</v>
       </c>
-      <c r="G6" s="2" t="n">
+      <c r="G6" s="4" t="n">
         <v>-2.18</v>
       </c>
-      <c r="H6" s="3" t="n">
+      <c r="H6" s="5" t="n">
         <v>0.44</v>
       </c>
       <c r="I6" t="n">
@@ -899,19 +981,19 @@
       <c r="C7" t="n">
         <v>4625.09</v>
       </c>
-      <c r="D7" s="3" t="n">
+      <c r="D7" s="5" t="n">
         <v>0.35</v>
       </c>
-      <c r="E7" s="3" t="n">
+      <c r="E7" s="5" t="n">
         <v>1.36</v>
       </c>
-      <c r="F7" s="3" t="n">
+      <c r="F7" s="5" t="n">
         <v>0.8</v>
       </c>
-      <c r="G7" s="2" t="n">
+      <c r="G7" s="4" t="n">
         <v>-5.89</v>
       </c>
-      <c r="H7" s="2" t="n">
+      <c r="H7" s="4" t="n">
         <v>-0.1</v>
       </c>
       <c r="I7" t="n">
@@ -937,19 +1019,19 @@
       <c r="C8" t="n">
         <v>25566.99</v>
       </c>
-      <c r="D8" s="2" t="n">
+      <c r="D8" s="4" t="n">
         <v>-0.07000000000000001</v>
       </c>
-      <c r="E8" s="3" t="n">
+      <c r="E8" s="5" t="n">
         <v>0.19</v>
       </c>
-      <c r="F8" s="2" t="n">
+      <c r="F8" s="4" t="n">
         <v>-1.23</v>
       </c>
-      <c r="G8" s="3" t="n">
+      <c r="G8" s="5" t="n">
         <v>0.66</v>
       </c>
-      <c r="H8" s="2" t="n">
+      <c r="H8" s="4" t="n">
         <v>-0.25</v>
       </c>
       <c r="I8" t="n">
@@ -975,19 +1057,19 @@
       <c r="C9" t="n">
         <v>4619.87</v>
       </c>
-      <c r="D9" s="3" t="n">
+      <c r="D9" s="5" t="n">
         <v>0.32</v>
       </c>
-      <c r="E9" s="3" t="n">
+      <c r="E9" s="5" t="n">
         <v>0.5600000000000001</v>
       </c>
-      <c r="F9" s="2" t="n">
+      <c r="F9" s="4" t="n">
         <v>-4.34</v>
       </c>
-      <c r="G9" s="2" t="n">
+      <c r="G9" s="4" t="n">
         <v>-6.95</v>
       </c>
-      <c r="H9" s="2" t="n">
+      <c r="H9" s="4" t="n">
         <v>-16.25</v>
       </c>
       <c r="I9" t="n">
@@ -1106,7 +1188,7 @@
       <c r="F2" t="n">
         <v>8</v>
       </c>
-      <c r="G2" s="4" t="inlineStr">
+      <c r="G2" s="6" t="inlineStr">
         <is>
           <t>강세</t>
         </is>
@@ -1147,7 +1229,7 @@
       <c r="F3" t="n">
         <v>6</v>
       </c>
-      <c r="G3" s="4" t="inlineStr">
+      <c r="G3" s="6" t="inlineStr">
         <is>
           <t>강세</t>
         </is>
@@ -1188,7 +1270,7 @@
       <c r="F4" t="n">
         <v>1</v>
       </c>
-      <c r="G4" s="4" t="inlineStr">
+      <c r="G4" s="6" t="inlineStr">
         <is>
           <t>강세</t>
         </is>
@@ -1229,7 +1311,7 @@
       <c r="F5" t="n">
         <v>1</v>
       </c>
-      <c r="G5" s="4" t="inlineStr">
+      <c r="G5" s="6" t="inlineStr">
         <is>
           <t>강세</t>
         </is>
@@ -1270,7 +1352,7 @@
       <c r="F6" t="n">
         <v>1</v>
       </c>
-      <c r="G6" s="4" t="inlineStr">
+      <c r="G6" s="6" t="inlineStr">
         <is>
           <t>강세</t>
         </is>
@@ -1311,7 +1393,7 @@
       <c r="F7" t="n">
         <v>1</v>
       </c>
-      <c r="G7" s="4" t="inlineStr">
+      <c r="G7" s="6" t="inlineStr">
         <is>
           <t>강세</t>
         </is>
@@ -1352,7 +1434,7 @@
       <c r="F8" t="n">
         <v>-1</v>
       </c>
-      <c r="G8" s="5" t="inlineStr">
+      <c r="G8" s="7" t="inlineStr">
         <is>
           <t>약세</t>
         </is>
@@ -1393,7 +1475,7 @@
       <c r="F9" t="n">
         <v>-1</v>
       </c>
-      <c r="G9" s="5" t="inlineStr">
+      <c r="G9" s="7" t="inlineStr">
         <is>
           <t>약세</t>
         </is>
@@ -1434,7 +1516,7 @@
       <c r="F10" t="n">
         <v>-3</v>
       </c>
-      <c r="G10" s="5" t="inlineStr">
+      <c r="G10" s="7" t="inlineStr">
         <is>
           <t>약세</t>
         </is>
@@ -1475,7 +1557,7 @@
       <c r="F11" t="n">
         <v>-3</v>
       </c>
-      <c r="G11" s="5" t="inlineStr">
+      <c r="G11" s="7" t="inlineStr">
         <is>
           <t>약세</t>
         </is>
@@ -1516,7 +1598,7 @@
       <c r="F12" t="n">
         <v>-3</v>
       </c>
-      <c r="G12" s="5" t="inlineStr">
+      <c r="G12" s="7" t="inlineStr">
         <is>
           <t>약세</t>
         </is>
@@ -1557,7 +1639,7 @@
       <c r="F13" t="n">
         <v>-4</v>
       </c>
-      <c r="G13" s="5" t="inlineStr">
+      <c r="G13" s="7" t="inlineStr">
         <is>
           <t>약세</t>
         </is>
@@ -1598,7 +1680,7 @@
       <c r="F14" t="n">
         <v>-10</v>
       </c>
-      <c r="G14" s="5" t="inlineStr">
+      <c r="G14" s="7" t="inlineStr">
         <is>
           <t>약세</t>
         </is>
@@ -1639,7 +1721,7 @@
       <c r="F15" t="n">
         <v>-10</v>
       </c>
-      <c r="G15" s="5" t="inlineStr">
+      <c r="G15" s="7" t="inlineStr">
         <is>
           <t>약세</t>
         </is>
@@ -1680,7 +1762,7 @@
       <c r="F16" t="n">
         <v>-11</v>
       </c>
-      <c r="G16" s="5" t="inlineStr">
+      <c r="G16" s="7" t="inlineStr">
         <is>
           <t>약세</t>
         </is>
@@ -1721,7 +1803,7 @@
       <c r="F17" t="n">
         <v>-21</v>
       </c>
-      <c r="G17" s="5" t="inlineStr">
+      <c r="G17" s="7" t="inlineStr">
         <is>
           <t>약세</t>
         </is>
@@ -1924,7 +2006,7 @@
       <c r="F22" t="n">
         <v>3</v>
       </c>
-      <c r="G22" s="4" t="inlineStr">
+      <c r="G22" s="6" t="inlineStr">
         <is>
           <t>강세</t>
         </is>
@@ -1965,7 +2047,7 @@
       <c r="F23" t="n">
         <v>3</v>
       </c>
-      <c r="G23" s="4" t="inlineStr">
+      <c r="G23" s="6" t="inlineStr">
         <is>
           <t>강세</t>
         </is>
@@ -2004,7 +2086,7 @@
       <c r="F24" t="n">
         <v>3</v>
       </c>
-      <c r="G24" s="4" t="inlineStr">
+      <c r="G24" s="6" t="inlineStr">
         <is>
           <t>강세</t>
         </is>
@@ -2045,7 +2127,7 @@
       <c r="F25" t="n">
         <v>2</v>
       </c>
-      <c r="G25" s="4" t="inlineStr">
+      <c r="G25" s="6" t="inlineStr">
         <is>
           <t>강세</t>
         </is>
@@ -2086,7 +2168,7 @@
       <c r="F26" t="n">
         <v>2</v>
       </c>
-      <c r="G26" s="4" t="inlineStr">
+      <c r="G26" s="6" t="inlineStr">
         <is>
           <t>강세</t>
         </is>
@@ -2125,7 +2207,7 @@
       <c r="F27" t="n">
         <v>1</v>
       </c>
-      <c r="G27" s="4" t="inlineStr">
+      <c r="G27" s="6" t="inlineStr">
         <is>
           <t>강세</t>
         </is>
@@ -2164,7 +2246,7 @@
       <c r="F28" t="n">
         <v>1</v>
       </c>
-      <c r="G28" s="4" t="inlineStr">
+      <c r="G28" s="6" t="inlineStr">
         <is>
           <t>강세</t>
         </is>
@@ -2203,7 +2285,7 @@
       <c r="F29" t="n">
         <v>1</v>
       </c>
-      <c r="G29" s="4" t="inlineStr">
+      <c r="G29" s="6" t="inlineStr">
         <is>
           <t>강세</t>
         </is>
@@ -2244,7 +2326,7 @@
       <c r="F30" t="n">
         <v>-1</v>
       </c>
-      <c r="G30" s="5" t="inlineStr">
+      <c r="G30" s="7" t="inlineStr">
         <is>
           <t>약세</t>
         </is>
@@ -2285,7 +2367,7 @@
       <c r="F31" t="n">
         <v>-1</v>
       </c>
-      <c r="G31" s="5" t="inlineStr">
+      <c r="G31" s="7" t="inlineStr">
         <is>
           <t>약세</t>
         </is>
@@ -2677,7 +2759,7 @@
       <c r="F41" t="n">
         <v>7</v>
       </c>
-      <c r="G41" s="4" t="inlineStr">
+      <c r="G41" s="6" t="inlineStr">
         <is>
           <t>강세</t>
         </is>
@@ -2718,7 +2800,7 @@
       <c r="F42" t="n">
         <v>1</v>
       </c>
-      <c r="G42" s="4" t="inlineStr">
+      <c r="G42" s="6" t="inlineStr">
         <is>
           <t>강세</t>
         </is>
@@ -2757,7 +2839,7 @@
       <c r="F43" t="n">
         <v>1</v>
       </c>
-      <c r="G43" s="4" t="inlineStr">
+      <c r="G43" s="6" t="inlineStr">
         <is>
           <t>강세</t>
         </is>
@@ -2796,7 +2878,7 @@
       <c r="F44" t="n">
         <v>-1</v>
       </c>
-      <c r="G44" s="5" t="inlineStr">
+      <c r="G44" s="7" t="inlineStr">
         <is>
           <t>약세</t>
         </is>
@@ -2835,7 +2917,7 @@
       <c r="F45" t="n">
         <v>-1</v>
       </c>
-      <c r="G45" s="5" t="inlineStr">
+      <c r="G45" s="7" t="inlineStr">
         <is>
           <t>약세</t>
         </is>
@@ -2876,7 +2958,7 @@
       <c r="F46" t="n">
         <v>-1</v>
       </c>
-      <c r="G46" s="5" t="inlineStr">
+      <c r="G46" s="7" t="inlineStr">
         <is>
           <t>약세</t>
         </is>
@@ -2917,7 +2999,7 @@
       <c r="F47" t="n">
         <v>-1</v>
       </c>
-      <c r="G47" s="5" t="inlineStr">
+      <c r="G47" s="7" t="inlineStr">
         <is>
           <t>약세</t>
         </is>
@@ -2956,7 +3038,7 @@
       <c r="F48" t="n">
         <v>-1</v>
       </c>
-      <c r="G48" s="5" t="inlineStr">
+      <c r="G48" s="7" t="inlineStr">
         <is>
           <t>약세</t>
         </is>
@@ -2997,7 +3079,7 @@
       <c r="F49" t="n">
         <v>-2</v>
       </c>
-      <c r="G49" s="5" t="inlineStr">
+      <c r="G49" s="7" t="inlineStr">
         <is>
           <t>약세</t>
         </is>
@@ -3036,7 +3118,7 @@
       <c r="F50" t="n">
         <v>-3</v>
       </c>
-      <c r="G50" s="5" t="inlineStr">
+      <c r="G50" s="7" t="inlineStr">
         <is>
           <t>약세</t>
         </is>
@@ -3393,7 +3475,7 @@
       <c r="F59" t="n">
         <v>6</v>
       </c>
-      <c r="G59" s="4" t="inlineStr">
+      <c r="G59" s="6" t="inlineStr">
         <is>
           <t>강세</t>
         </is>
@@ -3434,7 +3516,7 @@
       <c r="F60" t="n">
         <v>3</v>
       </c>
-      <c r="G60" s="4" t="inlineStr">
+      <c r="G60" s="6" t="inlineStr">
         <is>
           <t>강세</t>
         </is>
@@ -3473,7 +3555,7 @@
       <c r="F61" t="n">
         <v>2</v>
       </c>
-      <c r="G61" s="4" t="inlineStr">
+      <c r="G61" s="6" t="inlineStr">
         <is>
           <t>강세</t>
         </is>
@@ -3512,7 +3594,7 @@
       <c r="F62" t="n">
         <v>1</v>
       </c>
-      <c r="G62" s="4" t="inlineStr">
+      <c r="G62" s="6" t="inlineStr">
         <is>
           <t>강세</t>
         </is>
@@ -3551,7 +3633,7 @@
       <c r="F63" t="n">
         <v>1</v>
       </c>
-      <c r="G63" s="4" t="inlineStr">
+      <c r="G63" s="6" t="inlineStr">
         <is>
           <t>강세</t>
         </is>
@@ -3590,7 +3672,7 @@
       <c r="F64" t="n">
         <v>1</v>
       </c>
-      <c r="G64" s="4" t="inlineStr">
+      <c r="G64" s="6" t="inlineStr">
         <is>
           <t>강세</t>
         </is>
@@ -3631,7 +3713,7 @@
       <c r="F65" t="n">
         <v>1</v>
       </c>
-      <c r="G65" s="4" t="inlineStr">
+      <c r="G65" s="6" t="inlineStr">
         <is>
           <t>강세</t>
         </is>
@@ -3672,7 +3754,7 @@
       <c r="F66" t="n">
         <v>-3</v>
       </c>
-      <c r="G66" s="5" t="inlineStr">
+      <c r="G66" s="7" t="inlineStr">
         <is>
           <t>약세</t>
         </is>
@@ -4101,30 +4183,31 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U47"/>
+  <dimension ref="A1:V47"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
     <col width="19" customWidth="1" min="2" max="2"/>
     <col width="18" customWidth="1" min="3" max="3"/>
-    <col width="8" customWidth="1" min="4" max="4"/>
+    <col width="95" customWidth="1" min="4" max="4"/>
     <col width="8" customWidth="1" min="5" max="5"/>
     <col width="8" customWidth="1" min="6" max="6"/>
     <col width="8" customWidth="1" min="7" max="7"/>
     <col width="8" customWidth="1" min="8" max="8"/>
-    <col width="6" customWidth="1" min="9" max="9"/>
-    <col width="8" customWidth="1" min="10" max="10"/>
-    <col width="6" customWidth="1" min="11" max="11"/>
-    <col width="8" customWidth="1" min="12" max="12"/>
-    <col width="6" customWidth="1" min="13" max="13"/>
-    <col width="8" customWidth="1" min="14" max="14"/>
-    <col width="6" customWidth="1" min="15" max="15"/>
-    <col width="8" customWidth="1" min="16" max="16"/>
-    <col width="6" customWidth="1" min="17" max="17"/>
-    <col width="8" customWidth="1" min="18" max="18"/>
-    <col width="6" customWidth="1" min="19" max="19"/>
-    <col width="8" customWidth="1" min="20" max="20"/>
-    <col width="6" customWidth="1" min="21" max="21"/>
+    <col width="8" customWidth="1" min="9" max="9"/>
+    <col width="6" customWidth="1" min="10" max="10"/>
+    <col width="8" customWidth="1" min="11" max="11"/>
+    <col width="6" customWidth="1" min="12" max="12"/>
+    <col width="8" customWidth="1" min="13" max="13"/>
+    <col width="6" customWidth="1" min="14" max="14"/>
+    <col width="8" customWidth="1" min="15" max="15"/>
+    <col width="6" customWidth="1" min="16" max="16"/>
+    <col width="8" customWidth="1" min="17" max="17"/>
+    <col width="6" customWidth="1" min="18" max="18"/>
+    <col width="8" customWidth="1" min="19" max="19"/>
+    <col width="6" customWidth="1" min="20" max="20"/>
+    <col width="8" customWidth="1" min="21" max="21"/>
+    <col width="6" customWidth="1" min="22" max="22"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -4145,90 +4228,95 @@
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
+          <t>코멘트</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
           <t>1D</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>1주</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>1M</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>3M</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>YTD26</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>순위26</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>YTD25</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>순위25</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>YTD24</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>순위24</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="O1" s="1" t="inlineStr">
         <is>
           <t>YTD23</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="P1" s="1" t="inlineStr">
         <is>
           <t>순위23</t>
         </is>
       </c>
-      <c r="P1" s="1" t="inlineStr">
+      <c r="Q1" s="1" t="inlineStr">
         <is>
           <t>YTD22</t>
         </is>
       </c>
-      <c r="Q1" s="1" t="inlineStr">
+      <c r="R1" s="1" t="inlineStr">
         <is>
           <t>순위22</t>
         </is>
       </c>
-      <c r="R1" s="1" t="inlineStr">
+      <c r="S1" s="1" t="inlineStr">
         <is>
           <t>YTD21</t>
         </is>
       </c>
-      <c r="S1" s="1" t="inlineStr">
+      <c r="T1" s="1" t="inlineStr">
         <is>
           <t>순위21</t>
         </is>
       </c>
-      <c r="T1" s="1" t="inlineStr">
+      <c r="U1" s="1" t="inlineStr">
         <is>
           <t>YTD20</t>
         </is>
       </c>
-      <c r="U1" s="1" t="inlineStr">
+      <c r="V1" s="1" t="inlineStr">
         <is>
           <t>순위20</t>
         </is>
@@ -4250,58 +4338,63 @@
           <t>테크</t>
         </is>
       </c>
-      <c r="D2" s="6" t="n">
+      <c r="D2" s="8" t="inlineStr">
+        <is>
+          <t>ETF는 1.1% 내렸지만 기술서비스 순강도는 8로 소프트웨어와 하드웨어가 갈렸다.</t>
+        </is>
+      </c>
+      <c r="E2" s="9" t="n">
         <v>-1.1</v>
       </c>
-      <c r="E2" s="6" t="n">
+      <c r="F2" s="9" t="n">
         <v>1.7</v>
       </c>
-      <c r="F2" s="6" t="n">
+      <c r="G2" s="9" t="n">
         <v>6.1</v>
       </c>
-      <c r="G2" s="6" t="n">
+      <c r="H2" s="9" t="n">
         <v>-2.2</v>
       </c>
-      <c r="H2" s="6" t="n">
+      <c r="I2" s="9" t="n">
         <v>29.9</v>
       </c>
-      <c r="I2" t="n">
+      <c r="J2" t="n">
         <v>2</v>
       </c>
-      <c r="J2" s="6" t="n">
+      <c r="K2" s="9" t="n">
         <v>24.6</v>
       </c>
-      <c r="K2" t="n">
+      <c r="L2" t="n">
         <v>1</v>
       </c>
-      <c r="L2" s="6" t="n">
+      <c r="M2" s="9" t="n">
         <v>21.6</v>
       </c>
-      <c r="M2" t="n">
+      <c r="N2" t="n">
         <v>5</v>
       </c>
-      <c r="N2" s="6" t="n">
+      <c r="O2" s="9" t="n">
         <v>56</v>
       </c>
-      <c r="O2" t="n">
+      <c r="P2" t="n">
         <v>1</v>
       </c>
-      <c r="P2" s="6" t="n">
+      <c r="Q2" s="9" t="n">
         <v>-27.7</v>
       </c>
-      <c r="Q2" t="n">
+      <c r="R2" t="n">
         <v>9</v>
       </c>
-      <c r="R2" s="6" t="n">
+      <c r="S2" s="9" t="n">
         <v>34.7</v>
       </c>
-      <c r="S2" t="n">
+      <c r="T2" t="n">
         <v>4</v>
       </c>
-      <c r="T2" s="6" t="n">
+      <c r="U2" s="9" t="n">
         <v>43.6</v>
       </c>
-      <c r="U2" t="n">
+      <c r="V2" t="n">
         <v>1</v>
       </c>
     </row>
@@ -4321,58 +4414,63 @@
           <t>헬스케어</t>
         </is>
       </c>
-      <c r="D3" s="6" t="n">
+      <c r="D3" s="8" t="inlineStr">
+        <is>
+          <t>ETF는 0.6% 내렸고 헬스케어 신고가 우위도 순강도 1에 그쳤다.</t>
+        </is>
+      </c>
+      <c r="E3" s="9" t="n">
         <v>-0.6</v>
       </c>
-      <c r="E3" s="6" t="n">
+      <c r="F3" s="9" t="n">
         <v>-2.3</v>
       </c>
-      <c r="F3" s="6" t="n">
+      <c r="G3" s="9" t="n">
         <v>4.3</v>
       </c>
-      <c r="G3" s="6" t="n">
+      <c r="H3" s="9" t="n">
         <v>14.6</v>
       </c>
-      <c r="H3" s="6" t="n">
+      <c r="I3" s="9" t="n">
         <v>11.1</v>
       </c>
-      <c r="I3" t="n">
+      <c r="J3" t="n">
         <v>5</v>
       </c>
-      <c r="J3" s="6" t="n">
+      <c r="K3" s="9" t="n">
         <v>14.5</v>
       </c>
-      <c r="K3" t="n">
+      <c r="L3" t="n">
         <v>6</v>
       </c>
-      <c r="L3" s="6" t="n">
+      <c r="M3" s="9" t="n">
         <v>2.5</v>
       </c>
-      <c r="M3" t="n">
+      <c r="N3" t="n">
         <v>10</v>
       </c>
-      <c r="N3" s="6" t="n">
+      <c r="O3" s="9" t="n">
         <v>2.1</v>
       </c>
-      <c r="O3" t="n">
+      <c r="P3" t="n">
         <v>8</v>
       </c>
-      <c r="P3" s="6" t="n">
+      <c r="Q3" s="9" t="n">
         <v>-2.1</v>
       </c>
-      <c r="Q3" t="n">
+      <c r="R3" t="n">
         <v>4</v>
       </c>
-      <c r="R3" s="6" t="n">
+      <c r="S3" s="9" t="n">
         <v>26</v>
       </c>
-      <c r="S3" t="n">
+      <c r="T3" t="n">
         <v>7</v>
       </c>
-      <c r="T3" s="6" t="n">
+      <c r="U3" s="9" t="n">
         <v>13.3</v>
       </c>
-      <c r="U3" t="n">
+      <c r="V3" t="n">
         <v>5</v>
       </c>
     </row>
@@ -4392,58 +4490,63 @@
           <t>금융</t>
         </is>
       </c>
-      <c r="D4" s="6" t="n">
+      <c r="D4" s="8" t="inlineStr">
+        <is>
+          <t>ETF는 0.3% 내렸지만 금융 신저가가 13종으로 개별주 하방은 더 넓었다.</t>
+        </is>
+      </c>
+      <c r="E4" s="9" t="n">
         <v>-0.3</v>
       </c>
-      <c r="E4" s="6" t="n">
+      <c r="F4" s="9" t="n">
         <v>0.4</v>
       </c>
-      <c r="F4" s="6" t="n">
+      <c r="G4" s="9" t="n">
         <v>1.2</v>
       </c>
-      <c r="G4" s="6" t="n">
+      <c r="H4" s="9" t="n">
         <v>12.3</v>
       </c>
-      <c r="H4" s="6" t="n">
+      <c r="I4" s="9" t="n">
         <v>6.3</v>
       </c>
-      <c r="I4" t="n">
+      <c r="J4" t="n">
         <v>8</v>
       </c>
-      <c r="J4" s="6" t="n">
+      <c r="K4" s="9" t="n">
         <v>14.9</v>
       </c>
-      <c r="K4" t="n">
+      <c r="L4" t="n">
         <v>5</v>
       </c>
-      <c r="L4" s="6" t="n">
+      <c r="M4" s="9" t="n">
         <v>30.6</v>
       </c>
-      <c r="M4" t="n">
+      <c r="N4" t="n">
         <v>2</v>
       </c>
-      <c r="N4" s="6" t="n">
+      <c r="O4" s="9" t="n">
         <v>12</v>
       </c>
-      <c r="O4" t="n">
+      <c r="P4" t="n">
         <v>7</v>
       </c>
-      <c r="P4" s="6" t="n">
+      <c r="Q4" s="9" t="n">
         <v>-10.6</v>
       </c>
-      <c r="Q4" t="n">
+      <c r="R4" t="n">
         <v>6</v>
       </c>
-      <c r="R4" s="6" t="n">
+      <c r="S4" s="9" t="n">
         <v>34.8</v>
       </c>
-      <c r="S4" t="n">
+      <c r="T4" t="n">
         <v>3</v>
       </c>
-      <c r="T4" s="6" t="n">
+      <c r="U4" s="9" t="n">
         <v>-1.7</v>
       </c>
-      <c r="U4" t="n">
+      <c r="V4" t="n">
         <v>9</v>
       </c>
     </row>
@@ -4463,58 +4566,63 @@
           <t>경기소비재</t>
         </is>
       </c>
-      <c r="D5" s="6" t="n">
+      <c r="D5" s="8" t="inlineStr">
+        <is>
+          <t>ETF는 0.6% 올랐지만 내구소비재 순강도는 -1로 종목 확산은 약했다.</t>
+        </is>
+      </c>
+      <c r="E5" s="9" t="n">
         <v>0.6</v>
       </c>
-      <c r="E5" s="6" t="n">
+      <c r="F5" s="9" t="n">
         <v>-1.2</v>
       </c>
-      <c r="F5" s="6" t="n">
+      <c r="G5" s="9" t="n">
         <v>3.7</v>
       </c>
-      <c r="G5" s="6" t="n">
+      <c r="H5" s="9" t="n">
         <v>-3.3</v>
       </c>
-      <c r="H5" s="6" t="n">
+      <c r="I5" s="9" t="n">
         <v>-2</v>
       </c>
-      <c r="I5" t="n">
+      <c r="J5" t="n">
         <v>10</v>
       </c>
-      <c r="J5" s="6" t="n">
+      <c r="K5" s="9" t="n">
         <v>7.4</v>
       </c>
-      <c r="K5" t="n">
+      <c r="L5" t="n">
         <v>9</v>
       </c>
-      <c r="L5" s="6" t="n">
+      <c r="M5" s="9" t="n">
         <v>26.5</v>
       </c>
-      <c r="M5" t="n">
+      <c r="N5" t="n">
         <v>3</v>
       </c>
-      <c r="N5" s="6" t="n">
+      <c r="O5" s="9" t="n">
         <v>39.6</v>
       </c>
-      <c r="O5" t="n">
+      <c r="P5" t="n">
         <v>3</v>
       </c>
-      <c r="P5" s="6" t="n">
+      <c r="Q5" s="9" t="n">
         <v>-36.3</v>
       </c>
-      <c r="Q5" t="n">
+      <c r="R5" t="n">
         <v>10</v>
       </c>
-      <c r="R5" s="6" t="n">
+      <c r="S5" s="9" t="n">
         <v>27.9</v>
       </c>
-      <c r="S5" t="n">
+      <c r="T5" t="n">
         <v>5</v>
       </c>
-      <c r="T5" s="6" t="n">
+      <c r="U5" s="9" t="n">
         <v>29.6</v>
       </c>
-      <c r="U5" t="n">
+      <c r="V5" t="n">
         <v>2</v>
       </c>
     </row>
@@ -4534,58 +4642,63 @@
           <t>커뮤니케이션</t>
         </is>
       </c>
-      <c r="D6" s="6" t="n">
+      <c r="D6" s="8" t="inlineStr">
+        <is>
+          <t>ETF는 보합이었고 통신 순강도는 1로 뚜렷한 방향이 나타나지 않았다.</t>
+        </is>
+      </c>
+      <c r="E6" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="E6" s="6" t="n">
+      <c r="F6" s="9" t="n">
         <v>0.1</v>
       </c>
-      <c r="F6" s="6" t="n">
+      <c r="G6" s="9" t="n">
         <v>4.6</v>
       </c>
-      <c r="G6" s="6" t="n">
+      <c r="H6" s="9" t="n">
         <v>-3.4</v>
       </c>
-      <c r="H6" s="6" t="n">
+      <c r="I6" s="9" t="n">
         <v>-4.8</v>
       </c>
-      <c r="I6" t="n">
+      <c r="J6" t="n">
         <v>11</v>
       </c>
-      <c r="J6" s="6" t="n">
+      <c r="K6" s="9" t="n">
         <v>23.1</v>
       </c>
-      <c r="K6" t="n">
+      <c r="L6" t="n">
         <v>2</v>
       </c>
-      <c r="L6" s="6" t="n">
+      <c r="M6" s="9" t="n">
         <v>34.7</v>
       </c>
-      <c r="M6" t="n">
+      <c r="N6" t="n">
         <v>1</v>
       </c>
-      <c r="N6" s="6" t="n">
+      <c r="O6" s="9" t="n">
         <v>52.8</v>
       </c>
-      <c r="O6" t="n">
+      <c r="P6" t="n">
         <v>2</v>
       </c>
-      <c r="P6" s="6" t="n">
+      <c r="Q6" s="9" t="n">
         <v>-37.6</v>
       </c>
-      <c r="Q6" t="n">
+      <c r="R6" t="n">
         <v>11</v>
       </c>
-      <c r="R6" s="6" t="n">
+      <c r="S6" s="9" t="n">
         <v>16</v>
       </c>
-      <c r="S6" t="n">
+      <c r="T6" t="n">
         <v>11</v>
       </c>
-      <c r="T6" s="6" t="n">
+      <c r="U6" s="9" t="n">
         <v>26.9</v>
       </c>
-      <c r="U6" t="n">
+      <c r="V6" t="n">
         <v>3</v>
       </c>
     </row>
@@ -4605,58 +4718,63 @@
           <t>산업재</t>
         </is>
       </c>
-      <c r="D7" s="6" t="n">
+      <c r="D7" s="8" t="inlineStr">
+        <is>
+          <t>ETF는 2.1% 내렸고 생산재 신저가 11종이 산업주 전반의 약세를 확인했다.</t>
+        </is>
+      </c>
+      <c r="E7" s="9" t="n">
         <v>-2.1</v>
       </c>
-      <c r="E7" s="6" t="n">
+      <c r="F7" s="9" t="n">
         <v>-2.8</v>
       </c>
-      <c r="F7" s="6" t="n">
+      <c r="G7" s="9" t="n">
         <v>-1.8</v>
       </c>
-      <c r="G7" s="6" t="n">
+      <c r="H7" s="9" t="n">
         <v>1.4</v>
       </c>
-      <c r="H7" s="6" t="n">
+      <c r="I7" s="9" t="n">
         <v>13.5</v>
       </c>
-      <c r="I7" t="n">
+      <c r="J7" t="n">
         <v>4</v>
       </c>
-      <c r="J7" s="6" t="n">
+      <c r="K7" s="9" t="n">
         <v>19.3</v>
       </c>
-      <c r="K7" t="n">
+      <c r="L7" t="n">
         <v>3</v>
       </c>
-      <c r="L7" s="6" t="n">
+      <c r="M7" s="9" t="n">
         <v>17.3</v>
       </c>
-      <c r="M7" t="n">
+      <c r="N7" t="n">
         <v>6</v>
       </c>
-      <c r="N7" s="6" t="n">
+      <c r="O7" s="9" t="n">
         <v>18.1</v>
       </c>
-      <c r="O7" t="n">
+      <c r="P7" t="n">
         <v>4</v>
       </c>
-      <c r="P7" s="6" t="n">
+      <c r="Q7" s="9" t="n">
         <v>-5.6</v>
       </c>
-      <c r="Q7" t="n">
+      <c r="R7" t="n">
         <v>5</v>
       </c>
-      <c r="R7" s="6" t="n">
+      <c r="S7" s="9" t="n">
         <v>21.1</v>
       </c>
-      <c r="S7" t="n">
+      <c r="T7" t="n">
         <v>8</v>
       </c>
-      <c r="T7" s="6" t="n">
+      <c r="U7" s="9" t="n">
         <v>10.9</v>
       </c>
-      <c r="U7" t="n">
+      <c r="V7" t="n">
         <v>6</v>
       </c>
     </row>
@@ -4676,58 +4794,63 @@
           <t>필수소비재</t>
         </is>
       </c>
-      <c r="D8" s="6" t="n">
+      <c r="D8" s="8" t="inlineStr">
+        <is>
+          <t>ETF는 0.1% 내렸지만 필수소비재 순강도는 1로 방어력은 제한적이었다.</t>
+        </is>
+      </c>
+      <c r="E8" s="9" t="n">
         <v>-0.1</v>
       </c>
-      <c r="E8" s="6" t="n">
+      <c r="F8" s="9" t="n">
         <v>-1.2</v>
       </c>
-      <c r="F8" s="6" t="n">
+      <c r="G8" s="9" t="n">
         <v>-0.6</v>
       </c>
-      <c r="G8" s="6" t="n">
+      <c r="H8" s="9" t="n">
         <v>3.2</v>
       </c>
-      <c r="H8" s="6" t="n">
+      <c r="I8" s="9" t="n">
         <v>10.8</v>
       </c>
-      <c r="I8" t="n">
+      <c r="J8" t="n">
         <v>7</v>
       </c>
-      <c r="J8" s="6" t="n">
+      <c r="K8" s="9" t="n">
         <v>1.5</v>
       </c>
-      <c r="K8" t="n">
+      <c r="L8" t="n">
         <v>11</v>
       </c>
-      <c r="L8" s="6" t="n">
+      <c r="M8" s="9" t="n">
         <v>12.2</v>
       </c>
-      <c r="M8" t="n">
+      <c r="N8" t="n">
         <v>7</v>
       </c>
-      <c r="N8" s="6" t="n">
+      <c r="O8" s="9" t="n">
         <v>-0.8</v>
       </c>
-      <c r="O8" t="n">
+      <c r="P8" t="n">
         <v>10</v>
       </c>
-      <c r="P8" s="6" t="n">
+      <c r="Q8" s="9" t="n">
         <v>-0.8</v>
       </c>
-      <c r="Q8" t="n">
+      <c r="R8" t="n">
         <v>3</v>
       </c>
-      <c r="R8" s="6" t="n">
+      <c r="S8" s="9" t="n">
         <v>17.2</v>
       </c>
-      <c r="S8" t="n">
+      <c r="T8" t="n">
         <v>10</v>
       </c>
-      <c r="T8" s="6" t="n">
+      <c r="U8" s="9" t="n">
         <v>10.1</v>
       </c>
-      <c r="U8" t="n">
+      <c r="V8" t="n">
         <v>7</v>
       </c>
     </row>
@@ -4747,58 +4870,63 @@
           <t>에너지</t>
         </is>
       </c>
-      <c r="D9" s="6" t="n">
+      <c r="D9" s="8" t="inlineStr">
+        <is>
+          <t>ETF는 2.7% 올라 미국 섹터 1위를 기록했고 에너지 순강도도 6이었다.</t>
+        </is>
+      </c>
+      <c r="E9" s="9" t="n">
         <v>2.7</v>
       </c>
-      <c r="E9" s="6" t="n">
+      <c r="F9" s="9" t="n">
         <v>0.5</v>
       </c>
-      <c r="F9" s="6" t="n">
+      <c r="G9" s="9" t="n">
         <v>8.5</v>
       </c>
-      <c r="G9" s="6" t="n">
+      <c r="H9" s="9" t="n">
         <v>14.4</v>
       </c>
-      <c r="H9" s="6" t="n">
+      <c r="I9" s="9" t="n">
         <v>45</v>
       </c>
-      <c r="I9" t="n">
+      <c r="J9" t="n">
         <v>1</v>
       </c>
-      <c r="J9" s="6" t="n">
+      <c r="K9" s="9" t="n">
         <v>7.9</v>
       </c>
-      <c r="K9" t="n">
+      <c r="L9" t="n">
         <v>8</v>
       </c>
-      <c r="L9" s="6" t="n">
+      <c r="M9" s="9" t="n">
         <v>5.6</v>
       </c>
-      <c r="M9" t="n">
+      <c r="N9" t="n">
         <v>8</v>
       </c>
-      <c r="N9" s="6" t="n">
+      <c r="O9" s="9" t="n">
         <v>-0.6</v>
       </c>
-      <c r="O9" t="n">
+      <c r="P9" t="n">
         <v>9</v>
       </c>
-      <c r="P9" s="6" t="n">
+      <c r="Q9" s="9" t="n">
         <v>64.3</v>
       </c>
-      <c r="Q9" t="n">
+      <c r="R9" t="n">
         <v>1</v>
       </c>
-      <c r="R9" s="6" t="n">
+      <c r="S9" s="9" t="n">
         <v>53.3</v>
       </c>
-      <c r="S9" t="n">
+      <c r="T9" t="n">
         <v>1</v>
       </c>
-      <c r="T9" s="6" t="n">
+      <c r="U9" s="9" t="n">
         <v>-32.7</v>
       </c>
-      <c r="U9" t="n">
+      <c r="V9" t="n">
         <v>11</v>
       </c>
     </row>
@@ -4818,58 +4946,63 @@
           <t>유틸리티</t>
         </is>
       </c>
-      <c r="D10" s="6" t="n">
+      <c r="D10" s="8" t="inlineStr">
+        <is>
+          <t>ETF는 2.2% 내렸고 산불 법안 실망으로 유틸리티 순강도가 -21까지 밀렸다.</t>
+        </is>
+      </c>
+      <c r="E10" s="9" t="n">
         <v>-2.2</v>
       </c>
-      <c r="E10" s="6" t="n">
+      <c r="F10" s="9" t="n">
         <v>-1.3</v>
       </c>
-      <c r="F10" s="6" t="n">
+      <c r="G10" s="9" t="n">
         <v>-5.4</v>
       </c>
-      <c r="G10" s="6" t="n">
+      <c r="H10" s="9" t="n">
         <v>-4.3</v>
       </c>
-      <c r="H10" s="6" t="n">
+      <c r="I10" s="9" t="n">
         <v>0.3</v>
       </c>
-      <c r="I10" t="n">
+      <c r="J10" t="n">
         <v>9</v>
       </c>
-      <c r="J10" s="6" t="n">
+      <c r="K10" s="9" t="n">
         <v>16</v>
       </c>
-      <c r="K10" t="n">
+      <c r="L10" t="n">
         <v>4</v>
       </c>
-      <c r="L10" s="6" t="n">
+      <c r="M10" s="9" t="n">
         <v>23.3</v>
       </c>
-      <c r="M10" t="n">
+      <c r="N10" t="n">
         <v>4</v>
       </c>
-      <c r="N10" s="6" t="n">
+      <c r="O10" s="9" t="n">
         <v>-7.2</v>
       </c>
-      <c r="O10" t="n">
+      <c r="P10" t="n">
         <v>11</v>
       </c>
-      <c r="P10" s="6" t="n">
+      <c r="Q10" s="9" t="n">
         <v>1.4</v>
       </c>
-      <c r="Q10" t="n">
+      <c r="R10" t="n">
         <v>2</v>
       </c>
-      <c r="R10" s="6" t="n">
+      <c r="S10" s="9" t="n">
         <v>17.7</v>
       </c>
-      <c r="S10" t="n">
+      <c r="T10" t="n">
         <v>9</v>
       </c>
-      <c r="T10" s="6" t="n">
+      <c r="U10" s="9" t="n">
         <v>0.5</v>
       </c>
-      <c r="U10" t="n">
+      <c r="V10" t="n">
         <v>8</v>
       </c>
     </row>
@@ -4889,58 +5022,63 @@
           <t>소재</t>
         </is>
       </c>
-      <c r="D11" s="6" t="n">
+      <c r="D11" s="8" t="inlineStr">
+        <is>
+          <t>ETF는 1.0% 내렸고 비에너지 광물 신저가 3종이 소재 약세를 뒷받침했다.</t>
+        </is>
+      </c>
+      <c r="E11" s="9" t="n">
         <v>-1</v>
       </c>
-      <c r="E11" s="6" t="n">
+      <c r="F11" s="9" t="n">
         <v>-1.6</v>
       </c>
-      <c r="F11" s="6" t="n">
+      <c r="G11" s="9" t="n">
         <v>2</v>
       </c>
-      <c r="G11" s="6" t="n">
+      <c r="H11" s="9" t="n">
         <v>3.4</v>
       </c>
-      <c r="H11" s="6" t="n">
+      <c r="I11" s="9" t="n">
         <v>17.1</v>
       </c>
-      <c r="I11" t="n">
+      <c r="J11" t="n">
         <v>3</v>
       </c>
-      <c r="J11" s="6" t="n">
+      <c r="K11" s="9" t="n">
         <v>9.9</v>
       </c>
-      <c r="K11" t="n">
+      <c r="L11" t="n">
         <v>7</v>
       </c>
-      <c r="L11" s="6" t="n">
+      <c r="M11" s="9" t="n">
         <v>0.1</v>
       </c>
-      <c r="M11" t="n">
+      <c r="N11" t="n">
         <v>11</v>
       </c>
-      <c r="N11" s="6" t="n">
+      <c r="O11" s="9" t="n">
         <v>12.5</v>
       </c>
-      <c r="O11" t="n">
+      <c r="P11" t="n">
         <v>5</v>
       </c>
-      <c r="P11" s="6" t="n">
+      <c r="Q11" s="9" t="n">
         <v>-12.3</v>
       </c>
-      <c r="Q11" t="n">
+      <c r="R11" t="n">
         <v>7</v>
       </c>
-      <c r="R11" s="6" t="n">
+      <c r="S11" s="9" t="n">
         <v>27.4</v>
       </c>
-      <c r="S11" t="n">
+      <c r="T11" t="n">
         <v>6</v>
       </c>
-      <c r="T11" s="6" t="n">
+      <c r="U11" s="9" t="n">
         <v>20.5</v>
       </c>
-      <c r="U11" t="n">
+      <c r="V11" t="n">
         <v>4</v>
       </c>
     </row>
@@ -4960,58 +5098,63 @@
           <t>리츠</t>
         </is>
       </c>
-      <c r="D12" s="6" t="n">
+      <c r="D12" s="8" t="inlineStr">
+        <is>
+          <t>ETF는 1.2% 내렸고 최근 1개월 수익률도 -2.6%로 약세가 이어졌다.</t>
+        </is>
+      </c>
+      <c r="E12" s="9" t="n">
         <v>-1.2</v>
       </c>
-      <c r="E12" s="6" t="n">
+      <c r="F12" s="9" t="n">
         <v>-2.2</v>
       </c>
-      <c r="F12" s="6" t="n">
+      <c r="G12" s="9" t="n">
         <v>-2.6</v>
       </c>
-      <c r="G12" s="6" t="n">
+      <c r="H12" s="9" t="n">
         <v>1.2</v>
       </c>
-      <c r="H12" s="6" t="n">
+      <c r="I12" s="9" t="n">
         <v>11</v>
       </c>
-      <c r="I12" t="n">
+      <c r="J12" t="n">
         <v>6</v>
       </c>
-      <c r="J12" s="6" t="n">
+      <c r="K12" s="9" t="n">
         <v>2.6</v>
       </c>
-      <c r="K12" t="n">
+      <c r="L12" t="n">
         <v>10</v>
       </c>
-      <c r="L12" s="6" t="n">
+      <c r="M12" s="9" t="n">
         <v>5.1</v>
       </c>
-      <c r="M12" t="n">
+      <c r="N12" t="n">
         <v>9</v>
       </c>
-      <c r="N12" s="6" t="n">
+      <c r="O12" s="9" t="n">
         <v>12.4</v>
       </c>
-      <c r="O12" t="n">
+      <c r="P12" t="n">
         <v>6</v>
       </c>
-      <c r="P12" s="6" t="n">
+      <c r="Q12" s="9" t="n">
         <v>-26.2</v>
       </c>
-      <c r="Q12" t="n">
+      <c r="R12" t="n">
         <v>8</v>
       </c>
-      <c r="R12" s="6" t="n">
+      <c r="S12" s="9" t="n">
         <v>46.1</v>
       </c>
-      <c r="S12" t="n">
+      <c r="T12" t="n">
         <v>2</v>
       </c>
-      <c r="T12" s="6" t="n">
+      <c r="U12" s="9" t="n">
         <v>-2.2</v>
       </c>
-      <c r="U12" t="n">
+      <c r="V12" t="n">
         <v>10</v>
       </c>
     </row>
@@ -5031,58 +5174,59 @@
           <t>식품</t>
         </is>
       </c>
-      <c r="D13" s="6" t="n">
+      <c r="D13" s="8" t="inlineStr"/>
+      <c r="E13" s="9" t="n">
         <v>0.5</v>
       </c>
-      <c r="E13" s="6" t="n">
+      <c r="F13" s="9" t="n">
         <v>0.5</v>
       </c>
-      <c r="F13" s="6" t="n">
+      <c r="G13" s="9" t="n">
         <v>3.4</v>
       </c>
-      <c r="G13" s="6" t="n">
+      <c r="H13" s="9" t="n">
         <v>12.3</v>
       </c>
-      <c r="H13" s="6" t="n">
+      <c r="I13" s="9" t="n">
         <v>22.4</v>
       </c>
-      <c r="I13" t="n">
+      <c r="J13" t="n">
         <v>6</v>
       </c>
-      <c r="J13" s="6" t="n">
+      <c r="K13" s="9" t="n">
         <v>11.8</v>
       </c>
-      <c r="K13" t="n">
+      <c r="L13" t="n">
         <v>15</v>
       </c>
-      <c r="L13" s="6" t="n">
+      <c r="M13" s="9" t="n">
         <v>8.800000000000001</v>
       </c>
-      <c r="M13" t="n">
+      <c r="N13" t="n">
         <v>14</v>
       </c>
-      <c r="N13" s="6" t="n">
+      <c r="O13" s="9" t="n">
         <v>22.3</v>
       </c>
-      <c r="O13" t="n">
+      <c r="P13" t="n">
         <v>13</v>
       </c>
-      <c r="P13" s="6" t="n">
+      <c r="Q13" s="9" t="n">
         <v>6.4</v>
       </c>
-      <c r="Q13" t="n">
+      <c r="R13" t="n">
         <v>10</v>
       </c>
-      <c r="R13" s="6" t="n">
+      <c r="S13" s="9" t="n">
         <v>5.6</v>
       </c>
-      <c r="S13" t="n">
+      <c r="T13" t="n">
         <v>11</v>
       </c>
-      <c r="T13" s="6" t="n">
+      <c r="U13" s="9" t="n">
         <v>-3.4</v>
       </c>
-      <c r="U13" t="n">
+      <c r="V13" t="n">
         <v>9</v>
       </c>
     </row>
@@ -5102,58 +5246,59 @@
           <t>에너지자원</t>
         </is>
       </c>
-      <c r="D14" s="6" t="n">
+      <c r="D14" s="8" t="inlineStr"/>
+      <c r="E14" s="9" t="n">
         <v>2.1</v>
       </c>
-      <c r="E14" s="6" t="n">
+      <c r="F14" s="9" t="n">
         <v>3.7</v>
       </c>
-      <c r="F14" s="6" t="n">
+      <c r="G14" s="9" t="n">
         <v>8.800000000000001</v>
       </c>
-      <c r="G14" s="6" t="n">
+      <c r="H14" s="9" t="n">
         <v>11.4</v>
       </c>
-      <c r="H14" s="6" t="n">
+      <c r="I14" s="9" t="n">
         <v>26.3</v>
       </c>
-      <c r="I14" t="n">
+      <c r="J14" t="n">
         <v>5</v>
       </c>
-      <c r="J14" s="6" t="n">
+      <c r="K14" s="9" t="n">
         <v>41.4</v>
       </c>
-      <c r="K14" t="n">
+      <c r="L14" t="n">
         <v>6</v>
       </c>
-      <c r="L14" s="6" t="n">
+      <c r="M14" s="9" t="n">
         <v>29.9</v>
       </c>
-      <c r="M14" t="n">
+      <c r="N14" t="n">
         <v>3</v>
       </c>
-      <c r="N14" s="6" t="n">
+      <c r="O14" s="9" t="n">
         <v>37.2</v>
       </c>
-      <c r="O14" t="n">
+      <c r="P14" t="n">
         <v>3</v>
       </c>
-      <c r="P14" s="6" t="n">
+      <c r="Q14" s="9" t="n">
         <v>23.6</v>
       </c>
-      <c r="Q14" t="n">
+      <c r="R14" t="n">
         <v>2</v>
       </c>
-      <c r="R14" s="6" t="n">
+      <c r="S14" s="9" t="n">
         <v>39.3</v>
       </c>
-      <c r="S14" t="n">
+      <c r="T14" t="n">
         <v>1</v>
       </c>
-      <c r="T14" s="6" t="n">
+      <c r="U14" s="9" t="n">
         <v>-29</v>
       </c>
-      <c r="U14" t="n">
+      <c r="V14" t="n">
         <v>17</v>
       </c>
     </row>
@@ -5173,58 +5318,59 @@
           <t>건설·자재</t>
         </is>
       </c>
-      <c r="D15" s="6" t="n">
+      <c r="D15" s="8" t="inlineStr"/>
+      <c r="E15" s="9" t="n">
         <v>0.7</v>
       </c>
-      <c r="E15" s="6" t="n">
+      <c r="F15" s="9" t="n">
         <v>0.7</v>
       </c>
-      <c r="F15" s="6" t="n">
+      <c r="G15" s="9" t="n">
         <v>-0.7</v>
       </c>
-      <c r="G15" s="6" t="n">
+      <c r="H15" s="9" t="n">
         <v>-2.1</v>
       </c>
-      <c r="H15" s="6" t="n">
+      <c r="I15" s="9" t="n">
         <v>7.3</v>
       </c>
-      <c r="I15" t="n">
+      <c r="J15" t="n">
         <v>14</v>
       </c>
-      <c r="J15" s="6" t="n">
+      <c r="K15" s="9" t="n">
         <v>42</v>
       </c>
-      <c r="K15" t="n">
+      <c r="L15" t="n">
         <v>3</v>
       </c>
-      <c r="L15" s="6" t="n">
+      <c r="M15" s="9" t="n">
         <v>21.6</v>
       </c>
-      <c r="M15" t="n">
+      <c r="N15" t="n">
         <v>6</v>
       </c>
-      <c r="N15" s="6" t="n">
+      <c r="O15" s="9" t="n">
         <v>32</v>
       </c>
-      <c r="O15" t="n">
+      <c r="P15" t="n">
         <v>9</v>
       </c>
-      <c r="P15" s="6" t="n">
+      <c r="Q15" s="9" t="n">
         <v>-2.4</v>
       </c>
-      <c r="Q15" t="n">
+      <c r="R15" t="n">
         <v>12</v>
       </c>
-      <c r="R15" s="6" t="n">
+      <c r="S15" s="9" t="n">
         <v>12.6</v>
       </c>
-      <c r="S15" t="n">
+      <c r="T15" t="n">
         <v>8</v>
       </c>
-      <c r="T15" s="6" t="n">
+      <c r="U15" s="9" t="n">
         <v>-6.1</v>
       </c>
-      <c r="U15" t="n">
+      <c r="V15" t="n">
         <v>11</v>
       </c>
     </row>
@@ -5244,58 +5390,59 @@
           <t>소재·화학</t>
         </is>
       </c>
-      <c r="D16" s="6" t="n">
+      <c r="D16" s="8" t="inlineStr"/>
+      <c r="E16" s="9" t="n">
         <v>0.3</v>
       </c>
-      <c r="E16" s="6" t="n">
+      <c r="F16" s="9" t="n">
         <v>1.1</v>
       </c>
-      <c r="F16" s="6" t="n">
+      <c r="G16" s="9" t="n">
         <v>3.3</v>
       </c>
-      <c r="G16" s="6" t="n">
+      <c r="H16" s="9" t="n">
         <v>-0.7</v>
       </c>
-      <c r="H16" s="6" t="n">
+      <c r="I16" s="9" t="n">
         <v>22.2</v>
       </c>
-      <c r="I16" t="n">
+      <c r="J16" t="n">
         <v>7</v>
       </c>
-      <c r="J16" s="6" t="n">
+      <c r="K16" s="9" t="n">
         <v>8.6</v>
       </c>
-      <c r="K16" t="n">
+      <c r="L16" t="n">
         <v>17</v>
       </c>
-      <c r="L16" s="6" t="n">
+      <c r="M16" s="9" t="n">
         <v>3.9</v>
       </c>
-      <c r="M16" t="n">
+      <c r="N16" t="n">
         <v>16</v>
       </c>
-      <c r="N16" s="6" t="n">
+      <c r="O16" s="9" t="n">
         <v>23.1</v>
       </c>
-      <c r="O16" t="n">
+      <c r="P16" t="n">
         <v>12</v>
       </c>
-      <c r="P16" s="6" t="n">
+      <c r="Q16" s="9" t="n">
         <v>-9.4</v>
       </c>
-      <c r="Q16" t="n">
+      <c r="R16" t="n">
         <v>14</v>
       </c>
-      <c r="R16" s="6" t="n">
+      <c r="S16" s="9" t="n">
         <v>2.1</v>
       </c>
-      <c r="S16" t="n">
+      <c r="T16" t="n">
         <v>14</v>
       </c>
-      <c r="T16" s="6" t="n">
+      <c r="U16" s="9" t="n">
         <v>8.6</v>
       </c>
-      <c r="U16" t="n">
+      <c r="V16" t="n">
         <v>5</v>
       </c>
     </row>
@@ -5315,58 +5462,59 @@
           <t>의약품</t>
         </is>
       </c>
-      <c r="D17" s="6" t="n">
+      <c r="D17" s="8" t="inlineStr"/>
+      <c r="E17" s="9" t="n">
         <v>1.5</v>
       </c>
-      <c r="E17" s="6" t="n">
+      <c r="F17" s="9" t="n">
         <v>1.5</v>
       </c>
-      <c r="F17" s="6" t="n">
+      <c r="G17" s="9" t="n">
         <v>6.7</v>
       </c>
-      <c r="G17" s="6" t="n">
+      <c r="H17" s="9" t="n">
         <v>10.6</v>
       </c>
-      <c r="H17" s="6" t="n">
+      <c r="I17" s="9" t="n">
         <v>7.9</v>
       </c>
-      <c r="I17" t="n">
+      <c r="J17" t="n">
         <v>13</v>
       </c>
-      <c r="J17" s="6" t="n">
+      <c r="K17" s="9" t="n">
         <v>9.699999999999999</v>
       </c>
-      <c r="K17" t="n">
+      <c r="L17" t="n">
         <v>16</v>
       </c>
-      <c r="L17" s="6" t="n">
+      <c r="M17" s="9" t="n">
         <v>10.8</v>
       </c>
-      <c r="M17" t="n">
+      <c r="N17" t="n">
         <v>13</v>
       </c>
-      <c r="N17" s="6" t="n">
+      <c r="O17" s="9" t="n">
         <v>0.5</v>
       </c>
-      <c r="O17" t="n">
+      <c r="P17" t="n">
         <v>17</v>
       </c>
-      <c r="P17" s="6" t="n">
+      <c r="Q17" s="9" t="n">
         <v>16.4</v>
       </c>
-      <c r="Q17" t="n">
+      <c r="R17" t="n">
         <v>4</v>
       </c>
-      <c r="R17" s="6" t="n">
+      <c r="S17" s="9" t="n">
         <v>-8.4</v>
       </c>
-      <c r="S17" t="n">
+      <c r="T17" t="n">
         <v>17</v>
       </c>
-      <c r="T17" s="6" t="n">
+      <c r="U17" s="9" t="n">
         <v>4.6</v>
       </c>
-      <c r="U17" t="n">
+      <c r="V17" t="n">
         <v>6</v>
       </c>
     </row>
@@ -5386,58 +5534,59 @@
           <t>자동차·운송기기</t>
         </is>
       </c>
-      <c r="D18" s="6" t="n">
+      <c r="D18" s="8" t="inlineStr"/>
+      <c r="E18" s="9" t="n">
         <v>1.6</v>
       </c>
-      <c r="E18" s="6" t="n">
+      <c r="F18" s="9" t="n">
         <v>3</v>
       </c>
-      <c r="F18" s="6" t="n">
+      <c r="G18" s="9" t="n">
         <v>4.6</v>
       </c>
-      <c r="G18" s="6" t="n">
+      <c r="H18" s="9" t="n">
         <v>13</v>
       </c>
-      <c r="H18" s="6" t="n">
+      <c r="I18" s="9" t="n">
         <v>3</v>
       </c>
-      <c r="I18" t="n">
+      <c r="J18" t="n">
         <v>16</v>
       </c>
-      <c r="J18" s="6" t="n">
+      <c r="K18" s="9" t="n">
         <v>13.5</v>
       </c>
-      <c r="K18" t="n">
+      <c r="L18" t="n">
         <v>14</v>
       </c>
-      <c r="L18" s="6" t="n">
+      <c r="M18" s="9" t="n">
         <v>16.4</v>
       </c>
-      <c r="M18" t="n">
+      <c r="N18" t="n">
         <v>11</v>
       </c>
-      <c r="N18" s="6" t="n">
+      <c r="O18" s="9" t="n">
         <v>40.5</v>
       </c>
-      <c r="O18" t="n">
+      <c r="P18" t="n">
         <v>2</v>
       </c>
-      <c r="P18" s="6" t="n">
+      <c r="Q18" s="9" t="n">
         <v>-10.7</v>
       </c>
-      <c r="Q18" t="n">
+      <c r="R18" t="n">
         <v>16</v>
       </c>
-      <c r="R18" s="6" t="n">
+      <c r="S18" s="9" t="n">
         <v>27.8</v>
       </c>
-      <c r="S18" t="n">
+      <c r="T18" t="n">
         <v>3</v>
       </c>
-      <c r="T18" s="6" t="n">
+      <c r="U18" s="9" t="n">
         <v>0.7</v>
       </c>
-      <c r="U18" t="n">
+      <c r="V18" t="n">
         <v>8</v>
       </c>
     </row>
@@ -5457,58 +5606,59 @@
           <t>철강·비철</t>
         </is>
       </c>
-      <c r="D19" s="6" t="n">
+      <c r="D19" s="8" t="inlineStr"/>
+      <c r="E19" s="9" t="n">
         <v>-0.3</v>
       </c>
-      <c r="E19" s="6" t="n">
+      <c r="F19" s="9" t="n">
         <v>0.6</v>
       </c>
-      <c r="F19" s="6" t="n">
+      <c r="G19" s="9" t="n">
         <v>11.2</v>
       </c>
-      <c r="G19" s="6" t="n">
+      <c r="H19" s="9" t="n">
         <v>-4.2</v>
       </c>
-      <c r="H19" s="6" t="n">
+      <c r="I19" s="9" t="n">
         <v>51.2</v>
       </c>
-      <c r="I19" t="n">
+      <c r="J19" t="n">
         <v>1</v>
       </c>
-      <c r="J19" s="6" t="n">
+      <c r="K19" s="9" t="n">
         <v>68.8</v>
       </c>
-      <c r="K19" t="n">
+      <c r="L19" t="n">
         <v>1</v>
       </c>
-      <c r="L19" s="6" t="n">
+      <c r="M19" s="9" t="n">
         <v>20.6</v>
       </c>
-      <c r="M19" t="n">
+      <c r="N19" t="n">
         <v>8</v>
       </c>
-      <c r="N19" s="6" t="n">
+      <c r="O19" s="9" t="n">
         <v>35</v>
       </c>
-      <c r="O19" t="n">
+      <c r="P19" t="n">
         <v>4</v>
       </c>
-      <c r="P19" s="6" t="n">
+      <c r="Q19" s="9" t="n">
         <v>16.1</v>
       </c>
-      <c r="Q19" t="n">
+      <c r="R19" t="n">
         <v>5</v>
       </c>
-      <c r="R19" s="6" t="n">
+      <c r="S19" s="9" t="n">
         <v>20.8</v>
       </c>
-      <c r="S19" t="n">
+      <c r="T19" t="n">
         <v>7</v>
       </c>
-      <c r="T19" s="6" t="n">
+      <c r="U19" s="9" t="n">
         <v>-8.6</v>
       </c>
-      <c r="U19" t="n">
+      <c r="V19" t="n">
         <v>12</v>
       </c>
     </row>
@@ -5528,58 +5678,59 @@
           <t>기계</t>
         </is>
       </c>
-      <c r="D20" s="6" t="n">
+      <c r="D20" s="8" t="inlineStr"/>
+      <c r="E20" s="9" t="n">
         <v>0.1</v>
       </c>
-      <c r="E20" s="6" t="n">
+      <c r="F20" s="9" t="n">
         <v>-2.2</v>
       </c>
-      <c r="F20" s="6" t="n">
+      <c r="G20" s="9" t="n">
         <v>-0.6</v>
       </c>
-      <c r="G20" s="6" t="n">
+      <c r="H20" s="9" t="n">
         <v>1.7</v>
       </c>
-      <c r="H20" s="6" t="n">
+      <c r="I20" s="9" t="n">
         <v>16.1</v>
       </c>
-      <c r="I20" t="n">
+      <c r="J20" t="n">
         <v>10</v>
       </c>
-      <c r="J20" s="6" t="n">
+      <c r="K20" s="9" t="n">
         <v>31.1</v>
       </c>
-      <c r="K20" t="n">
+      <c r="L20" t="n">
         <v>8</v>
       </c>
-      <c r="L20" s="6" t="n">
+      <c r="M20" s="9" t="n">
         <v>22.3</v>
       </c>
-      <c r="M20" t="n">
+      <c r="N20" t="n">
         <v>5</v>
       </c>
-      <c r="N20" s="6" t="n">
+      <c r="O20" s="9" t="n">
         <v>33.9</v>
       </c>
-      <c r="O20" t="n">
+      <c r="P20" t="n">
         <v>6</v>
       </c>
-      <c r="P20" s="6" t="n">
+      <c r="Q20" s="9" t="n">
         <v>-9.9</v>
       </c>
-      <c r="Q20" t="n">
+      <c r="R20" t="n">
         <v>15</v>
       </c>
-      <c r="R20" s="6" t="n">
+      <c r="S20" s="9" t="n">
         <v>7.5</v>
       </c>
-      <c r="S20" t="n">
+      <c r="T20" t="n">
         <v>9</v>
       </c>
-      <c r="T20" s="6" t="n">
+      <c r="U20" s="9" t="n">
         <v>17.7</v>
       </c>
-      <c r="U20" t="n">
+      <c r="V20" t="n">
         <v>3</v>
       </c>
     </row>
@@ -5599,58 +5750,59 @@
           <t>전기·정밀</t>
         </is>
       </c>
-      <c r="D21" s="6" t="n">
+      <c r="D21" s="8" t="inlineStr"/>
+      <c r="E21" s="9" t="n">
         <v>-0.9</v>
       </c>
-      <c r="E21" s="6" t="n">
+      <c r="F21" s="9" t="n">
         <v>0.4</v>
       </c>
-      <c r="F21" s="6" t="n">
+      <c r="G21" s="9" t="n">
         <v>1.3</v>
       </c>
-      <c r="G21" s="6" t="n">
+      <c r="H21" s="9" t="n">
         <v>-2.1</v>
       </c>
-      <c r="H21" s="6" t="n">
+      <c r="I21" s="9" t="n">
         <v>32.8</v>
       </c>
-      <c r="I21" t="n">
+      <c r="J21" t="n">
         <v>3</v>
       </c>
-      <c r="J21" s="6" t="n">
+      <c r="K21" s="9" t="n">
         <v>27.5</v>
       </c>
-      <c r="K21" t="n">
+      <c r="L21" t="n">
         <v>9</v>
       </c>
-      <c r="L21" s="6" t="n">
+      <c r="M21" s="9" t="n">
         <v>17.9</v>
       </c>
-      <c r="M21" t="n">
+      <c r="N21" t="n">
         <v>10</v>
       </c>
-      <c r="N21" s="6" t="n">
+      <c r="O21" s="9" t="n">
         <v>33.7</v>
       </c>
-      <c r="O21" t="n">
+      <c r="P21" t="n">
         <v>7</v>
       </c>
-      <c r="P21" s="6" t="n">
+      <c r="Q21" s="9" t="n">
         <v>-23</v>
       </c>
-      <c r="Q21" t="n">
+      <c r="R21" t="n">
         <v>17</v>
       </c>
-      <c r="R21" s="6" t="n">
+      <c r="S21" s="9" t="n">
         <v>25</v>
       </c>
-      <c r="S21" t="n">
+      <c r="T21" t="n">
         <v>5</v>
       </c>
-      <c r="T21" s="6" t="n">
+      <c r="U21" s="9" t="n">
         <v>26.2</v>
       </c>
-      <c r="U21" t="n">
+      <c r="V21" t="n">
         <v>1</v>
       </c>
     </row>
@@ -5670,58 +5822,59 @@
           <t>정보통신·서비스</t>
         </is>
       </c>
-      <c r="D22" s="6" t="n">
+      <c r="D22" s="8" t="inlineStr"/>
+      <c r="E22" s="9" t="n">
         <v>-0.3</v>
       </c>
-      <c r="E22" s="6" t="n">
+      <c r="F22" s="9" t="n">
         <v>2.6</v>
       </c>
-      <c r="F22" s="6" t="n">
+      <c r="G22" s="9" t="n">
         <v>10.9</v>
       </c>
-      <c r="G22" s="6" t="n">
+      <c r="H22" s="9" t="n">
         <v>7.9</v>
       </c>
-      <c r="H22" s="6" t="n">
+      <c r="I22" s="9" t="n">
         <v>17.5</v>
       </c>
-      <c r="I22" t="n">
+      <c r="J22" t="n">
         <v>9</v>
       </c>
-      <c r="J22" s="6" t="n">
+      <c r="K22" s="9" t="n">
         <v>13.9</v>
       </c>
-      <c r="K22" t="n">
+      <c r="L22" t="n">
         <v>13</v>
       </c>
-      <c r="L22" s="6" t="n">
+      <c r="M22" s="9" t="n">
         <v>21</v>
       </c>
-      <c r="M22" t="n">
+      <c r="N22" t="n">
         <v>7</v>
       </c>
-      <c r="N22" s="6" t="n">
+      <c r="O22" s="9" t="n">
         <v>17.9</v>
       </c>
-      <c r="O22" t="n">
+      <c r="P22" t="n">
         <v>15</v>
       </c>
-      <c r="P22" s="6" t="n">
+      <c r="Q22" s="9" t="n">
         <v>-5.9</v>
       </c>
-      <c r="Q22" t="n">
+      <c r="R22" t="n">
         <v>13</v>
       </c>
-      <c r="R22" s="6" t="n">
+      <c r="S22" s="9" t="n">
         <v>3.5</v>
       </c>
-      <c r="S22" t="n">
+      <c r="T22" t="n">
         <v>13</v>
       </c>
-      <c r="T22" s="6" t="n">
+      <c r="U22" s="9" t="n">
         <v>21.9</v>
       </c>
-      <c r="U22" t="n">
+      <c r="V22" t="n">
         <v>2</v>
       </c>
     </row>
@@ -5741,58 +5894,59 @@
           <t>전력·가스</t>
         </is>
       </c>
-      <c r="D23" s="6" t="n">
+      <c r="D23" s="8" t="inlineStr"/>
+      <c r="E23" s="9" t="n">
         <v>3.3</v>
       </c>
-      <c r="E23" s="6" t="n">
+      <c r="F23" s="9" t="n">
         <v>6.4</v>
       </c>
-      <c r="F23" s="6" t="n">
+      <c r="G23" s="9" t="n">
         <v>9.9</v>
       </c>
-      <c r="G23" s="6" t="n">
+      <c r="H23" s="9" t="n">
         <v>13.5</v>
       </c>
-      <c r="H23" s="6" t="n">
+      <c r="I23" s="9" t="n">
         <v>13.4</v>
       </c>
-      <c r="I23" t="n">
+      <c r="J23" t="n">
         <v>11</v>
       </c>
-      <c r="J23" s="6" t="n">
+      <c r="K23" s="9" t="n">
         <v>37.4</v>
       </c>
-      <c r="K23" t="n">
+      <c r="L23" t="n">
         <v>7</v>
       </c>
-      <c r="L23" s="6" t="n">
+      <c r="M23" s="9" t="n">
         <v>6.3</v>
       </c>
-      <c r="M23" t="n">
+      <c r="N23" t="n">
         <v>15</v>
       </c>
-      <c r="N23" s="6" t="n">
+      <c r="O23" s="9" t="n">
         <v>35</v>
       </c>
-      <c r="O23" t="n">
+      <c r="P23" t="n">
         <v>4</v>
       </c>
-      <c r="P23" s="6" t="n">
+      <c r="Q23" s="9" t="n">
         <v>13.2</v>
       </c>
-      <c r="Q23" t="n">
+      <c r="R23" t="n">
         <v>7</v>
       </c>
-      <c r="R23" s="6" t="n">
+      <c r="S23" s="9" t="n">
         <v>-8.300000000000001</v>
       </c>
-      <c r="S23" t="n">
+      <c r="T23" t="n">
         <v>16</v>
       </c>
-      <c r="T23" s="6" t="n">
+      <c r="U23" s="9" t="n">
         <v>-10.7</v>
       </c>
-      <c r="U23" t="n">
+      <c r="V23" t="n">
         <v>13</v>
       </c>
     </row>
@@ -5812,58 +5966,59 @@
           <t>운수·물류</t>
         </is>
       </c>
-      <c r="D24" s="6" t="n">
+      <c r="D24" s="8" t="inlineStr"/>
+      <c r="E24" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="E24" s="6" t="n">
+      <c r="F24" s="9" t="n">
         <v>-0.5</v>
       </c>
-      <c r="F24" s="6" t="n">
+      <c r="G24" s="9" t="n">
         <v>3</v>
       </c>
-      <c r="G24" s="6" t="n">
+      <c r="H24" s="9" t="n">
         <v>14</v>
       </c>
-      <c r="H24" s="6" t="n">
+      <c r="I24" s="9" t="n">
         <v>8.9</v>
       </c>
-      <c r="I24" t="n">
+      <c r="J24" t="n">
         <v>12</v>
       </c>
-      <c r="J24" s="6" t="n">
+      <c r="K24" s="9" t="n">
         <v>19.9</v>
       </c>
-      <c r="K24" t="n">
+      <c r="L24" t="n">
         <v>11</v>
       </c>
-      <c r="L24" s="6" t="n">
+      <c r="M24" s="9" t="n">
         <v>-0</v>
       </c>
-      <c r="M24" t="n">
+      <c r="N24" t="n">
         <v>17</v>
       </c>
-      <c r="N24" s="6" t="n">
+      <c r="O24" s="9" t="n">
         <v>19</v>
       </c>
-      <c r="O24" t="n">
+      <c r="P24" t="n">
         <v>14</v>
       </c>
-      <c r="P24" s="6" t="n">
+      <c r="Q24" s="9" t="n">
         <v>13.1</v>
       </c>
-      <c r="Q24" t="n">
+      <c r="R24" t="n">
         <v>8</v>
       </c>
-      <c r="R24" s="6" t="n">
+      <c r="S24" s="9" t="n">
         <v>4.7</v>
       </c>
-      <c r="S24" t="n">
+      <c r="T24" t="n">
         <v>12</v>
       </c>
-      <c r="T24" s="6" t="n">
+      <c r="U24" s="9" t="n">
         <v>-17.1</v>
       </c>
-      <c r="U24" t="n">
+      <c r="V24" t="n">
         <v>16</v>
       </c>
     </row>
@@ -5883,58 +6038,59 @@
           <t>상사·도매</t>
         </is>
       </c>
-      <c r="D25" s="6" t="n">
+      <c r="D25" s="8" t="inlineStr"/>
+      <c r="E25" s="9" t="n">
         <v>2.1</v>
       </c>
-      <c r="E25" s="6" t="n">
+      <c r="F25" s="9" t="n">
         <v>2.5</v>
       </c>
-      <c r="F25" s="6" t="n">
+      <c r="G25" s="9" t="n">
         <v>5</v>
       </c>
-      <c r="G25" s="6" t="n">
+      <c r="H25" s="9" t="n">
         <v>7.3</v>
       </c>
-      <c r="H25" s="6" t="n">
+      <c r="I25" s="9" t="n">
         <v>22</v>
       </c>
-      <c r="I25" t="n">
+      <c r="J25" t="n">
         <v>8</v>
       </c>
-      <c r="J25" s="6" t="n">
+      <c r="K25" s="9" t="n">
         <v>41.5</v>
       </c>
-      <c r="K25" t="n">
+      <c r="L25" t="n">
         <v>5</v>
       </c>
-      <c r="L25" s="6" t="n">
+      <c r="M25" s="9" t="n">
         <v>20.1</v>
       </c>
-      <c r="M25" t="n">
+      <c r="N25" t="n">
         <v>9</v>
       </c>
-      <c r="N25" s="6" t="n">
+      <c r="O25" s="9" t="n">
         <v>42</v>
       </c>
-      <c r="O25" t="n">
+      <c r="P25" t="n">
         <v>1</v>
       </c>
-      <c r="P25" s="6" t="n">
+      <c r="Q25" s="9" t="n">
         <v>21.3</v>
       </c>
-      <c r="Q25" t="n">
+      <c r="R25" t="n">
         <v>3</v>
       </c>
-      <c r="R25" s="6" t="n">
+      <c r="S25" s="9" t="n">
         <v>29.2</v>
       </c>
-      <c r="S25" t="n">
+      <c r="T25" t="n">
         <v>2</v>
       </c>
-      <c r="T25" s="6" t="n">
+      <c r="U25" s="9" t="n">
         <v>1.9</v>
       </c>
-      <c r="U25" t="n">
+      <c r="V25" t="n">
         <v>7</v>
       </c>
     </row>
@@ -5954,58 +6110,59 @@
           <t>소매</t>
         </is>
       </c>
-      <c r="D26" s="6" t="n">
+      <c r="D26" s="8" t="inlineStr"/>
+      <c r="E26" s="9" t="n">
         <v>0.1</v>
       </c>
-      <c r="E26" s="6" t="n">
+      <c r="F26" s="9" t="n">
         <v>-0.3</v>
       </c>
-      <c r="F26" s="6" t="n">
+      <c r="G26" s="9" t="n">
         <v>-0.8</v>
       </c>
-      <c r="G26" s="6" t="n">
+      <c r="H26" s="9" t="n">
         <v>5.8</v>
       </c>
-      <c r="H26" s="6" t="n">
+      <c r="I26" s="9" t="n">
         <v>3.6</v>
       </c>
-      <c r="I26" t="n">
+      <c r="J26" t="n">
         <v>15</v>
       </c>
-      <c r="J26" s="6" t="n">
+      <c r="K26" s="9" t="n">
         <v>16.8</v>
       </c>
-      <c r="K26" t="n">
+      <c r="L26" t="n">
         <v>12</v>
       </c>
-      <c r="L26" s="6" t="n">
+      <c r="M26" s="9" t="n">
         <v>23.4</v>
       </c>
-      <c r="M26" t="n">
+      <c r="N26" t="n">
         <v>4</v>
       </c>
-      <c r="N26" s="6" t="n">
+      <c r="O26" s="9" t="n">
         <v>16.4</v>
       </c>
-      <c r="O26" t="n">
+      <c r="P26" t="n">
         <v>16</v>
       </c>
-      <c r="P26" s="6" t="n">
+      <c r="Q26" s="9" t="n">
         <v>10.2</v>
       </c>
-      <c r="Q26" t="n">
+      <c r="R26" t="n">
         <v>9</v>
       </c>
-      <c r="R26" s="6" t="n">
+      <c r="S26" s="9" t="n">
         <v>-4.4</v>
       </c>
-      <c r="S26" t="n">
+      <c r="T26" t="n">
         <v>15</v>
       </c>
-      <c r="T26" s="6" t="n">
+      <c r="U26" s="9" t="n">
         <v>8.699999999999999</v>
       </c>
-      <c r="U26" t="n">
+      <c r="V26" t="n">
         <v>4</v>
       </c>
     </row>
@@ -6025,58 +6182,59 @@
           <t>은행</t>
         </is>
       </c>
-      <c r="D27" s="6" t="n">
+      <c r="D27" s="8" t="inlineStr"/>
+      <c r="E27" s="9" t="n">
         <v>-0.1</v>
       </c>
-      <c r="E27" s="6" t="n">
+      <c r="F27" s="9" t="n">
         <v>4.5</v>
       </c>
-      <c r="F27" s="6" t="n">
+      <c r="G27" s="9" t="n">
         <v>5.4</v>
       </c>
-      <c r="G27" s="6" t="n">
+      <c r="H27" s="9" t="n">
         <v>20.5</v>
       </c>
-      <c r="H27" s="6" t="n">
+      <c r="I27" s="9" t="n">
         <v>51.1</v>
       </c>
-      <c r="I27" t="n">
+      <c r="J27" t="n">
         <v>2</v>
       </c>
-      <c r="J27" s="6" t="n">
+      <c r="K27" s="9" t="n">
         <v>44.8</v>
       </c>
-      <c r="K27" t="n">
+      <c r="L27" t="n">
         <v>2</v>
       </c>
-      <c r="L27" s="6" t="n">
+      <c r="M27" s="9" t="n">
         <v>50.4</v>
       </c>
-      <c r="M27" t="n">
+      <c r="N27" t="n">
         <v>1</v>
       </c>
-      <c r="N27" s="6" t="n">
+      <c r="O27" s="9" t="n">
         <v>33.2</v>
       </c>
-      <c r="O27" t="n">
+      <c r="P27" t="n">
         <v>8</v>
       </c>
-      <c r="P27" s="6" t="n">
+      <c r="Q27" s="9" t="n">
         <v>38.3</v>
       </c>
-      <c r="Q27" t="n">
+      <c r="R27" t="n">
         <v>1</v>
       </c>
-      <c r="R27" s="6" t="n">
+      <c r="S27" s="9" t="n">
         <v>26.7</v>
       </c>
-      <c r="S27" t="n">
+      <c r="T27" t="n">
         <v>4</v>
       </c>
-      <c r="T27" s="6" t="n">
+      <c r="U27" s="9" t="n">
         <v>-16.3</v>
       </c>
-      <c r="U27" t="n">
+      <c r="V27" t="n">
         <v>15</v>
       </c>
     </row>
@@ -6096,58 +6254,59 @@
           <t>금융(은행외)</t>
         </is>
       </c>
-      <c r="D28" s="6" t="n">
+      <c r="D28" s="8" t="inlineStr"/>
+      <c r="E28" s="9" t="n">
         <v>0.5</v>
       </c>
-      <c r="E28" s="6" t="n">
+      <c r="F28" s="9" t="n">
         <v>2.8</v>
       </c>
-      <c r="F28" s="6" t="n">
+      <c r="G28" s="9" t="n">
         <v>-0.1</v>
       </c>
-      <c r="G28" s="6" t="n">
+      <c r="H28" s="9" t="n">
         <v>14.3</v>
       </c>
-      <c r="H28" s="6" t="n">
+      <c r="I28" s="9" t="n">
         <v>31.3</v>
       </c>
-      <c r="I28" t="n">
+      <c r="J28" t="n">
         <v>4</v>
       </c>
-      <c r="J28" s="6" t="n">
+      <c r="K28" s="9" t="n">
         <v>21.4</v>
       </c>
-      <c r="K28" t="n">
+      <c r="L28" t="n">
         <v>10</v>
       </c>
-      <c r="L28" s="6" t="n">
+      <c r="M28" s="9" t="n">
         <v>49</v>
       </c>
-      <c r="M28" t="n">
+      <c r="N28" t="n">
         <v>2</v>
       </c>
-      <c r="N28" s="6" t="n">
+      <c r="O28" s="9" t="n">
         <v>27.2</v>
       </c>
-      <c r="O28" t="n">
+      <c r="P28" t="n">
         <v>10</v>
       </c>
-      <c r="P28" s="6" t="n">
+      <c r="Q28" s="9" t="n">
         <v>13.7</v>
       </c>
-      <c r="Q28" t="n">
+      <c r="R28" t="n">
         <v>6</v>
       </c>
-      <c r="R28" s="6" t="n">
+      <c r="S28" s="9" t="n">
         <v>22.6</v>
       </c>
-      <c r="S28" t="n">
+      <c r="T28" t="n">
         <v>6</v>
       </c>
-      <c r="T28" s="6" t="n">
+      <c r="U28" s="9" t="n">
         <v>-3.6</v>
       </c>
-      <c r="U28" t="n">
+      <c r="V28" t="n">
         <v>10</v>
       </c>
     </row>
@@ -6167,58 +6326,59 @@
           <t>부동산</t>
         </is>
       </c>
-      <c r="D29" s="6" t="n">
+      <c r="D29" s="8" t="inlineStr"/>
+      <c r="E29" s="9" t="n">
         <v>0.8</v>
       </c>
-      <c r="E29" s="6" t="n">
+      <c r="F29" s="9" t="n">
         <v>1.2</v>
       </c>
-      <c r="F29" s="6" t="n">
+      <c r="G29" s="9" t="n">
         <v>-0.9</v>
       </c>
-      <c r="G29" s="6" t="n">
+      <c r="H29" s="9" t="n">
         <v>2</v>
       </c>
-      <c r="H29" s="6" t="n">
+      <c r="I29" s="9" t="n">
         <v>-3.1</v>
       </c>
-      <c r="I29" t="n">
+      <c r="J29" t="n">
         <v>17</v>
       </c>
-      <c r="J29" s="6" t="n">
+      <c r="K29" s="9" t="n">
         <v>41.6</v>
       </c>
-      <c r="K29" t="n">
+      <c r="L29" t="n">
         <v>4</v>
       </c>
-      <c r="L29" s="6" t="n">
+      <c r="M29" s="9" t="n">
         <v>13.9</v>
       </c>
-      <c r="M29" t="n">
+      <c r="N29" t="n">
         <v>12</v>
       </c>
-      <c r="N29" s="6" t="n">
+      <c r="O29" s="9" t="n">
         <v>23.6</v>
       </c>
-      <c r="O29" t="n">
+      <c r="P29" t="n">
         <v>11</v>
       </c>
-      <c r="P29" s="6" t="n">
+      <c r="Q29" s="9" t="n">
         <v>4.4</v>
       </c>
-      <c r="Q29" t="n">
+      <c r="R29" t="n">
         <v>11</v>
       </c>
-      <c r="R29" s="6" t="n">
+      <c r="S29" s="9" t="n">
         <v>6.8</v>
       </c>
-      <c r="S29" t="n">
+      <c r="T29" t="n">
         <v>10</v>
       </c>
-      <c r="T29" s="6" t="n">
+      <c r="U29" s="9" t="n">
         <v>-13.3</v>
       </c>
-      <c r="U29" t="n">
+      <c r="V29" t="n">
         <v>14</v>
       </c>
     </row>
@@ -6238,58 +6398,59 @@
           <t>항셍지수</t>
         </is>
       </c>
-      <c r="D30" s="6" t="n">
+      <c r="D30" s="8" t="inlineStr"/>
+      <c r="E30" s="9" t="n">
         <v>-0.2</v>
       </c>
-      <c r="E30" s="6" t="n">
+      <c r="F30" s="9" t="n">
         <v>0.4</v>
       </c>
-      <c r="F30" s="6" t="n">
+      <c r="G30" s="9" t="n">
         <v>-1.2</v>
       </c>
-      <c r="G30" s="6" t="n">
+      <c r="H30" s="9" t="n">
         <v>1.6</v>
       </c>
-      <c r="H30" s="6" t="n">
+      <c r="I30" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="I30" t="n">
+      <c r="J30" t="n">
         <v>1</v>
       </c>
-      <c r="J30" s="6" t="n">
+      <c r="K30" s="9" t="n">
         <v>27.4</v>
       </c>
-      <c r="K30" t="n">
+      <c r="L30" t="n">
         <v>1</v>
       </c>
-      <c r="L30" s="6" t="n">
+      <c r="M30" s="9" t="n">
         <v>17.9</v>
       </c>
-      <c r="M30" t="n">
+      <c r="N30" t="n">
         <v>3</v>
       </c>
-      <c r="N30" s="6" t="n">
+      <c r="O30" s="9" t="n">
         <v>-13.7</v>
       </c>
-      <c r="O30" t="n">
+      <c r="P30" t="n">
         <v>3</v>
       </c>
-      <c r="P30" s="6" t="n">
+      <c r="Q30" s="9" t="n">
         <v>-15.3</v>
       </c>
-      <c r="Q30" t="n">
+      <c r="R30" t="n">
         <v>1</v>
       </c>
-      <c r="R30" s="6" t="n">
+      <c r="S30" s="9" t="n">
         <v>-14.2</v>
       </c>
-      <c r="S30" t="n">
+      <c r="T30" t="n">
         <v>1</v>
       </c>
-      <c r="T30" s="6" t="n">
+      <c r="U30" s="9" t="n">
         <v>-3.7</v>
       </c>
-      <c r="U30" t="n">
+      <c r="V30" t="n">
         <v>2</v>
       </c>
     </row>
@@ -6309,58 +6470,59 @@
           <t>H주(중국기업)</t>
         </is>
       </c>
-      <c r="D31" s="6" t="n">
+      <c r="D31" s="8" t="inlineStr"/>
+      <c r="E31" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="E31" s="6" t="n">
+      <c r="F31" s="9" t="n">
         <v>0.7</v>
       </c>
-      <c r="F31" s="6" t="n">
+      <c r="G31" s="9" t="n">
         <v>-1.5</v>
       </c>
-      <c r="G31" s="6" t="n">
+      <c r="H31" s="9" t="n">
         <v>-2.2</v>
       </c>
-      <c r="H31" s="6" t="n">
+      <c r="I31" s="9" t="n">
         <v>-3.4</v>
       </c>
-      <c r="I31" t="n">
+      <c r="J31" t="n">
         <v>2</v>
       </c>
-      <c r="J31" s="6" t="n">
+      <c r="K31" s="9" t="n">
         <v>26.2</v>
       </c>
-      <c r="K31" t="n">
+      <c r="L31" t="n">
         <v>2</v>
       </c>
-      <c r="L31" s="6" t="n">
+      <c r="M31" s="9" t="n">
         <v>32.1</v>
       </c>
-      <c r="M31" t="n">
+      <c r="N31" t="n">
         <v>1</v>
       </c>
-      <c r="N31" s="6" t="n">
+      <c r="O31" s="9" t="n">
         <v>-12.8</v>
       </c>
-      <c r="O31" t="n">
+      <c r="P31" t="n">
         <v>2</v>
       </c>
-      <c r="P31" s="6" t="n">
+      <c r="Q31" s="9" t="n">
         <v>-17.8</v>
       </c>
-      <c r="Q31" t="n">
+      <c r="R31" t="n">
         <v>2</v>
       </c>
-      <c r="R31" s="6" t="n">
+      <c r="S31" s="9" t="n">
         <v>-23.6</v>
       </c>
-      <c r="S31" t="n">
+      <c r="T31" t="n">
         <v>2</v>
       </c>
-      <c r="T31" s="6" t="n">
+      <c r="U31" s="9" t="n">
         <v>-2</v>
       </c>
-      <c r="U31" t="n">
+      <c r="V31" t="n">
         <v>1</v>
       </c>
     </row>
@@ -6380,56 +6542,57 @@
           <t>항셍테크</t>
         </is>
       </c>
-      <c r="D32" s="6" t="n">
+      <c r="D32" s="8" t="inlineStr"/>
+      <c r="E32" s="9" t="n">
         <v>-0.5</v>
       </c>
-      <c r="E32" s="6" t="n">
+      <c r="F32" s="9" t="n">
         <v>0.3</v>
       </c>
-      <c r="F32" s="6" t="n">
+      <c r="G32" s="9" t="n">
         <v>-5.6</v>
       </c>
-      <c r="G32" s="6" t="n">
+      <c r="H32" s="9" t="n">
         <v>-11.5</v>
       </c>
-      <c r="H32" s="6" t="n">
+      <c r="I32" s="9" t="n">
         <v>-16.3</v>
       </c>
-      <c r="I32" t="n">
+      <c r="J32" t="n">
         <v>3</v>
       </c>
-      <c r="J32" s="6" t="n">
+      <c r="K32" s="9" t="n">
         <v>22.7</v>
       </c>
-      <c r="K32" t="n">
+      <c r="L32" t="n">
         <v>3</v>
       </c>
-      <c r="L32" s="6" t="n">
+      <c r="M32" s="9" t="n">
         <v>18.9</v>
       </c>
-      <c r="M32" t="n">
+      <c r="N32" t="n">
         <v>2</v>
       </c>
-      <c r="N32" s="6" t="n">
+      <c r="O32" s="9" t="n">
         <v>-9.300000000000001</v>
       </c>
-      <c r="O32" t="n">
+      <c r="P32" t="n">
         <v>1</v>
       </c>
-      <c r="P32" s="6" t="n">
+      <c r="Q32" s="9" t="n">
         <v>-27.4</v>
       </c>
-      <c r="Q32" t="n">
+      <c r="R32" t="n">
         <v>3</v>
       </c>
-      <c r="R32" s="6" t="n">
+      <c r="S32" s="9" t="n">
         <v>-32.9</v>
       </c>
-      <c r="S32" t="n">
+      <c r="T32" t="n">
         <v>3</v>
       </c>
-      <c r="T32" s="6" t="inlineStr"/>
-      <c r="U32" t="inlineStr"/>
+      <c r="U32" s="9" t="inlineStr"/>
+      <c r="V32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -6447,58 +6610,63 @@
           <t>반도체</t>
         </is>
       </c>
-      <c r="D33" s="6" t="n">
+      <c r="D33" s="8" t="inlineStr">
+        <is>
+          <t>반도체 ETF는 1.8% 올랐고 전자기술 순강도도 1로 신고가가 우세했다.</t>
+        </is>
+      </c>
+      <c r="E33" s="9" t="n">
         <v>1.8</v>
       </c>
-      <c r="E33" s="6" t="n">
+      <c r="F33" s="9" t="n">
         <v>4.8</v>
       </c>
-      <c r="F33" s="6" t="n">
+      <c r="G33" s="9" t="n">
         <v>6.7</v>
       </c>
-      <c r="G33" s="6" t="n">
+      <c r="H33" s="9" t="n">
         <v>1.7</v>
       </c>
-      <c r="H33" s="6" t="n">
+      <c r="I33" s="9" t="n">
         <v>44.5</v>
       </c>
-      <c r="I33" t="n">
+      <c r="J33" t="n">
         <v>1</v>
       </c>
-      <c r="J33" s="6" t="n">
+      <c r="K33" s="9" t="n">
         <v>45</v>
       </c>
-      <c r="K33" t="n">
+      <c r="L33" t="n">
         <v>5</v>
       </c>
-      <c r="L33" s="6" t="n">
+      <c r="M33" s="9" t="n">
         <v>25.6</v>
       </c>
-      <c r="M33" t="n">
+      <c r="N33" t="n">
         <v>3</v>
       </c>
-      <c r="N33" s="6" t="n">
+      <c r="O33" s="9" t="n">
         <v>-2.4</v>
       </c>
-      <c r="O33" t="n">
+      <c r="P33" t="n">
         <v>4</v>
       </c>
-      <c r="P33" s="6" t="n">
+      <c r="Q33" s="9" t="n">
         <v>-36.6</v>
       </c>
-      <c r="Q33" t="n">
+      <c r="R33" t="n">
         <v>12</v>
       </c>
-      <c r="R33" s="6" t="n">
+      <c r="S33" s="9" t="n">
         <v>23.8</v>
       </c>
-      <c r="S33" t="n">
+      <c r="T33" t="n">
         <v>4</v>
       </c>
-      <c r="T33" s="6" t="n">
+      <c r="U33" s="9" t="n">
         <v>46.2</v>
       </c>
-      <c r="U33" t="n">
+      <c r="V33" t="n">
         <v>5</v>
       </c>
     </row>
@@ -6518,58 +6686,63 @@
           <t>테크(科技)</t>
         </is>
       </c>
-      <c r="D34" s="6" t="n">
+      <c r="D34" s="8" t="inlineStr">
+        <is>
+          <t>테크 ETF는 1.1% 올랐고 1개월 수익률은 6.1%로 단기 반등이 이어졌다.</t>
+        </is>
+      </c>
+      <c r="E34" s="9" t="n">
         <v>1.1</v>
       </c>
-      <c r="E34" s="6" t="n">
+      <c r="F34" s="9" t="n">
         <v>4.7</v>
       </c>
-      <c r="F34" s="6" t="n">
+      <c r="G34" s="9" t="n">
         <v>6.1</v>
       </c>
-      <c r="G34" s="6" t="n">
+      <c r="H34" s="9" t="n">
         <v>-6.6</v>
       </c>
-      <c r="H34" s="6" t="n">
+      <c r="I34" s="9" t="n">
         <v>29.8</v>
       </c>
-      <c r="I34" t="n">
+      <c r="J34" t="n">
         <v>3</v>
       </c>
-      <c r="J34" s="6" t="n">
+      <c r="K34" s="9" t="n">
         <v>52.1</v>
       </c>
-      <c r="K34" t="n">
+      <c r="L34" t="n">
         <v>4</v>
       </c>
-      <c r="L34" s="6" t="n">
+      <c r="M34" s="9" t="n">
         <v>12</v>
       </c>
-      <c r="M34" t="n">
+      <c r="N34" t="n">
         <v>5</v>
       </c>
-      <c r="N34" s="6" t="n">
+      <c r="O34" s="9" t="n">
         <v>0.5</v>
       </c>
-      <c r="O34" t="n">
+      <c r="P34" t="n">
         <v>3</v>
       </c>
-      <c r="P34" s="6" t="n">
+      <c r="Q34" s="9" t="n">
         <v>-34</v>
       </c>
-      <c r="Q34" t="n">
+      <c r="R34" t="n">
         <v>11</v>
       </c>
-      <c r="R34" s="6" t="n">
+      <c r="S34" s="9" t="n">
         <v>-2.8</v>
       </c>
-      <c r="S34" t="n">
+      <c r="T34" t="n">
         <v>8</v>
       </c>
-      <c r="T34" s="6" t="n">
+      <c r="U34" s="9" t="n">
         <v>44</v>
       </c>
-      <c r="U34" t="n">
+      <c r="V34" t="n">
         <v>6</v>
       </c>
     </row>
@@ -6589,58 +6762,63 @@
           <t>5G통신</t>
         </is>
       </c>
-      <c r="D35" s="6" t="n">
+      <c r="D35" s="8" t="inlineStr">
+        <is>
+          <t>5G ETF는 1.4% 올랐고 1개월 14.1% 상승으로 단기 모멘텀이 강했다.</t>
+        </is>
+      </c>
+      <c r="E35" s="9" t="n">
         <v>1.4</v>
       </c>
-      <c r="E35" s="6" t="n">
+      <c r="F35" s="9" t="n">
         <v>4.7</v>
       </c>
-      <c r="F35" s="6" t="n">
+      <c r="G35" s="9" t="n">
         <v>14.1</v>
       </c>
-      <c r="G35" s="6" t="n">
+      <c r="H35" s="9" t="n">
         <v>-14.1</v>
       </c>
-      <c r="H35" s="6" t="n">
+      <c r="I35" s="9" t="n">
         <v>38.3</v>
       </c>
-      <c r="I35" t="n">
+      <c r="J35" t="n">
         <v>2</v>
       </c>
-      <c r="J35" s="6" t="n">
+      <c r="K35" s="9" t="n">
         <v>99.7</v>
       </c>
-      <c r="K35" t="n">
+      <c r="L35" t="n">
         <v>2</v>
       </c>
-      <c r="L35" s="6" t="n">
+      <c r="M35" s="9" t="n">
         <v>24.2</v>
       </c>
-      <c r="M35" t="n">
+      <c r="N35" t="n">
         <v>4</v>
       </c>
-      <c r="N35" s="6" t="n">
+      <c r="O35" s="9" t="n">
         <v>16.3</v>
       </c>
-      <c r="O35" t="n">
+      <c r="P35" t="n">
         <v>1</v>
       </c>
-      <c r="P35" s="6" t="n">
+      <c r="Q35" s="9" t="n">
         <v>-37.8</v>
       </c>
-      <c r="Q35" t="n">
+      <c r="R35" t="n">
         <v>13</v>
       </c>
-      <c r="R35" s="6" t="n">
+      <c r="S35" s="9" t="n">
         <v>6.8</v>
       </c>
-      <c r="S35" t="n">
+      <c r="T35" t="n">
         <v>6</v>
       </c>
-      <c r="T35" s="6" t="n">
+      <c r="U35" s="9" t="n">
         <v>20.7</v>
       </c>
-      <c r="U35" t="n">
+      <c r="V35" t="n">
         <v>8</v>
       </c>
     </row>
@@ -6660,56 +6838,61 @@
           <t>신에너지차</t>
         </is>
       </c>
-      <c r="D36" s="6" t="n">
+      <c r="D36" s="8" t="inlineStr">
+        <is>
+          <t>신에너지차 ETF는 1.1% 내렸고 세레스가 새 신저가에 들어갔다.</t>
+        </is>
+      </c>
+      <c r="E36" s="9" t="n">
         <v>-1.1</v>
       </c>
-      <c r="E36" s="6" t="n">
+      <c r="F36" s="9" t="n">
         <v>-1.1</v>
       </c>
-      <c r="F36" s="6" t="n">
+      <c r="G36" s="9" t="n">
         <v>-0.2</v>
       </c>
-      <c r="G36" s="6" t="n">
+      <c r="H36" s="9" t="n">
         <v>-16.9</v>
       </c>
-      <c r="H36" s="6" t="n">
+      <c r="I36" s="9" t="n">
         <v>-13.6</v>
       </c>
-      <c r="I36" t="n">
+      <c r="J36" t="n">
         <v>9</v>
       </c>
-      <c r="J36" s="6" t="n">
+      <c r="K36" s="9" t="n">
         <v>56.6</v>
       </c>
-      <c r="K36" t="n">
+      <c r="L36" t="n">
         <v>3</v>
       </c>
-      <c r="L36" s="6" t="n">
+      <c r="M36" s="9" t="n">
         <v>0.3</v>
       </c>
-      <c r="M36" t="n">
+      <c r="N36" t="n">
         <v>8</v>
       </c>
-      <c r="N36" s="6" t="n">
+      <c r="O36" s="9" t="n">
         <v>-29</v>
       </c>
-      <c r="O36" t="n">
+      <c r="P36" t="n">
         <v>12</v>
       </c>
-      <c r="P36" s="6" t="n">
+      <c r="Q36" s="9" t="n">
         <v>-28.9</v>
       </c>
-      <c r="Q36" t="n">
+      <c r="R36" t="n">
         <v>10</v>
       </c>
-      <c r="R36" s="6" t="n">
+      <c r="S36" s="9" t="n">
         <v>41.9</v>
       </c>
-      <c r="S36" t="n">
+      <c r="T36" t="n">
         <v>2</v>
       </c>
-      <c r="T36" s="6" t="inlineStr"/>
-      <c r="U36" t="inlineStr"/>
+      <c r="U36" s="9" t="inlineStr"/>
+      <c r="V36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
@@ -6727,58 +6910,63 @@
           <t>방산(军工)</t>
         </is>
       </c>
-      <c r="D37" s="6" t="n">
+      <c r="D37" s="8" t="inlineStr">
+        <is>
+          <t>방산 ETF는 1.7% 올랐고 우주산업 기대에 레이트론 급등이 보탬이 됐다.</t>
+        </is>
+      </c>
+      <c r="E37" s="9" t="n">
         <v>1.7</v>
       </c>
-      <c r="E37" s="6" t="n">
+      <c r="F37" s="9" t="n">
         <v>4.8</v>
       </c>
-      <c r="F37" s="6" t="n">
+      <c r="G37" s="9" t="n">
         <v>4.5</v>
       </c>
-      <c r="G37" s="6" t="n">
+      <c r="H37" s="9" t="n">
         <v>-9.9</v>
       </c>
-      <c r="H37" s="6" t="n">
+      <c r="I37" s="9" t="n">
         <v>-16.8</v>
       </c>
-      <c r="I37" t="n">
+      <c r="J37" t="n">
         <v>11</v>
       </c>
-      <c r="J37" s="6" t="n">
+      <c r="K37" s="9" t="n">
         <v>31.8</v>
       </c>
-      <c r="K37" t="n">
+      <c r="L37" t="n">
         <v>6</v>
       </c>
-      <c r="L37" s="6" t="n">
+      <c r="M37" s="9" t="n">
         <v>8.5</v>
       </c>
-      <c r="M37" t="n">
+      <c r="N37" t="n">
         <v>6</v>
       </c>
-      <c r="N37" s="6" t="n">
+      <c r="O37" s="9" t="n">
         <v>-10.8</v>
       </c>
-      <c r="O37" t="n">
+      <c r="P37" t="n">
         <v>6</v>
       </c>
-      <c r="P37" s="6" t="n">
+      <c r="Q37" s="9" t="n">
         <v>-26.1</v>
       </c>
-      <c r="Q37" t="n">
+      <c r="R37" t="n">
         <v>8</v>
       </c>
-      <c r="R37" s="6" t="n">
+      <c r="S37" s="9" t="n">
         <v>13.1</v>
       </c>
-      <c r="S37" t="n">
+      <c r="T37" t="n">
         <v>5</v>
       </c>
-      <c r="T37" s="6" t="n">
+      <c r="U37" s="9" t="n">
         <v>69.90000000000001</v>
       </c>
-      <c r="U37" t="n">
+      <c r="V37" t="n">
         <v>3</v>
       </c>
     </row>
@@ -6798,56 +6986,61 @@
           <t>태양광</t>
         </is>
       </c>
-      <c r="D38" s="6" t="n">
+      <c r="D38" s="8" t="inlineStr">
+        <is>
+          <t>태양광 ETF는 1.4% 내렸고 실적 악화가 확인된 선그로우가 6.3% 급락했다.</t>
+        </is>
+      </c>
+      <c r="E38" s="9" t="n">
         <v>-1.4</v>
       </c>
-      <c r="E38" s="6" t="n">
+      <c r="F38" s="9" t="n">
         <v>-1</v>
       </c>
-      <c r="F38" s="6" t="n">
+      <c r="G38" s="9" t="n">
         <v>2.2</v>
       </c>
-      <c r="G38" s="6" t="n">
+      <c r="H38" s="9" t="n">
         <v>-20.9</v>
       </c>
-      <c r="H38" s="6" t="n">
+      <c r="I38" s="9" t="n">
         <v>-13.3</v>
       </c>
-      <c r="I38" t="n">
+      <c r="J38" t="n">
         <v>8</v>
       </c>
-      <c r="J38" s="6" t="n">
+      <c r="K38" s="9" t="n">
         <v>27.1</v>
       </c>
-      <c r="K38" t="n">
+      <c r="L38" t="n">
         <v>7</v>
       </c>
-      <c r="L38" s="6" t="n">
+      <c r="M38" s="9" t="n">
         <v>-14.9</v>
       </c>
-      <c r="M38" t="n">
+      <c r="N38" t="n">
         <v>13</v>
       </c>
-      <c r="N38" s="6" t="n">
+      <c r="O38" s="9" t="n">
         <v>-35.2</v>
       </c>
-      <c r="O38" t="n">
+      <c r="P38" t="n">
         <v>13</v>
       </c>
-      <c r="P38" s="6" t="n">
+      <c r="Q38" s="9" t="n">
         <v>-19.7</v>
       </c>
-      <c r="Q38" t="n">
+      <c r="R38" t="n">
         <v>5</v>
       </c>
-      <c r="R38" s="6" t="n">
+      <c r="S38" s="9" t="n">
         <v>50.7</v>
       </c>
-      <c r="S38" t="n">
+      <c r="T38" t="n">
         <v>1</v>
       </c>
-      <c r="T38" s="6" t="inlineStr"/>
-      <c r="U38" t="inlineStr"/>
+      <c r="U38" s="9" t="inlineStr"/>
+      <c r="V38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
@@ -6865,58 +7058,63 @@
           <t>백주(주류)</t>
         </is>
       </c>
-      <c r="D39" s="6" t="n">
+      <c r="D39" s="8" t="inlineStr">
+        <is>
+          <t>주류 ETF는 0.9% 내렸고 1개월 수익률도 -7.5%로 소비 약세가 이어졌다.</t>
+        </is>
+      </c>
+      <c r="E39" s="9" t="n">
         <v>-0.9</v>
       </c>
-      <c r="E39" s="6" t="n">
+      <c r="F39" s="9" t="n">
         <v>-0.5</v>
       </c>
-      <c r="F39" s="6" t="n">
+      <c r="G39" s="9" t="n">
         <v>-7.5</v>
       </c>
-      <c r="G39" s="6" t="n">
+      <c r="H39" s="9" t="n">
         <v>-6.5</v>
       </c>
-      <c r="H39" s="6" t="n">
+      <c r="I39" s="9" t="n">
         <v>-21.8</v>
       </c>
-      <c r="I39" t="n">
+      <c r="J39" t="n">
         <v>13</v>
       </c>
-      <c r="J39" s="6" t="n">
+      <c r="K39" s="9" t="n">
         <v>-13</v>
       </c>
-      <c r="K39" t="n">
+      <c r="L39" t="n">
         <v>13</v>
       </c>
-      <c r="L39" s="6" t="n">
+      <c r="M39" s="9" t="n">
         <v>-11</v>
       </c>
-      <c r="M39" t="n">
+      <c r="N39" t="n">
         <v>11</v>
       </c>
-      <c r="N39" s="6" t="n">
+      <c r="O39" s="9" t="n">
         <v>-18.6</v>
       </c>
-      <c r="O39" t="n">
+      <c r="P39" t="n">
         <v>10</v>
       </c>
-      <c r="P39" s="6" t="n">
+      <c r="Q39" s="9" t="n">
         <v>-11.9</v>
       </c>
-      <c r="Q39" t="n">
+      <c r="R39" t="n">
         <v>3</v>
       </c>
-      <c r="R39" s="6" t="n">
+      <c r="S39" s="9" t="n">
         <v>-3</v>
       </c>
-      <c r="S39" t="n">
+      <c r="T39" t="n">
         <v>9</v>
       </c>
-      <c r="T39" s="6" t="n">
+      <c r="U39" s="9" t="n">
         <v>302.8</v>
       </c>
-      <c r="U39" t="n">
+      <c r="V39" t="n">
         <v>1</v>
       </c>
     </row>
@@ -6936,58 +7134,63 @@
           <t>은행</t>
         </is>
       </c>
-      <c r="D40" s="6" t="n">
+      <c r="D40" s="8" t="inlineStr">
+        <is>
+          <t>은행 ETF는 1.5% 올랐고 금융 순강도 6으로 신고가 확산이 가장 뚜렷했다.</t>
+        </is>
+      </c>
+      <c r="E40" s="9" t="n">
         <v>1.5</v>
       </c>
-      <c r="E40" s="6" t="n">
+      <c r="F40" s="9" t="n">
         <v>0.2</v>
       </c>
-      <c r="F40" s="6" t="n">
+      <c r="G40" s="9" t="n">
         <v>-0.8</v>
       </c>
-      <c r="G40" s="6" t="n">
+      <c r="H40" s="9" t="n">
         <v>4.9</v>
       </c>
-      <c r="H40" s="6" t="n">
+      <c r="I40" s="9" t="n">
         <v>0.7</v>
       </c>
-      <c r="I40" t="n">
+      <c r="J40" t="n">
         <v>5</v>
       </c>
-      <c r="J40" s="6" t="n">
+      <c r="K40" s="9" t="n">
         <v>10.8</v>
       </c>
-      <c r="K40" t="n">
+      <c r="L40" t="n">
         <v>8</v>
       </c>
-      <c r="L40" s="6" t="n">
+      <c r="M40" s="9" t="n">
         <v>42.6</v>
       </c>
-      <c r="M40" t="n">
+      <c r="N40" t="n">
         <v>1</v>
       </c>
-      <c r="N40" s="6" t="n">
+      <c r="O40" s="9" t="n">
         <v>-3.3</v>
       </c>
-      <c r="O40" t="n">
+      <c r="P40" t="n">
         <v>5</v>
       </c>
-      <c r="P40" s="6" t="n">
+      <c r="Q40" s="9" t="n">
         <v>-4.8</v>
       </c>
-      <c r="Q40" t="n">
+      <c r="R40" t="n">
         <v>1</v>
       </c>
-      <c r="R40" s="6" t="n">
+      <c r="S40" s="9" t="n">
         <v>-1.2</v>
       </c>
-      <c r="S40" t="n">
+      <c r="T40" t="n">
         <v>7</v>
       </c>
-      <c r="T40" s="6" t="n">
+      <c r="U40" s="9" t="n">
         <v>1.2</v>
       </c>
-      <c r="U40" t="n">
+      <c r="V40" t="n">
         <v>10</v>
       </c>
     </row>
@@ -7007,58 +7210,63 @@
           <t>유색금속</t>
         </is>
       </c>
-      <c r="D41" s="6" t="n">
+      <c r="D41" s="8" t="inlineStr">
+        <is>
+          <t>유색금속 ETF는 1.5% 내렸지만 1개월 수익률은 9.0%로 차익실현 성격이 컸다.</t>
+        </is>
+      </c>
+      <c r="E41" s="9" t="n">
         <v>-1.5</v>
       </c>
-      <c r="E41" s="6" t="n">
+      <c r="F41" s="9" t="n">
         <v>0.2</v>
       </c>
-      <c r="F41" s="6" t="n">
+      <c r="G41" s="9" t="n">
         <v>9</v>
       </c>
-      <c r="G41" s="6" t="n">
+      <c r="H41" s="9" t="n">
         <v>-3.1</v>
       </c>
-      <c r="H41" s="6" t="n">
+      <c r="I41" s="9" t="n">
         <v>1.3</v>
       </c>
-      <c r="I41" t="n">
+      <c r="J41" t="n">
         <v>4</v>
       </c>
-      <c r="J41" s="6" t="n">
+      <c r="K41" s="9" t="n">
         <v>101.1</v>
       </c>
-      <c r="K41" t="n">
+      <c r="L41" t="n">
         <v>1</v>
       </c>
-      <c r="L41" s="6" t="n">
+      <c r="M41" s="9" t="n">
         <v>4.1</v>
       </c>
-      <c r="M41" t="n">
+      <c r="N41" t="n">
         <v>7</v>
       </c>
-      <c r="N41" s="6" t="n">
+      <c r="O41" s="9" t="n">
         <v>-11.4</v>
       </c>
-      <c r="O41" t="n">
+      <c r="P41" t="n">
         <v>7</v>
       </c>
-      <c r="P41" s="6" t="n">
+      <c r="Q41" s="9" t="n">
         <v>-21.6</v>
       </c>
-      <c r="Q41" t="n">
+      <c r="R41" t="n">
         <v>6</v>
       </c>
-      <c r="R41" s="6" t="n">
+      <c r="S41" s="9" t="n">
         <v>33.2</v>
       </c>
-      <c r="S41" t="n">
+      <c r="T41" t="n">
         <v>3</v>
       </c>
-      <c r="T41" s="6" t="n">
+      <c r="U41" s="9" t="n">
         <v>43.2</v>
       </c>
-      <c r="U41" t="n">
+      <c r="V41" t="n">
         <v>7</v>
       </c>
     </row>
@@ -7078,58 +7286,63 @@
           <t>부동산</t>
         </is>
       </c>
-      <c r="D42" s="6" t="n">
+      <c r="D42" s="8" t="inlineStr">
+        <is>
+          <t>부동산 ETF는 1.6% 내려 정책 기대보다 단기 실적 우려가 우세했다.</t>
+        </is>
+      </c>
+      <c r="E42" s="9" t="n">
         <v>-1.6</v>
       </c>
-      <c r="E42" s="6" t="n">
+      <c r="F42" s="9" t="n">
         <v>2.8</v>
       </c>
-      <c r="F42" s="6" t="n">
+      <c r="G42" s="9" t="n">
         <v>2.8</v>
       </c>
-      <c r="G42" s="6" t="n">
+      <c r="H42" s="9" t="n">
         <v>-8.300000000000001</v>
       </c>
-      <c r="H42" s="6" t="n">
+      <c r="I42" s="9" t="n">
         <v>-18.5</v>
       </c>
-      <c r="I42" t="n">
+      <c r="J42" t="n">
         <v>12</v>
       </c>
-      <c r="J42" s="6" t="n">
+      <c r="K42" s="9" t="n">
         <v>2.5</v>
       </c>
-      <c r="K42" t="n">
+      <c r="L42" t="n">
         <v>11</v>
       </c>
-      <c r="L42" s="6" t="n">
+      <c r="M42" s="9" t="n">
         <v>-0.5</v>
       </c>
-      <c r="M42" t="n">
+      <c r="N42" t="n">
         <v>9</v>
       </c>
-      <c r="N42" s="6" t="n">
+      <c r="O42" s="9" t="n">
         <v>-27</v>
       </c>
-      <c r="O42" t="n">
+      <c r="P42" t="n">
         <v>11</v>
       </c>
-      <c r="P42" s="6" t="n">
+      <c r="Q42" s="9" t="n">
         <v>-10.4</v>
       </c>
-      <c r="Q42" t="n">
+      <c r="R42" t="n">
         <v>2</v>
       </c>
-      <c r="R42" s="6" t="n">
+      <c r="S42" s="9" t="n">
         <v>-6.4</v>
       </c>
-      <c r="S42" t="n">
+      <c r="T42" t="n">
         <v>11</v>
       </c>
-      <c r="T42" s="6" t="n">
+      <c r="U42" s="9" t="n">
         <v>-4.3</v>
       </c>
-      <c r="U42" t="n">
+      <c r="V42" t="n">
         <v>11</v>
       </c>
     </row>
@@ -7149,58 +7362,63 @@
           <t>증권</t>
         </is>
       </c>
-      <c r="D43" s="6" t="n">
+      <c r="D43" s="8" t="inlineStr">
+        <is>
+          <t>증권 ETF는 0.1% 올라 주간 3.6% 반등 뒤 숨고르기에 들어갔다.</t>
+        </is>
+      </c>
+      <c r="E43" s="9" t="n">
         <v>0.1</v>
       </c>
-      <c r="E43" s="6" t="n">
+      <c r="F43" s="9" t="n">
         <v>3.6</v>
       </c>
-      <c r="F43" s="6" t="n">
+      <c r="G43" s="9" t="n">
         <v>-0.2</v>
       </c>
-      <c r="G43" s="6" t="n">
+      <c r="H43" s="9" t="n">
         <v>6.6</v>
       </c>
-      <c r="H43" s="6" t="n">
+      <c r="I43" s="9" t="n">
         <v>-8.800000000000001</v>
       </c>
-      <c r="I43" t="n">
+      <c r="J43" t="n">
         <v>7</v>
       </c>
-      <c r="J43" s="6" t="n">
+      <c r="K43" s="9" t="n">
         <v>3.5</v>
       </c>
-      <c r="K43" t="n">
+      <c r="L43" t="n">
         <v>10</v>
       </c>
-      <c r="L43" s="6" t="n">
+      <c r="M43" s="9" t="n">
         <v>29.7</v>
       </c>
-      <c r="M43" t="n">
+      <c r="N43" t="n">
         <v>2</v>
       </c>
-      <c r="N43" s="6" t="n">
+      <c r="O43" s="9" t="n">
         <v>3.8</v>
       </c>
-      <c r="O43" t="n">
+      <c r="P43" t="n">
         <v>2</v>
       </c>
-      <c r="P43" s="6" t="n">
+      <c r="Q43" s="9" t="n">
         <v>-26.1</v>
       </c>
-      <c r="Q43" t="n">
+      <c r="R43" t="n">
         <v>8</v>
       </c>
-      <c r="R43" s="6" t="n">
+      <c r="S43" s="9" t="n">
         <v>-3.8</v>
       </c>
-      <c r="S43" t="n">
+      <c r="T43" t="n">
         <v>10</v>
       </c>
-      <c r="T43" s="6" t="n">
+      <c r="U43" s="9" t="n">
         <v>17.5</v>
       </c>
-      <c r="U43" t="n">
+      <c r="V43" t="n">
         <v>9</v>
       </c>
     </row>
@@ -7220,58 +7438,63 @@
           <t>의약</t>
         </is>
       </c>
-      <c r="D44" s="6" t="n">
+      <c r="D44" s="8" t="inlineStr">
+        <is>
+          <t>의약 ETF는 1.8% 내렸지만 3개월 수익률은 11.9%로 중기 강세는 남았다.</t>
+        </is>
+      </c>
+      <c r="E44" s="9" t="n">
         <v>-1.8</v>
       </c>
-      <c r="E44" s="6" t="n">
+      <c r="F44" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="F44" s="6" t="n">
+      <c r="G44" s="9" t="n">
         <v>-0.3</v>
       </c>
-      <c r="G44" s="6" t="n">
+      <c r="H44" s="9" t="n">
         <v>11.9</v>
       </c>
-      <c r="H44" s="6" t="n">
+      <c r="I44" s="9" t="n">
         <v>-0.5</v>
       </c>
-      <c r="I44" t="n">
+      <c r="J44" t="n">
         <v>6</v>
       </c>
-      <c r="J44" s="6" t="n">
+      <c r="K44" s="9" t="n">
         <v>4.7</v>
       </c>
-      <c r="K44" t="n">
+      <c r="L44" t="n">
         <v>9</v>
       </c>
-      <c r="L44" s="6" t="n">
+      <c r="M44" s="9" t="n">
         <v>-12.2</v>
       </c>
-      <c r="M44" t="n">
+      <c r="N44" t="n">
         <v>12</v>
       </c>
-      <c r="N44" s="6" t="n">
+      <c r="O44" s="9" t="n">
         <v>-14</v>
       </c>
-      <c r="O44" t="n">
+      <c r="P44" t="n">
         <v>8</v>
       </c>
-      <c r="P44" s="6" t="n">
+      <c r="Q44" s="9" t="n">
         <v>-24.5</v>
       </c>
-      <c r="Q44" t="n">
+      <c r="R44" t="n">
         <v>7</v>
       </c>
-      <c r="R44" s="6" t="n">
+      <c r="S44" s="9" t="n">
         <v>-15.7</v>
       </c>
-      <c r="S44" t="n">
+      <c r="T44" t="n">
         <v>13</v>
       </c>
-      <c r="T44" s="6" t="n">
+      <c r="U44" s="9" t="n">
         <v>62.9</v>
       </c>
-      <c r="U44" t="n">
+      <c r="V44" t="n">
         <v>4</v>
       </c>
     </row>
@@ -7291,58 +7514,63 @@
           <t>소비(消费)</t>
         </is>
       </c>
-      <c r="D45" s="6" t="n">
+      <c r="D45" s="8" t="inlineStr">
+        <is>
+          <t>소비 ETF는 0.7% 내렸고 1개월 수익률도 -4.4%로 약세가 이어졌다.</t>
+        </is>
+      </c>
+      <c r="E45" s="9" t="n">
         <v>-0.7</v>
       </c>
-      <c r="E45" s="6" t="n">
+      <c r="F45" s="9" t="n">
         <v>0.9</v>
       </c>
-      <c r="F45" s="6" t="n">
+      <c r="G45" s="9" t="n">
         <v>-4.4</v>
       </c>
-      <c r="G45" s="6" t="n">
+      <c r="H45" s="9" t="n">
         <v>-2.1</v>
       </c>
-      <c r="H45" s="6" t="n">
+      <c r="I45" s="9" t="n">
         <v>-16</v>
       </c>
-      <c r="I45" t="n">
+      <c r="J45" t="n">
         <v>10</v>
       </c>
-      <c r="J45" s="6" t="n">
+      <c r="K45" s="9" t="n">
         <v>-2.9</v>
       </c>
-      <c r="K45" t="n">
+      <c r="L45" t="n">
         <v>12</v>
       </c>
-      <c r="L45" s="6" t="n">
+      <c r="M45" s="9" t="n">
         <v>-4.2</v>
       </c>
-      <c r="M45" t="n">
+      <c r="N45" t="n">
         <v>10</v>
       </c>
-      <c r="N45" s="6" t="n">
+      <c r="O45" s="9" t="n">
         <v>-18.3</v>
       </c>
-      <c r="O45" t="n">
+      <c r="P45" t="n">
         <v>9</v>
       </c>
-      <c r="P45" s="6" t="n">
+      <c r="Q45" s="9" t="n">
         <v>-13.4</v>
       </c>
-      <c r="Q45" t="n">
+      <c r="R45" t="n">
         <v>4</v>
       </c>
-      <c r="R45" s="6" t="n">
+      <c r="S45" s="9" t="n">
         <v>-7.5</v>
       </c>
-      <c r="S45" t="n">
+      <c r="T45" t="n">
         <v>12</v>
       </c>
-      <c r="T45" s="6" t="n">
+      <c r="U45" s="9" t="n">
         <v>77.40000000000001</v>
       </c>
-      <c r="U45" t="n">
+      <c r="V45" t="n">
         <v>2</v>
       </c>
     </row>
@@ -7354,7 +7582,7 @@
       </c>
     </row>
   </sheetData>
-  <conditionalFormatting sqref="D2:D45">
+  <conditionalFormatting sqref="E2:E45">
     <cfRule type="colorScale" priority="1">
       <colorScale>
         <cfvo type="num" val="-2.2"/>
@@ -7366,7 +7594,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="E2:E45">
+  <conditionalFormatting sqref="F2:F45">
     <cfRule type="colorScale" priority="2">
       <colorScale>
         <cfvo type="num" val="-2.8"/>
@@ -7378,7 +7606,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F2:F45">
+  <conditionalFormatting sqref="G2:G45">
     <cfRule type="colorScale" priority="3">
       <colorScale>
         <cfvo type="num" val="-7.5"/>
@@ -7390,7 +7618,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G2:G45">
+  <conditionalFormatting sqref="H2:H45">
     <cfRule type="colorScale" priority="4">
       <colorScale>
         <cfvo type="num" val="-20.9"/>
@@ -7402,7 +7630,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="H2:H45">
+  <conditionalFormatting sqref="I2:I45">
     <cfRule type="colorScale" priority="5">
       <colorScale>
         <cfvo type="num" val="-21.8"/>
@@ -7414,7 +7642,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="J2:J45">
+  <conditionalFormatting sqref="K2:K45">
     <cfRule type="colorScale" priority="6">
       <colorScale>
         <cfvo type="num" val="-13"/>
@@ -7426,7 +7654,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="L2:L45">
+  <conditionalFormatting sqref="M2:M45">
     <cfRule type="colorScale" priority="7">
       <colorScale>
         <cfvo type="num" val="-14.9"/>
@@ -7438,7 +7666,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="N2:N45">
+  <conditionalFormatting sqref="O2:O45">
     <cfRule type="colorScale" priority="8">
       <colorScale>
         <cfvo type="num" val="-35.2"/>
@@ -7450,7 +7678,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="P2:P45">
+  <conditionalFormatting sqref="Q2:Q45">
     <cfRule type="colorScale" priority="9">
       <colorScale>
         <cfvo type="num" val="-37.8"/>
@@ -7462,7 +7690,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="R2:R45">
+  <conditionalFormatting sqref="S2:S45">
     <cfRule type="colorScale" priority="10">
       <colorScale>
         <cfvo type="num" val="-32.9"/>
@@ -7474,7 +7702,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="T2:T45">
+  <conditionalFormatting sqref="U2:U45">
     <cfRule type="colorScale" priority="11">
       <colorScale>
         <cfvo type="num" val="-32.7"/>
@@ -7588,12 +7816,12 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="4" t="inlineStr">
+      <c r="A2" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
       </c>
-      <c r="B2" s="7" t="inlineStr">
+      <c r="B2" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -7641,10 +7869,14 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N2" s="8" t="inlineStr"/>
+      <c r="N2" s="10" t="inlineStr">
+        <is>
+          <t>크라우드스트라이크(클라우드 보안): 8월 27일 분기 호실적 뒤 매수세가 이어졌다.</t>
+        </is>
+      </c>
     </row>
     <row r="3">
-      <c r="A3" s="4" t="inlineStr">
+      <c r="A3" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -7693,14 +7925,14 @@
         </is>
       </c>
       <c r="M3" t="inlineStr"/>
-      <c r="N3" s="8" t="inlineStr">
+      <c r="N3" s="10" t="inlineStr">
         <is>
           <t>(전일) AT&amp;T(통신): 3분기 실적 발표 일정 공지 외 신규 촉매 미확인</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="5" t="inlineStr">
+      <c r="A4" s="7" t="inlineStr">
         <is>
           <t>신저가</t>
         </is>
@@ -7749,15 +7981,15 @@
         </is>
       </c>
       <c r="M4" t="inlineStr"/>
-      <c r="N4" s="8" t="inlineStr"/>
+      <c r="N4" s="10" t="inlineStr"/>
     </row>
     <row r="5">
-      <c r="A5" s="4" t="inlineStr">
+      <c r="A5" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
       </c>
-      <c r="B5" s="7" t="inlineStr">
+      <c r="B5" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -7805,15 +8037,15 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N5" s="8" t="inlineStr"/>
+      <c r="N5" s="10" t="inlineStr"/>
     </row>
     <row r="6">
-      <c r="A6" s="4" t="inlineStr">
+      <c r="A6" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
       </c>
-      <c r="B6" s="7" t="inlineStr">
+      <c r="B6" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -7857,10 +8089,10 @@
         </is>
       </c>
       <c r="M6" t="inlineStr"/>
-      <c r="N6" s="8" t="inlineStr"/>
+      <c r="N6" s="10" t="inlineStr"/>
     </row>
     <row r="7">
-      <c r="A7" s="4" t="inlineStr">
+      <c r="A7" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -7909,14 +8141,14 @@
         </is>
       </c>
       <c r="M7" t="inlineStr"/>
-      <c r="N7" s="8" t="inlineStr">
+      <c r="N7" s="10" t="inlineStr">
         <is>
           <t>(전일) 서비스나우(기업 업무자동화 플랫폼): 세일즈포스 호실적에 대형 소프트웨어 동반 강세</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="5" t="inlineStr">
+      <c r="A8" s="7" t="inlineStr">
         <is>
           <t>신저가</t>
         </is>
@@ -7969,14 +8201,14 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N8" s="8" t="inlineStr">
+      <c r="N8" s="10" t="inlineStr">
         <is>
           <t>(전일) TJX(티제이맥스·마셜스 할인 유통): 마막스 부문 둔화를 짚은 투자의견 하향 여파</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="4" t="inlineStr">
+      <c r="A9" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -8025,14 +8257,14 @@
         </is>
       </c>
       <c r="M9" t="inlineStr"/>
-      <c r="N9" s="8" t="inlineStr">
+      <c r="N9" s="10" t="inlineStr">
         <is>
           <t>(전일) 어도비(크리에이티브·문서 소프트웨어): 선행 PER 11배 저평가 부각되며 섹터 랠리에 동반</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="4" t="inlineStr">
+      <c r="A10" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -8085,15 +8317,15 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N10" s="8" t="inlineStr"/>
+      <c r="N10" s="10" t="inlineStr"/>
     </row>
     <row r="11">
-      <c r="A11" s="4" t="inlineStr">
+      <c r="A11" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
       </c>
-      <c r="B11" s="7" t="inlineStr">
+      <c r="B11" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -8141,10 +8373,14 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N11" s="8" t="inlineStr"/>
+      <c r="N11" s="10" t="inlineStr">
+        <is>
+          <t>발레로(정유): 특별한 뉴스 없음. 정유마진과 에너지 업종 강세에 따른 흐름으로 추정한다.</t>
+        </is>
+      </c>
     </row>
     <row r="12">
-      <c r="A12" s="4" t="inlineStr">
+      <c r="A12" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -8193,10 +8429,10 @@
         </is>
       </c>
       <c r="M12" t="inlineStr"/>
-      <c r="N12" s="8" t="inlineStr"/>
+      <c r="N12" s="10" t="inlineStr"/>
     </row>
     <row r="13">
-      <c r="A13" s="5" t="inlineStr">
+      <c r="A13" s="7" t="inlineStr">
         <is>
           <t>신저가</t>
         </is>
@@ -8245,15 +8481,15 @@
         </is>
       </c>
       <c r="M13" t="inlineStr"/>
-      <c r="N13" s="8" t="inlineStr"/>
+      <c r="N13" s="10" t="inlineStr"/>
     </row>
     <row r="14">
-      <c r="A14" s="4" t="inlineStr">
+      <c r="A14" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
       </c>
-      <c r="B14" s="7" t="inlineStr">
+      <c r="B14" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -8301,15 +8537,15 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N14" s="8" t="inlineStr"/>
+      <c r="N14" s="10" t="inlineStr"/>
     </row>
     <row r="15">
-      <c r="A15" s="5" t="inlineStr">
+      <c r="A15" s="7" t="inlineStr">
         <is>
           <t>신저가</t>
         </is>
       </c>
-      <c r="B15" s="7" t="inlineStr">
+      <c r="B15" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -8353,10 +8589,14 @@
         </is>
       </c>
       <c r="M15" t="inlineStr"/>
-      <c r="N15" s="8" t="inlineStr"/>
+      <c r="N15" s="10" t="inlineStr">
+        <is>
+          <t>하우멧(항공우주 부품): 특별한 뉴스 없음. 고평가 항공우주주 차익실현으로 추정한다.</t>
+        </is>
+      </c>
     </row>
     <row r="16">
-      <c r="A16" s="5" t="inlineStr">
+      <c r="A16" s="7" t="inlineStr">
         <is>
           <t>신저가</t>
         </is>
@@ -8405,15 +8645,15 @@
         </is>
       </c>
       <c r="M16" t="inlineStr"/>
-      <c r="N16" s="8" t="inlineStr"/>
+      <c r="N16" s="10" t="inlineStr"/>
     </row>
     <row r="17">
-      <c r="A17" s="5" t="inlineStr">
+      <c r="A17" s="7" t="inlineStr">
         <is>
           <t>신저가</t>
         </is>
       </c>
-      <c r="B17" s="7" t="inlineStr">
+      <c r="B17" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -8457,15 +8697,15 @@
         </is>
       </c>
       <c r="M17" t="inlineStr"/>
-      <c r="N17" s="8" t="inlineStr"/>
+      <c r="N17" s="10" t="inlineStr"/>
     </row>
     <row r="18">
-      <c r="A18" s="4" t="inlineStr">
+      <c r="A18" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
       </c>
-      <c r="B18" s="7" t="inlineStr">
+      <c r="B18" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -8513,10 +8753,14 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N18" s="8" t="inlineStr"/>
+      <c r="N18" s="10" t="inlineStr">
+        <is>
+          <t>SLB(유전서비스): 유전 데이터 접근과 탄소저장 계약 기대가 에너지 강세에 힘을 보탰다.</t>
+        </is>
+      </c>
     </row>
     <row r="19">
-      <c r="A19" s="5" t="inlineStr">
+      <c r="A19" s="7" t="inlineStr">
         <is>
           <t>신저가</t>
         </is>
@@ -8565,15 +8809,15 @@
         </is>
       </c>
       <c r="M19" t="inlineStr"/>
-      <c r="N19" s="8" t="inlineStr"/>
+      <c r="N19" s="10" t="inlineStr"/>
     </row>
     <row r="20">
-      <c r="A20" s="5" t="inlineStr">
+      <c r="A20" s="7" t="inlineStr">
         <is>
           <t>신저가</t>
         </is>
       </c>
-      <c r="B20" s="7" t="inlineStr">
+      <c r="B20" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -8617,10 +8861,10 @@
         </is>
       </c>
       <c r="M20" t="inlineStr"/>
-      <c r="N20" s="8" t="inlineStr"/>
+      <c r="N20" s="10" t="inlineStr"/>
     </row>
     <row r="21">
-      <c r="A21" s="5" t="inlineStr">
+      <c r="A21" s="7" t="inlineStr">
         <is>
           <t>신저가</t>
         </is>
@@ -8667,15 +8911,15 @@
         </is>
       </c>
       <c r="M21" t="inlineStr"/>
-      <c r="N21" s="8" t="inlineStr"/>
+      <c r="N21" s="10" t="inlineStr"/>
     </row>
     <row r="22">
-      <c r="A22" s="4" t="inlineStr">
+      <c r="A22" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
       </c>
-      <c r="B22" s="7" t="inlineStr">
+      <c r="B22" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -8719,15 +8963,19 @@
         </is>
       </c>
       <c r="M22" t="inlineStr"/>
-      <c r="N22" s="8" t="inlineStr"/>
+      <c r="N22" s="10" t="inlineStr">
+        <is>
+          <t>셰니어에너지(LNG 수출): CCL 3단계 완공과 5천번째 화물 수출 발표가 촉매였다.</t>
+        </is>
+      </c>
     </row>
     <row r="23">
-      <c r="A23" s="5" t="inlineStr">
+      <c r="A23" s="7" t="inlineStr">
         <is>
           <t>신저가</t>
         </is>
       </c>
-      <c r="B23" s="7" t="inlineStr">
+      <c r="B23" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -8771,15 +9019,15 @@
         </is>
       </c>
       <c r="M23" t="inlineStr"/>
-      <c r="N23" s="8" t="inlineStr"/>
+      <c r="N23" s="10" t="inlineStr"/>
     </row>
     <row r="24">
-      <c r="A24" s="5" t="inlineStr">
+      <c r="A24" s="7" t="inlineStr">
         <is>
           <t>신저가</t>
         </is>
       </c>
-      <c r="B24" s="7" t="inlineStr">
+      <c r="B24" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -8823,10 +9071,14 @@
         </is>
       </c>
       <c r="M24" t="inlineStr"/>
-      <c r="N24" s="8" t="inlineStr"/>
+      <c r="N24" s="10" t="inlineStr">
+        <is>
+          <t>셈프라(가스·전력): 산불 책임법 실망으로 캘리포니아 유틸리티 매도가 번진 것으로 추정한다.</t>
+        </is>
+      </c>
     </row>
     <row r="25">
-      <c r="A25" s="4" t="inlineStr">
+      <c r="A25" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -8877,14 +9129,14 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N25" s="8" t="inlineStr">
+      <c r="N25" s="10" t="inlineStr">
         <is>
           <t>(전일) 아틀라시안(지라·컨플루언스 협업 도구): 세일즈포스발 SaaS 재평가에 동반 상승</t>
         </is>
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="5" t="inlineStr">
+      <c r="A26" s="7" t="inlineStr">
         <is>
           <t>신저가</t>
         </is>
@@ -8933,15 +9185,15 @@
         </is>
       </c>
       <c r="M26" t="inlineStr"/>
-      <c r="N26" s="8" t="inlineStr"/>
+      <c r="N26" s="10" t="inlineStr"/>
     </row>
     <row r="27">
-      <c r="A27" s="5" t="inlineStr">
+      <c r="A27" s="7" t="inlineStr">
         <is>
           <t>신저가</t>
         </is>
       </c>
-      <c r="B27" s="7" t="inlineStr">
+      <c r="B27" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -8985,15 +9237,15 @@
         </is>
       </c>
       <c r="M27" t="inlineStr"/>
-      <c r="N27" s="8" t="inlineStr"/>
+      <c r="N27" s="10" t="inlineStr"/>
     </row>
     <row r="28">
-      <c r="A28" s="5" t="inlineStr">
+      <c r="A28" s="7" t="inlineStr">
         <is>
           <t>신저가</t>
         </is>
       </c>
-      <c r="B28" s="7" t="inlineStr">
+      <c r="B28" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -9037,10 +9289,10 @@
         </is>
       </c>
       <c r="M28" t="inlineStr"/>
-      <c r="N28" s="8" t="inlineStr"/>
+      <c r="N28" s="10" t="inlineStr"/>
     </row>
     <row r="29">
-      <c r="A29" s="5" t="inlineStr">
+      <c r="A29" s="7" t="inlineStr">
         <is>
           <t>신저가</t>
         </is>
@@ -9087,19 +9339,19 @@
         </is>
       </c>
       <c r="M29" t="inlineStr"/>
-      <c r="N29" s="8" t="inlineStr">
+      <c r="N29" s="10" t="inlineStr">
         <is>
           <t>(전일) 페로비알(유료도로·공항 인프라 운영): 특별한 뉴스 없음(개별 약세 지속)</t>
         </is>
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="5" t="inlineStr">
+      <c r="A30" s="7" t="inlineStr">
         <is>
           <t>신저가</t>
         </is>
       </c>
-      <c r="B30" s="7" t="inlineStr">
+      <c r="B30" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -9143,15 +9395,15 @@
         </is>
       </c>
       <c r="M30" t="inlineStr"/>
-      <c r="N30" s="8" t="inlineStr"/>
+      <c r="N30" s="10" t="inlineStr"/>
     </row>
     <row r="31">
-      <c r="A31" s="5" t="inlineStr">
+      <c r="A31" s="7" t="inlineStr">
         <is>
           <t>신저가</t>
         </is>
       </c>
-      <c r="B31" s="7" t="inlineStr">
+      <c r="B31" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -9193,15 +9445,15 @@
         </is>
       </c>
       <c r="M31" t="inlineStr"/>
-      <c r="N31" s="8" t="inlineStr"/>
+      <c r="N31" s="10" t="inlineStr"/>
     </row>
     <row r="32">
-      <c r="A32" s="5" t="inlineStr">
+      <c r="A32" s="7" t="inlineStr">
         <is>
           <t>신저가</t>
         </is>
       </c>
-      <c r="B32" s="7" t="inlineStr">
+      <c r="B32" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -9249,10 +9501,10 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N32" s="8" t="inlineStr"/>
+      <c r="N32" s="10" t="inlineStr"/>
     </row>
     <row r="33">
-      <c r="A33" s="4" t="inlineStr">
+      <c r="A33" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -9301,15 +9553,15 @@
         </is>
       </c>
       <c r="M33" t="inlineStr"/>
-      <c r="N33" s="8" t="inlineStr"/>
+      <c r="N33" s="10" t="inlineStr"/>
     </row>
     <row r="34">
-      <c r="A34" s="5" t="inlineStr">
+      <c r="A34" s="7" t="inlineStr">
         <is>
           <t>신저가</t>
         </is>
       </c>
-      <c r="B34" s="7" t="inlineStr">
+      <c r="B34" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -9353,15 +9605,15 @@
         </is>
       </c>
       <c r="M34" t="inlineStr"/>
-      <c r="N34" s="8" t="inlineStr"/>
+      <c r="N34" s="10" t="inlineStr"/>
     </row>
     <row r="35">
-      <c r="A35" s="5" t="inlineStr">
+      <c r="A35" s="7" t="inlineStr">
         <is>
           <t>신저가</t>
         </is>
       </c>
-      <c r="B35" s="7" t="inlineStr">
+      <c r="B35" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -9403,15 +9655,15 @@
         </is>
       </c>
       <c r="M35" t="inlineStr"/>
-      <c r="N35" s="8" t="inlineStr"/>
+      <c r="N35" s="10" t="inlineStr"/>
     </row>
     <row r="36">
-      <c r="A36" s="4" t="inlineStr">
+      <c r="A36" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
       </c>
-      <c r="B36" s="7" t="inlineStr">
+      <c r="B36" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -9459,10 +9711,14 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N36" s="8" t="inlineStr"/>
+      <c r="N36" s="10" t="inlineStr">
+        <is>
+          <t>셰니어파트너스(LNG 터미널): CCL 3단계 완공으로 현금흐름 기대가 높아졌다.</t>
+        </is>
+      </c>
     </row>
     <row r="37">
-      <c r="A37" s="5" t="inlineStr">
+      <c r="A37" s="7" t="inlineStr">
         <is>
           <t>신저가</t>
         </is>
@@ -9509,10 +9765,10 @@
         </is>
       </c>
       <c r="M37" t="inlineStr"/>
-      <c r="N37" s="8" t="inlineStr"/>
+      <c r="N37" s="10" t="inlineStr"/>
     </row>
     <row r="38">
-      <c r="A38" s="5" t="inlineStr">
+      <c r="A38" s="7" t="inlineStr">
         <is>
           <t>신저가</t>
         </is>
@@ -9561,15 +9817,15 @@
         </is>
       </c>
       <c r="M38" t="inlineStr"/>
-      <c r="N38" s="8" t="inlineStr"/>
+      <c r="N38" s="10" t="inlineStr"/>
     </row>
     <row r="39">
-      <c r="A39" s="5" t="inlineStr">
+      <c r="A39" s="7" t="inlineStr">
         <is>
           <t>신저가</t>
         </is>
       </c>
-      <c r="B39" s="7" t="inlineStr">
+      <c r="B39" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -9613,15 +9869,15 @@
         </is>
       </c>
       <c r="M39" t="inlineStr"/>
-      <c r="N39" s="8" t="inlineStr"/>
+      <c r="N39" s="10" t="inlineStr"/>
     </row>
     <row r="40">
-      <c r="A40" s="5" t="inlineStr">
+      <c r="A40" s="7" t="inlineStr">
         <is>
           <t>신저가</t>
         </is>
       </c>
-      <c r="B40" s="7" t="inlineStr">
+      <c r="B40" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -9665,10 +9921,10 @@
         </is>
       </c>
       <c r="M40" t="inlineStr"/>
-      <c r="N40" s="8" t="inlineStr"/>
+      <c r="N40" s="10" t="inlineStr"/>
     </row>
     <row r="41">
-      <c r="A41" s="5" t="inlineStr">
+      <c r="A41" s="7" t="inlineStr">
         <is>
           <t>신저가</t>
         </is>
@@ -9721,19 +9977,19 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N41" s="8" t="inlineStr">
-        <is>
-          <t>(전일) PG&amp;E(캘리포니아 전력): 산불 책임 관련 보험사 구상권 제한 협상 무산</t>
+      <c r="N41" s="10" t="inlineStr">
+        <is>
+          <t>PG&amp;E(캘리포니아 전력): 산불기금 보충과 책임상한이 법안에서 빠져 추가 매도됐다.</t>
         </is>
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="5" t="inlineStr">
+      <c r="A42" s="7" t="inlineStr">
         <is>
           <t>신저가</t>
         </is>
       </c>
-      <c r="B42" s="7" t="inlineStr">
+      <c r="B42" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -9781,15 +10037,15 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N42" s="8" t="inlineStr"/>
+      <c r="N42" s="10" t="inlineStr"/>
     </row>
     <row r="43">
-      <c r="A43" s="5" t="inlineStr">
+      <c r="A43" s="7" t="inlineStr">
         <is>
           <t>신저가</t>
         </is>
       </c>
-      <c r="B43" s="7" t="inlineStr">
+      <c r="B43" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -9833,15 +10089,15 @@
         </is>
       </c>
       <c r="M43" t="inlineStr"/>
-      <c r="N43" s="8" t="inlineStr"/>
+      <c r="N43" s="10" t="inlineStr"/>
     </row>
     <row r="44">
-      <c r="A44" s="5" t="inlineStr">
+      <c r="A44" s="7" t="inlineStr">
         <is>
           <t>신저가</t>
         </is>
       </c>
-      <c r="B44" s="7" t="inlineStr">
+      <c r="B44" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -9889,15 +10145,15 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N44" s="8" t="inlineStr"/>
+      <c r="N44" s="10" t="inlineStr"/>
     </row>
     <row r="45">
-      <c r="A45" s="5" t="inlineStr">
+      <c r="A45" s="7" t="inlineStr">
         <is>
           <t>신저가</t>
         </is>
       </c>
-      <c r="B45" s="7" t="inlineStr">
+      <c r="B45" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -9941,15 +10197,15 @@
         </is>
       </c>
       <c r="M45" t="inlineStr"/>
-      <c r="N45" s="8" t="inlineStr"/>
+      <c r="N45" s="10" t="inlineStr"/>
     </row>
     <row r="46">
-      <c r="A46" s="5" t="inlineStr">
+      <c r="A46" s="7" t="inlineStr">
         <is>
           <t>신저가</t>
         </is>
       </c>
-      <c r="B46" s="7" t="inlineStr">
+      <c r="B46" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -9993,10 +10249,10 @@
         </is>
       </c>
       <c r="M46" t="inlineStr"/>
-      <c r="N46" s="8" t="inlineStr"/>
+      <c r="N46" s="10" t="inlineStr"/>
     </row>
     <row r="47">
-      <c r="A47" s="5" t="inlineStr">
+      <c r="A47" s="7" t="inlineStr">
         <is>
           <t>신저가</t>
         </is>
@@ -10045,10 +10301,10 @@
         </is>
       </c>
       <c r="M47" t="inlineStr"/>
-      <c r="N47" s="8" t="inlineStr"/>
+      <c r="N47" s="10" t="inlineStr"/>
     </row>
     <row r="48">
-      <c r="A48" s="5" t="inlineStr">
+      <c r="A48" s="7" t="inlineStr">
         <is>
           <t>신저가</t>
         </is>
@@ -10097,15 +10353,15 @@
         </is>
       </c>
       <c r="M48" t="inlineStr"/>
-      <c r="N48" s="8" t="inlineStr"/>
+      <c r="N48" s="10" t="inlineStr"/>
     </row>
     <row r="49">
-      <c r="A49" s="5" t="inlineStr">
+      <c r="A49" s="7" t="inlineStr">
         <is>
           <t>신저가</t>
         </is>
       </c>
-      <c r="B49" s="7" t="inlineStr">
+      <c r="B49" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -10149,10 +10405,10 @@
         </is>
       </c>
       <c r="M49" t="inlineStr"/>
-      <c r="N49" s="8" t="inlineStr"/>
+      <c r="N49" s="10" t="inlineStr"/>
     </row>
     <row r="50">
-      <c r="A50" s="5" t="inlineStr">
+      <c r="A50" s="7" t="inlineStr">
         <is>
           <t>신저가</t>
         </is>
@@ -10201,15 +10457,15 @@
         </is>
       </c>
       <c r="M50" t="inlineStr"/>
-      <c r="N50" s="8" t="inlineStr"/>
+      <c r="N50" s="10" t="inlineStr"/>
     </row>
     <row r="51">
-      <c r="A51" s="5" t="inlineStr">
+      <c r="A51" s="7" t="inlineStr">
         <is>
           <t>신저가</t>
         </is>
       </c>
-      <c r="B51" s="7" t="inlineStr">
+      <c r="B51" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -10257,15 +10513,15 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N51" s="8" t="inlineStr"/>
+      <c r="N51" s="10" t="inlineStr"/>
     </row>
     <row r="52">
-      <c r="A52" s="5" t="inlineStr">
+      <c r="A52" s="7" t="inlineStr">
         <is>
           <t>신저가</t>
         </is>
       </c>
-      <c r="B52" s="7" t="inlineStr">
+      <c r="B52" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -10309,15 +10565,15 @@
         </is>
       </c>
       <c r="M52" t="inlineStr"/>
-      <c r="N52" s="8" t="inlineStr"/>
+      <c r="N52" s="10" t="inlineStr"/>
     </row>
     <row r="53">
-      <c r="A53" s="5" t="inlineStr">
+      <c r="A53" s="7" t="inlineStr">
         <is>
           <t>신저가</t>
         </is>
       </c>
-      <c r="B53" s="7" t="inlineStr">
+      <c r="B53" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -10361,10 +10617,10 @@
         </is>
       </c>
       <c r="M53" t="inlineStr"/>
-      <c r="N53" s="8" t="inlineStr"/>
+      <c r="N53" s="10" t="inlineStr"/>
     </row>
     <row r="54">
-      <c r="A54" s="5" t="inlineStr">
+      <c r="A54" s="7" t="inlineStr">
         <is>
           <t>신저가</t>
         </is>
@@ -10417,10 +10673,10 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N54" s="8" t="inlineStr"/>
+      <c r="N54" s="10" t="inlineStr"/>
     </row>
     <row r="55">
-      <c r="A55" s="4" t="inlineStr">
+      <c r="A55" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -10469,10 +10725,10 @@
         </is>
       </c>
       <c r="M55" t="inlineStr"/>
-      <c r="N55" s="8" t="inlineStr"/>
+      <c r="N55" s="10" t="inlineStr"/>
     </row>
     <row r="56">
-      <c r="A56" s="4" t="inlineStr">
+      <c r="A56" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -10519,14 +10775,14 @@
         </is>
       </c>
       <c r="M56" t="inlineStr"/>
-      <c r="N56" s="8" t="inlineStr">
+      <c r="N56" s="10" t="inlineStr">
         <is>
           <t>(전일) 제너럴밀스(가공식품): 특별한 회사 뉴스 없음(방어주 수급 영향 추정)</t>
         </is>
       </c>
     </row>
     <row r="57">
-      <c r="A57" s="5" t="inlineStr">
+      <c r="A57" s="7" t="inlineStr">
         <is>
           <t>신저가</t>
         </is>
@@ -10575,15 +10831,15 @@
         </is>
       </c>
       <c r="M57" t="inlineStr"/>
-      <c r="N57" s="8" t="inlineStr"/>
+      <c r="N57" s="10" t="inlineStr"/>
     </row>
     <row r="58">
-      <c r="A58" s="5" t="inlineStr">
+      <c r="A58" s="7" t="inlineStr">
         <is>
           <t>신저가</t>
         </is>
       </c>
-      <c r="B58" s="7" t="inlineStr">
+      <c r="B58" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -10631,15 +10887,15 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N58" s="8" t="inlineStr"/>
+      <c r="N58" s="10" t="inlineStr"/>
     </row>
     <row r="59">
-      <c r="A59" s="5" t="inlineStr">
+      <c r="A59" s="7" t="inlineStr">
         <is>
           <t>신저가</t>
         </is>
       </c>
-      <c r="B59" s="7" t="inlineStr">
+      <c r="B59" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -10683,10 +10939,14 @@
         </is>
       </c>
       <c r="M59" t="inlineStr"/>
-      <c r="N59" s="8" t="inlineStr"/>
+      <c r="N59" s="10" t="inlineStr">
+        <is>
+          <t>에디슨인터내셔널(전력): 산불 책임상한이 법안에서 빠져 화재 소송 부담이 재평가됐다.</t>
+        </is>
+      </c>
     </row>
     <row r="60">
-      <c r="A60" s="5" t="inlineStr">
+      <c r="A60" s="7" t="inlineStr">
         <is>
           <t>신저가</t>
         </is>
@@ -10735,10 +10995,10 @@
         </is>
       </c>
       <c r="M60" t="inlineStr"/>
-      <c r="N60" s="8" t="inlineStr"/>
+      <c r="N60" s="10" t="inlineStr"/>
     </row>
     <row r="61">
-      <c r="A61" s="5" t="inlineStr">
+      <c r="A61" s="7" t="inlineStr">
         <is>
           <t>신저가</t>
         </is>
@@ -10787,10 +11047,10 @@
         </is>
       </c>
       <c r="M61" t="inlineStr"/>
-      <c r="N61" s="8" t="inlineStr"/>
+      <c r="N61" s="10" t="inlineStr"/>
     </row>
     <row r="62">
-      <c r="A62" s="5" t="inlineStr">
+      <c r="A62" s="7" t="inlineStr">
         <is>
           <t>신저가</t>
         </is>
@@ -10839,10 +11099,10 @@
         </is>
       </c>
       <c r="M62" t="inlineStr"/>
-      <c r="N62" s="8" t="inlineStr"/>
+      <c r="N62" s="10" t="inlineStr"/>
     </row>
     <row r="63">
-      <c r="A63" s="5" t="inlineStr">
+      <c r="A63" s="7" t="inlineStr">
         <is>
           <t>신저가</t>
         </is>
@@ -10891,15 +11151,15 @@
         </is>
       </c>
       <c r="M63" t="inlineStr"/>
-      <c r="N63" s="8" t="inlineStr"/>
+      <c r="N63" s="10" t="inlineStr"/>
     </row>
     <row r="64">
-      <c r="A64" s="5" t="inlineStr">
+      <c r="A64" s="7" t="inlineStr">
         <is>
           <t>신저가</t>
         </is>
       </c>
-      <c r="B64" s="7" t="inlineStr">
+      <c r="B64" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -10943,10 +11203,10 @@
         </is>
       </c>
       <c r="M64" t="inlineStr"/>
-      <c r="N64" s="8" t="inlineStr"/>
+      <c r="N64" s="10" t="inlineStr"/>
     </row>
     <row r="65">
-      <c r="A65" s="4" t="inlineStr">
+      <c r="A65" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -10999,15 +11259,15 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N65" s="8" t="inlineStr"/>
+      <c r="N65" s="10" t="inlineStr"/>
     </row>
     <row r="66">
-      <c r="A66" s="5" t="inlineStr">
+      <c r="A66" s="7" t="inlineStr">
         <is>
           <t>신저가</t>
         </is>
       </c>
-      <c r="B66" s="7" t="inlineStr">
+      <c r="B66" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -11051,15 +11311,15 @@
         </is>
       </c>
       <c r="M66" t="inlineStr"/>
-      <c r="N66" s="8" t="inlineStr"/>
+      <c r="N66" s="10" t="inlineStr"/>
     </row>
     <row r="67">
-      <c r="A67" s="5" t="inlineStr">
+      <c r="A67" s="7" t="inlineStr">
         <is>
           <t>신저가</t>
         </is>
       </c>
-      <c r="B67" s="7" t="inlineStr">
+      <c r="B67" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -11103,10 +11363,10 @@
         </is>
       </c>
       <c r="M67" t="inlineStr"/>
-      <c r="N67" s="8" t="inlineStr"/>
+      <c r="N67" s="10" t="inlineStr"/>
     </row>
     <row r="68">
-      <c r="A68" s="5" t="inlineStr">
+      <c r="A68" s="7" t="inlineStr">
         <is>
           <t>신저가</t>
         </is>
@@ -11155,10 +11415,10 @@
         </is>
       </c>
       <c r="M68" t="inlineStr"/>
-      <c r="N68" s="8" t="inlineStr"/>
+      <c r="N68" s="10" t="inlineStr"/>
     </row>
     <row r="69">
-      <c r="A69" s="4" t="inlineStr">
+      <c r="A69" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -11207,10 +11467,10 @@
         </is>
       </c>
       <c r="M69" t="inlineStr"/>
-      <c r="N69" s="8" t="inlineStr"/>
+      <c r="N69" s="10" t="inlineStr"/>
     </row>
     <row r="70">
-      <c r="A70" s="5" t="inlineStr">
+      <c r="A70" s="7" t="inlineStr">
         <is>
           <t>신저가</t>
         </is>
@@ -11259,19 +11519,19 @@
         </is>
       </c>
       <c r="M70" t="inlineStr"/>
-      <c r="N70" s="8" t="inlineStr">
+      <c r="N70" s="10" t="inlineStr">
         <is>
           <t>(전일) 벌링턴스토어스(할인 의류 유통): 2분기 매출 컨센 미달, 동일점포매출 둔화 부각</t>
         </is>
       </c>
     </row>
     <row r="71">
-      <c r="A71" s="5" t="inlineStr">
+      <c r="A71" s="7" t="inlineStr">
         <is>
           <t>신저가</t>
         </is>
       </c>
-      <c r="B71" s="7" t="inlineStr">
+      <c r="B71" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -11315,10 +11575,10 @@
         </is>
       </c>
       <c r="M71" t="inlineStr"/>
-      <c r="N71" s="8" t="inlineStr"/>
+      <c r="N71" s="10" t="inlineStr"/>
     </row>
     <row r="72">
-      <c r="A72" s="4" t="inlineStr">
+      <c r="A72" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -11371,15 +11631,15 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N72" s="8" t="inlineStr"/>
+      <c r="N72" s="10" t="inlineStr"/>
     </row>
     <row r="73">
-      <c r="A73" s="5" t="inlineStr">
+      <c r="A73" s="7" t="inlineStr">
         <is>
           <t>신저가</t>
         </is>
       </c>
-      <c r="B73" s="7" t="inlineStr">
+      <c r="B73" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -11423,10 +11683,10 @@
         </is>
       </c>
       <c r="M73" t="inlineStr"/>
-      <c r="N73" s="8" t="inlineStr"/>
+      <c r="N73" s="10" t="inlineStr"/>
     </row>
     <row r="74">
-      <c r="A74" s="4" t="inlineStr">
+      <c r="A74" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -11475,10 +11735,10 @@
         </is>
       </c>
       <c r="M74" t="inlineStr"/>
-      <c r="N74" s="8" t="inlineStr"/>
+      <c r="N74" s="10" t="inlineStr"/>
     </row>
     <row r="75">
-      <c r="A75" s="5" t="inlineStr">
+      <c r="A75" s="7" t="inlineStr">
         <is>
           <t>신저가</t>
         </is>
@@ -11529,19 +11789,19 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N75" s="8" t="inlineStr">
+      <c r="N75" s="10" t="inlineStr">
         <is>
           <t>(전일) INNIO(가스엔진·발전설비): 특별한 회사 뉴스 없음(신규 상장 변동성 추정)</t>
         </is>
       </c>
     </row>
     <row r="76">
-      <c r="A76" s="5" t="inlineStr">
+      <c r="A76" s="7" t="inlineStr">
         <is>
           <t>신저가</t>
         </is>
       </c>
-      <c r="B76" s="7" t="inlineStr">
+      <c r="B76" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -11585,10 +11845,10 @@
         </is>
       </c>
       <c r="M76" t="inlineStr"/>
-      <c r="N76" s="8" t="inlineStr"/>
+      <c r="N76" s="10" t="inlineStr"/>
     </row>
     <row r="77">
-      <c r="A77" s="5" t="inlineStr">
+      <c r="A77" s="7" t="inlineStr">
         <is>
           <t>신저가</t>
         </is>
@@ -11637,15 +11897,15 @@
         </is>
       </c>
       <c r="M77" t="inlineStr"/>
-      <c r="N77" s="8" t="inlineStr"/>
+      <c r="N77" s="10" t="inlineStr"/>
     </row>
     <row r="78">
-      <c r="A78" s="5" t="inlineStr">
+      <c r="A78" s="7" t="inlineStr">
         <is>
           <t>신저가</t>
         </is>
       </c>
-      <c r="B78" s="7" t="inlineStr">
+      <c r="B78" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -11689,10 +11949,10 @@
         </is>
       </c>
       <c r="M78" t="inlineStr"/>
-      <c r="N78" s="8" t="inlineStr"/>
+      <c r="N78" s="10" t="inlineStr"/>
     </row>
     <row r="79">
-      <c r="A79" s="5" t="inlineStr">
+      <c r="A79" s="7" t="inlineStr">
         <is>
           <t>신저가</t>
         </is>
@@ -11737,15 +11997,15 @@
         </is>
       </c>
       <c r="M79" t="inlineStr"/>
-      <c r="N79" s="8" t="inlineStr"/>
+      <c r="N79" s="10" t="inlineStr"/>
     </row>
     <row r="80">
-      <c r="A80" s="4" t="inlineStr">
+      <c r="A80" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
       </c>
-      <c r="B80" s="7" t="inlineStr">
+      <c r="B80" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -11789,15 +12049,15 @@
         </is>
       </c>
       <c r="M80" t="inlineStr"/>
-      <c r="N80" s="8" t="inlineStr"/>
+      <c r="N80" s="10" t="inlineStr"/>
     </row>
     <row r="81">
-      <c r="A81" s="4" t="inlineStr">
+      <c r="A81" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
       </c>
-      <c r="B81" s="7" t="inlineStr">
+      <c r="B81" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -11841,10 +12101,10 @@
         </is>
       </c>
       <c r="M81" t="inlineStr"/>
-      <c r="N81" s="8" t="inlineStr"/>
+      <c r="N81" s="10" t="inlineStr"/>
     </row>
     <row r="82">
-      <c r="A82" s="5" t="inlineStr">
+      <c r="A82" s="7" t="inlineStr">
         <is>
           <t>신저가</t>
         </is>
@@ -11893,19 +12153,19 @@
         </is>
       </c>
       <c r="M82" t="inlineStr"/>
-      <c r="N82" s="8" t="inlineStr">
+      <c r="N82" s="10" t="inlineStr">
         <is>
           <t>(전일) 스털링인프라(전문 건설): 특별한 회사 뉴스 없음(AI 전력 인프라 차익실현 추정)</t>
         </is>
       </c>
     </row>
     <row r="83">
-      <c r="A83" s="5" t="inlineStr">
+      <c r="A83" s="7" t="inlineStr">
         <is>
           <t>신저가</t>
         </is>
       </c>
-      <c r="B83" s="7" t="inlineStr">
+      <c r="B83" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -11949,10 +12209,10 @@
         </is>
       </c>
       <c r="M83" t="inlineStr"/>
-      <c r="N83" s="8" t="inlineStr"/>
+      <c r="N83" s="10" t="inlineStr"/>
     </row>
     <row r="84">
-      <c r="A84" s="5" t="inlineStr">
+      <c r="A84" s="7" t="inlineStr">
         <is>
           <t>신저가</t>
         </is>
@@ -12003,15 +12263,15 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N84" s="8" t="inlineStr"/>
+      <c r="N84" s="10" t="inlineStr"/>
     </row>
     <row r="85">
-      <c r="A85" s="5" t="inlineStr">
+      <c r="A85" s="7" t="inlineStr">
         <is>
           <t>신저가</t>
         </is>
       </c>
-      <c r="B85" s="7" t="inlineStr">
+      <c r="B85" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -12055,10 +12315,14 @@
         </is>
       </c>
       <c r="M85" t="inlineStr"/>
-      <c r="N85" s="8" t="inlineStr"/>
+      <c r="N85" s="10" t="inlineStr">
+        <is>
+          <t>텍스트론(항공우주·방산): 특별한 뉴스 없음. 항공우주주 수급 약화로 추정한다.</t>
+        </is>
+      </c>
     </row>
     <row r="86">
-      <c r="A86" s="5" t="inlineStr">
+      <c r="A86" s="7" t="inlineStr">
         <is>
           <t>신저가</t>
         </is>
@@ -12107,15 +12371,15 @@
         </is>
       </c>
       <c r="M86" t="inlineStr"/>
-      <c r="N86" s="8" t="inlineStr"/>
+      <c r="N86" s="10" t="inlineStr"/>
     </row>
     <row r="87">
-      <c r="A87" s="5" t="inlineStr">
+      <c r="A87" s="7" t="inlineStr">
         <is>
           <t>신저가</t>
         </is>
       </c>
-      <c r="B87" s="7" t="inlineStr">
+      <c r="B87" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -12163,10 +12427,10 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N87" s="8" t="inlineStr"/>
+      <c r="N87" s="10" t="inlineStr"/>
     </row>
     <row r="88">
-      <c r="A88" s="4" t="inlineStr">
+      <c r="A88" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -12215,10 +12479,10 @@
         </is>
       </c>
       <c r="M88" t="inlineStr"/>
-      <c r="N88" s="8" t="inlineStr"/>
+      <c r="N88" s="10" t="inlineStr"/>
     </row>
     <row r="89">
-      <c r="A89" s="4" t="inlineStr">
+      <c r="A89" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -12267,15 +12531,15 @@
         </is>
       </c>
       <c r="M89" t="inlineStr"/>
-      <c r="N89" s="8" t="inlineStr"/>
+      <c r="N89" s="10" t="inlineStr"/>
     </row>
     <row r="90">
-      <c r="A90" s="4" t="inlineStr">
+      <c r="A90" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
       </c>
-      <c r="B90" s="7" t="inlineStr">
+      <c r="B90" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -12321,15 +12585,15 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N90" s="8" t="inlineStr"/>
+      <c r="N90" s="10" t="inlineStr"/>
     </row>
     <row r="91">
-      <c r="A91" s="5" t="inlineStr">
+      <c r="A91" s="7" t="inlineStr">
         <is>
           <t>신저가</t>
         </is>
       </c>
-      <c r="B91" s="7" t="inlineStr">
+      <c r="B91" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -12373,15 +12637,19 @@
         </is>
       </c>
       <c r="M91" t="inlineStr"/>
-      <c r="N91" s="8" t="inlineStr"/>
+      <c r="N91" s="10" t="inlineStr">
+        <is>
+          <t>넥스트파워(태양광 추적장치): 호실적 뒤 차익실현과 내부자 매도 공시가 부담이었다.</t>
+        </is>
+      </c>
     </row>
     <row r="92">
-      <c r="A92" s="4" t="inlineStr">
+      <c r="A92" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
       </c>
-      <c r="B92" s="7" t="inlineStr">
+      <c r="B92" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -12423,15 +12691,15 @@
         </is>
       </c>
       <c r="M92" t="inlineStr"/>
-      <c r="N92" s="8" t="inlineStr"/>
+      <c r="N92" s="10" t="inlineStr"/>
     </row>
     <row r="93">
-      <c r="A93" s="5" t="inlineStr">
+      <c r="A93" s="7" t="inlineStr">
         <is>
           <t>신저가</t>
         </is>
       </c>
-      <c r="B93" s="7" t="inlineStr">
+      <c r="B93" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -12475,15 +12743,15 @@
         </is>
       </c>
       <c r="M93" t="inlineStr"/>
-      <c r="N93" s="8" t="inlineStr"/>
+      <c r="N93" s="10" t="inlineStr"/>
     </row>
     <row r="94">
-      <c r="A94" s="5" t="inlineStr">
+      <c r="A94" s="7" t="inlineStr">
         <is>
           <t>신저가</t>
         </is>
       </c>
-      <c r="B94" s="7" t="inlineStr">
+      <c r="B94" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -12527,15 +12795,15 @@
         </is>
       </c>
       <c r="M94" t="inlineStr"/>
-      <c r="N94" s="8" t="inlineStr"/>
+      <c r="N94" s="10" t="inlineStr"/>
     </row>
     <row r="95">
-      <c r="A95" s="4" t="inlineStr">
+      <c r="A95" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
       </c>
-      <c r="B95" s="7" t="inlineStr">
+      <c r="B95" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -12579,10 +12847,10 @@
         </is>
       </c>
       <c r="M95" t="inlineStr"/>
-      <c r="N95" s="8" t="inlineStr"/>
+      <c r="N95" s="10" t="inlineStr"/>
     </row>
     <row r="96">
-      <c r="A96" s="5" t="inlineStr">
+      <c r="A96" s="7" t="inlineStr">
         <is>
           <t>신저가</t>
         </is>
@@ -12631,10 +12899,10 @@
         </is>
       </c>
       <c r="M96" t="inlineStr"/>
-      <c r="N96" s="8" t="inlineStr"/>
+      <c r="N96" s="10" t="inlineStr"/>
     </row>
     <row r="97">
-      <c r="A97" s="5" t="inlineStr">
+      <c r="A97" s="7" t="inlineStr">
         <is>
           <t>신저가</t>
         </is>
@@ -12679,10 +12947,10 @@
         </is>
       </c>
       <c r="M97" t="inlineStr"/>
-      <c r="N97" s="8" t="inlineStr"/>
+      <c r="N97" s="10" t="inlineStr"/>
     </row>
     <row r="98">
-      <c r="A98" s="5" t="inlineStr">
+      <c r="A98" s="7" t="inlineStr">
         <is>
           <t>신저가</t>
         </is>
@@ -12731,10 +12999,10 @@
         </is>
       </c>
       <c r="M98" t="inlineStr"/>
-      <c r="N98" s="8" t="inlineStr"/>
+      <c r="N98" s="10" t="inlineStr"/>
     </row>
     <row r="99">
-      <c r="A99" s="4" t="inlineStr">
+      <c r="A99" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -12783,10 +13051,10 @@
         </is>
       </c>
       <c r="M99" t="inlineStr"/>
-      <c r="N99" s="8" t="inlineStr"/>
+      <c r="N99" s="10" t="inlineStr"/>
     </row>
     <row r="100">
-      <c r="A100" s="5" t="inlineStr">
+      <c r="A100" s="7" t="inlineStr">
         <is>
           <t>신저가</t>
         </is>
@@ -12835,14 +13103,14 @@
         </is>
       </c>
       <c r="M100" t="inlineStr"/>
-      <c r="N100" s="8" t="inlineStr">
+      <c r="N100" s="10" t="inlineStr">
         <is>
           <t>(전일) 노바(반도체 계측): 금리 재평가 속 반도체 장비주 전반 약세</t>
         </is>
       </c>
     </row>
     <row r="101">
-      <c r="A101" s="5" t="inlineStr">
+      <c r="A101" s="7" t="inlineStr">
         <is>
           <t>신저가</t>
         </is>
@@ -12891,15 +13159,15 @@
         </is>
       </c>
       <c r="M101" t="inlineStr"/>
-      <c r="N101" s="8" t="inlineStr"/>
+      <c r="N101" s="10" t="inlineStr"/>
     </row>
     <row r="102">
-      <c r="A102" s="5" t="inlineStr">
+      <c r="A102" s="7" t="inlineStr">
         <is>
           <t>신저가</t>
         </is>
       </c>
-      <c r="B102" s="7" t="inlineStr">
+      <c r="B102" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -12943,15 +13211,15 @@
         </is>
       </c>
       <c r="M102" t="inlineStr"/>
-      <c r="N102" s="8" t="inlineStr"/>
+      <c r="N102" s="10" t="inlineStr"/>
     </row>
     <row r="103">
-      <c r="A103" s="5" t="inlineStr">
+      <c r="A103" s="7" t="inlineStr">
         <is>
           <t>신저가</t>
         </is>
       </c>
-      <c r="B103" s="7" t="inlineStr">
+      <c r="B103" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -12993,10 +13261,10 @@
         </is>
       </c>
       <c r="M103" t="inlineStr"/>
-      <c r="N103" s="8" t="inlineStr"/>
+      <c r="N103" s="10" t="inlineStr"/>
     </row>
     <row r="104">
-      <c r="A104" s="5" t="inlineStr">
+      <c r="A104" s="7" t="inlineStr">
         <is>
           <t>신저가</t>
         </is>
@@ -13045,14 +13313,14 @@
         </is>
       </c>
       <c r="M104" t="inlineStr"/>
-      <c r="N104" s="8" t="inlineStr">
+      <c r="N104" s="10" t="inlineStr">
         <is>
           <t>(전일) 제너랙(비상발전기): 회사 신규 뉴스 없이 전력·그리드 종목 동반 약세</t>
         </is>
       </c>
     </row>
     <row r="105">
-      <c r="A105" s="5" t="inlineStr">
+      <c r="A105" s="7" t="inlineStr">
         <is>
           <t>신저가</t>
         </is>
@@ -13101,10 +13369,10 @@
         </is>
       </c>
       <c r="M105" t="inlineStr"/>
-      <c r="N105" s="8" t="inlineStr"/>
+      <c r="N105" s="10" t="inlineStr"/>
     </row>
     <row r="106">
-      <c r="A106" s="5" t="inlineStr">
+      <c r="A106" s="7" t="inlineStr">
         <is>
           <t>신저가</t>
         </is>
@@ -13153,10 +13421,10 @@
         </is>
       </c>
       <c r="M106" t="inlineStr"/>
-      <c r="N106" s="8" t="inlineStr"/>
+      <c r="N106" s="10" t="inlineStr"/>
     </row>
     <row r="107">
-      <c r="A107" s="5" t="inlineStr">
+      <c r="A107" s="7" t="inlineStr">
         <is>
           <t>신저가</t>
         </is>
@@ -13203,15 +13471,15 @@
         </is>
       </c>
       <c r="M107" t="inlineStr"/>
-      <c r="N107" s="8" t="inlineStr"/>
+      <c r="N107" s="10" t="inlineStr"/>
     </row>
     <row r="108">
-      <c r="A108" s="4" t="inlineStr">
+      <c r="A108" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
       </c>
-      <c r="B108" s="7" t="inlineStr">
+      <c r="B108" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -13255,15 +13523,15 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N108" s="8" t="inlineStr"/>
+      <c r="N108" s="10" t="inlineStr"/>
     </row>
     <row r="109">
-      <c r="A109" s="5" t="inlineStr">
+      <c r="A109" s="7" t="inlineStr">
         <is>
           <t>신저가</t>
         </is>
       </c>
-      <c r="B109" s="7" t="inlineStr">
+      <c r="B109" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -13307,15 +13575,15 @@
         </is>
       </c>
       <c r="M109" t="inlineStr"/>
-      <c r="N109" s="8" t="inlineStr"/>
+      <c r="N109" s="10" t="inlineStr"/>
     </row>
     <row r="110">
-      <c r="A110" s="5" t="inlineStr">
+      <c r="A110" s="7" t="inlineStr">
         <is>
           <t>신저가</t>
         </is>
       </c>
-      <c r="B110" s="7" t="inlineStr">
+      <c r="B110" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -13359,7 +13627,7 @@
         </is>
       </c>
       <c r="M110" t="inlineStr"/>
-      <c r="N110" s="8" t="inlineStr"/>
+      <c r="N110" s="10" t="inlineStr"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:N110"/>
@@ -13465,12 +13733,12 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="4" t="inlineStr">
+      <c r="A2" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
       </c>
-      <c r="B2" s="7" t="inlineStr">
+      <c r="B2" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -13514,10 +13782,14 @@
         </is>
       </c>
       <c r="M2" t="inlineStr"/>
-      <c r="N2" s="8" t="inlineStr"/>
+      <c r="N2" s="10" t="inlineStr">
+        <is>
+          <t>이토추(종합상사): 원유와 자원가격 상승으로 자원 익스포저가 부각됐다.</t>
+        </is>
+      </c>
     </row>
     <row r="3">
-      <c r="A3" s="4" t="inlineStr">
+      <c r="A3" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -13568,19 +13840,19 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N3" s="8" t="inlineStr">
+      <c r="N3" s="10" t="inlineStr">
         <is>
           <t>(전일) NTT(통신): 특별한 회사 뉴스 없음(방어적 통신주 수급 추정)</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="4" t="inlineStr">
+      <c r="A4" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
       </c>
-      <c r="B4" s="7" t="inlineStr">
+      <c r="B4" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -13624,15 +13896,19 @@
         </is>
       </c>
       <c r="M4" t="inlineStr"/>
-      <c r="N4" s="8" t="inlineStr"/>
+      <c r="N4" s="10" t="inlineStr">
+        <is>
+          <t>미쓰이물산(종합상사): 원유와 자원가격 상승으로 자원사업 가치가 재평가됐다.</t>
+        </is>
+      </c>
     </row>
     <row r="5">
-      <c r="A5" s="4" t="inlineStr">
+      <c r="A5" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
       </c>
-      <c r="B5" s="7" t="inlineStr">
+      <c r="B5" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -13676,15 +13952,15 @@
         </is>
       </c>
       <c r="M5" t="inlineStr"/>
-      <c r="N5" s="8" t="inlineStr"/>
+      <c r="N5" s="10" t="inlineStr"/>
     </row>
     <row r="6">
-      <c r="A6" s="4" t="inlineStr">
+      <c r="A6" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
       </c>
-      <c r="B6" s="7" t="inlineStr">
+      <c r="B6" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -13732,15 +14008,15 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N6" s="8" t="inlineStr"/>
+      <c r="N6" s="10" t="inlineStr"/>
     </row>
     <row r="7">
-      <c r="A7" s="4" t="inlineStr">
+      <c r="A7" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
       </c>
-      <c r="B7" s="7" t="inlineStr">
+      <c r="B7" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -13784,15 +14060,15 @@
         </is>
       </c>
       <c r="M7" t="inlineStr"/>
-      <c r="N7" s="8" t="inlineStr"/>
+      <c r="N7" s="10" t="inlineStr"/>
     </row>
     <row r="8">
-      <c r="A8" s="4" t="inlineStr">
+      <c r="A8" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
       </c>
-      <c r="B8" s="7" t="inlineStr">
+      <c r="B8" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -13840,15 +14116,15 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N8" s="8" t="inlineStr"/>
+      <c r="N8" s="10" t="inlineStr"/>
     </row>
     <row r="9">
-      <c r="A9" s="4" t="inlineStr">
+      <c r="A9" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
       </c>
-      <c r="B9" s="7" t="inlineStr">
+      <c r="B9" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -13890,10 +14166,14 @@
         </is>
       </c>
       <c r="M9" t="inlineStr"/>
-      <c r="N9" s="8" t="inlineStr"/>
+      <c r="N9" s="10" t="inlineStr">
+        <is>
+          <t>인펙스(원유·가스 개발): 이란 긴장으로 원유가격이 급등해 매수세가 유입됐다.</t>
+        </is>
+      </c>
     </row>
     <row r="10">
-      <c r="A10" s="4" t="inlineStr">
+      <c r="A10" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -13942,19 +14222,19 @@
         </is>
       </c>
       <c r="M10" t="inlineStr"/>
-      <c r="N10" s="8" t="inlineStr">
+      <c r="N10" s="10" t="inlineStr">
         <is>
           <t>(전일) 스즈키(자동차): 특별한 회사 뉴스 없음(자동차 업종 순환매 추정)</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="4" t="inlineStr">
+      <c r="A11" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
       </c>
-      <c r="B11" s="7" t="inlineStr">
+      <c r="B11" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -14000,10 +14280,10 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N11" s="8" t="inlineStr"/>
+      <c r="N11" s="10" t="inlineStr"/>
     </row>
     <row r="12">
-      <c r="A12" s="4" t="inlineStr">
+      <c r="A12" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -14054,15 +14334,15 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N12" s="8" t="inlineStr"/>
+      <c r="N12" s="10" t="inlineStr"/>
     </row>
     <row r="13">
-      <c r="A13" s="4" t="inlineStr">
+      <c r="A13" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
       </c>
-      <c r="B13" s="7" t="inlineStr">
+      <c r="B13" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -14104,10 +14384,14 @@
         </is>
       </c>
       <c r="M13" t="inlineStr"/>
-      <c r="N13" s="8" t="inlineStr"/>
+      <c r="N13" s="10" t="inlineStr">
+        <is>
+          <t>에네오스(정유): 중동 긴장으로 원유가 올라 재고평가와 정유마진 기대가 커졌다.</t>
+        </is>
+      </c>
     </row>
     <row r="14">
-      <c r="A14" s="5" t="inlineStr">
+      <c r="A14" s="7" t="inlineStr">
         <is>
           <t>신저가</t>
         </is>
@@ -14156,14 +14440,14 @@
         </is>
       </c>
       <c r="M14" t="inlineStr"/>
-      <c r="N14" s="8" t="inlineStr">
+      <c r="N14" s="10" t="inlineStr">
         <is>
           <t>(전일) 레이저텍(반도체 검사장비): 시장 기대를 밑돈 FY27 가이던스 부담 지속</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="4" t="inlineStr">
+      <c r="A15" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -14214,19 +14498,19 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N15" s="8" t="inlineStr">
-        <is>
-          <t>(전일) 간사이전력(전력): 특별한 회사 뉴스 없음(전력주 수급 영향 추정)</t>
+      <c r="N15" s="10" t="inlineStr">
+        <is>
+          <t>간사이전력(원전 비중 전력사): 증권사의 목표가 상향이 추가 매수를 불렀다.</t>
         </is>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="5" t="inlineStr">
+      <c r="A16" s="7" t="inlineStr">
         <is>
           <t>신저가</t>
         </is>
       </c>
-      <c r="B16" s="7" t="inlineStr">
+      <c r="B16" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -14274,15 +14558,19 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N16" s="8" t="inlineStr"/>
+      <c r="N16" s="10" t="inlineStr">
+        <is>
+          <t>팬퍼시픽(돈키호테 운영): 이익전망이 기대에 못 미친 뒤 실망 매도가 이어졌다.</t>
+        </is>
+      </c>
     </row>
     <row r="17">
-      <c r="A17" s="4" t="inlineStr">
+      <c r="A17" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
       </c>
-      <c r="B17" s="7" t="inlineStr">
+      <c r="B17" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -14324,10 +14612,10 @@
         </is>
       </c>
       <c r="M17" t="inlineStr"/>
-      <c r="N17" s="8" t="inlineStr"/>
+      <c r="N17" s="10" t="inlineStr"/>
     </row>
     <row r="18">
-      <c r="A18" s="4" t="inlineStr">
+      <c r="A18" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -14374,19 +14662,19 @@
         </is>
       </c>
       <c r="M18" t="inlineStr"/>
-      <c r="N18" s="8" t="inlineStr">
+      <c r="N18" s="10" t="inlineStr">
         <is>
           <t>(전일) 오빅(기업용 소프트웨어): 특별한 회사 뉴스 없음(소프트웨어 강세 연장 추정)</t>
         </is>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="4" t="inlineStr">
+      <c r="A19" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
       </c>
-      <c r="B19" s="7" t="inlineStr">
+      <c r="B19" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -14428,7 +14716,11 @@
         </is>
       </c>
       <c r="M19" t="inlineStr"/>
-      <c r="N19" s="8" t="inlineStr"/>
+      <c r="N19" s="10" t="inlineStr">
+        <is>
+          <t>이데미쓰(정유·석유화학): 원유 급등으로 재고평가와 정유마진 개선 기대가 반영됐다.</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:N19"/>
@@ -14534,12 +14826,12 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="4" t="inlineStr">
+      <c r="A2" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
       </c>
-      <c r="B2" s="7" t="inlineStr">
+      <c r="B2" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -14587,15 +14879,19 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N2" s="8" t="inlineStr"/>
+      <c r="N2" s="10" t="inlineStr">
+        <is>
+          <t>중국건설은행(국유은행): 반기 순익 증가와 중간배당 확대가 배당 매력을 높였다.</t>
+        </is>
+      </c>
     </row>
     <row r="3">
-      <c r="A3" s="4" t="inlineStr">
+      <c r="A3" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
       </c>
-      <c r="B3" s="7" t="inlineStr">
+      <c r="B3" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -14643,15 +14939,19 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N3" s="8" t="inlineStr"/>
+      <c r="N3" s="10" t="inlineStr">
+        <is>
+          <t>중국은행(국유은행): 반기 실적과 배당 확대 뒤 재평가 기대가 신고가를 이끌었다.</t>
+        </is>
+      </c>
     </row>
     <row r="4">
-      <c r="A4" s="4" t="inlineStr">
+      <c r="A4" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
       </c>
-      <c r="B4" s="7" t="inlineStr">
+      <c r="B4" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -14697,15 +14997,15 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N4" s="8" t="inlineStr"/>
+      <c r="N4" s="10" t="inlineStr"/>
     </row>
     <row r="5">
-      <c r="A5" s="4" t="inlineStr">
+      <c r="A5" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
       </c>
-      <c r="B5" s="7" t="inlineStr">
+      <c r="B5" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -14753,15 +15053,15 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N5" s="8" t="inlineStr"/>
+      <c r="N5" s="10" t="inlineStr"/>
     </row>
     <row r="6">
-      <c r="A6" s="4" t="inlineStr">
+      <c r="A6" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
       </c>
-      <c r="B6" s="7" t="inlineStr">
+      <c r="B6" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -14805,15 +15105,15 @@
         </is>
       </c>
       <c r="M6" t="inlineStr"/>
-      <c r="N6" s="8" t="inlineStr"/>
+      <c r="N6" s="10" t="inlineStr"/>
     </row>
     <row r="7">
-      <c r="A7" s="4" t="inlineStr">
+      <c r="A7" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
       </c>
-      <c r="B7" s="7" t="inlineStr">
+      <c r="B7" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -14857,15 +15157,19 @@
         </is>
       </c>
       <c r="M7" t="inlineStr"/>
-      <c r="N7" s="8" t="inlineStr"/>
+      <c r="N7" s="10" t="inlineStr">
+        <is>
+          <t>중국우정저축은행(국유은행): 반기 실적 뒤 배당 확대 기대가 재평가 매수를 이끌었다.</t>
+        </is>
+      </c>
     </row>
     <row r="8">
-      <c r="A8" s="4" t="inlineStr">
+      <c r="A8" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
       </c>
-      <c r="B8" s="7" t="inlineStr">
+      <c r="B8" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -14909,15 +15213,19 @@
         </is>
       </c>
       <c r="M8" t="inlineStr"/>
-      <c r="N8" s="8" t="inlineStr"/>
+      <c r="N8" s="10" t="inlineStr">
+        <is>
+          <t>피아이씨씨손해보험(손해보험): 뱅크오브아메리카의 목표가 상향이 촉매였다.</t>
+        </is>
+      </c>
     </row>
     <row r="9">
-      <c r="A9" s="4" t="inlineStr">
+      <c r="A9" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
       </c>
-      <c r="B9" s="7" t="inlineStr">
+      <c r="B9" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -14961,15 +15269,19 @@
         </is>
       </c>
       <c r="M9" t="inlineStr"/>
-      <c r="N9" s="8" t="inlineStr"/>
+      <c r="N9" s="10" t="inlineStr">
+        <is>
+          <t>중국인민보험그룹(종합보험): 고배당 전략과 계열 손보사 목표가 상향이 부각됐다.</t>
+        </is>
+      </c>
     </row>
     <row r="10">
-      <c r="A10" s="4" t="inlineStr">
+      <c r="A10" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
       </c>
-      <c r="B10" s="7" t="inlineStr">
+      <c r="B10" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -15011,15 +15323,15 @@
         </is>
       </c>
       <c r="M10" t="inlineStr"/>
-      <c r="N10" s="8" t="inlineStr"/>
+      <c r="N10" s="10" t="inlineStr"/>
     </row>
     <row r="11">
-      <c r="A11" s="5" t="inlineStr">
+      <c r="A11" s="7" t="inlineStr">
         <is>
           <t>신저가</t>
         </is>
       </c>
-      <c r="B11" s="7" t="inlineStr">
+      <c r="B11" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -15065,15 +15377,15 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N11" s="8" t="inlineStr"/>
+      <c r="N11" s="10" t="inlineStr"/>
     </row>
     <row r="12">
-      <c r="A12" s="5" t="inlineStr">
+      <c r="A12" s="7" t="inlineStr">
         <is>
           <t>신저가</t>
         </is>
       </c>
-      <c r="B12" s="7" t="inlineStr">
+      <c r="B12" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -15121,10 +15433,14 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N12" s="8" t="inlineStr"/>
+      <c r="N12" s="10" t="inlineStr">
+        <is>
+          <t>중국광대은행(상업은행): 특별한 개별 뉴스 없이 은행주 재평가 흐름에서 엇갈렸다.</t>
+        </is>
+      </c>
     </row>
     <row r="13">
-      <c r="A13" s="4" t="inlineStr">
+      <c r="A13" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -15173,19 +15489,19 @@
         </is>
       </c>
       <c r="M13" t="inlineStr"/>
-      <c r="N13" s="8" t="inlineStr">
+      <c r="N13" s="10" t="inlineStr">
         <is>
           <t>(전일) KE홀딩스(주택 중개 플랫폼): 특별한 회사 뉴스 없음(부동산주 개별 수급 추정)</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="5" t="inlineStr">
+      <c r="A14" s="7" t="inlineStr">
         <is>
           <t>신저가</t>
         </is>
       </c>
-      <c r="B14" s="7" t="inlineStr">
+      <c r="B14" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -15231,15 +15547,15 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N14" s="8" t="inlineStr"/>
+      <c r="N14" s="10" t="inlineStr"/>
     </row>
     <row r="15">
-      <c r="A15" s="5" t="inlineStr">
+      <c r="A15" s="7" t="inlineStr">
         <is>
           <t>신저가</t>
         </is>
       </c>
-      <c r="B15" s="7" t="inlineStr">
+      <c r="B15" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -15281,15 +15597,19 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N15" s="8" t="inlineStr"/>
+      <c r="N15" s="10" t="inlineStr">
+        <is>
+          <t>중국국제항공(항공사): 상반기 적자 확대와 항공유 비용 상승이 확인돼 매도됐다.</t>
+        </is>
+      </c>
     </row>
     <row r="16">
-      <c r="A16" s="4" t="inlineStr">
+      <c r="A16" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
       </c>
-      <c r="B16" s="7" t="inlineStr">
+      <c r="B16" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -15335,15 +15655,15 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N16" s="8" t="inlineStr"/>
+      <c r="N16" s="10" t="inlineStr"/>
     </row>
     <row r="17">
-      <c r="A17" s="5" t="inlineStr">
+      <c r="A17" s="7" t="inlineStr">
         <is>
           <t>신저가</t>
         </is>
       </c>
-      <c r="B17" s="7" t="inlineStr">
+      <c r="B17" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -15381,15 +15701,15 @@
         </is>
       </c>
       <c r="M17" t="inlineStr"/>
-      <c r="N17" s="8" t="inlineStr"/>
+      <c r="N17" s="10" t="inlineStr"/>
     </row>
     <row r="18">
-      <c r="A18" s="5" t="inlineStr">
+      <c r="A18" s="7" t="inlineStr">
         <is>
           <t>신저가</t>
         </is>
       </c>
-      <c r="B18" s="7" t="inlineStr">
+      <c r="B18" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -15435,15 +15755,15 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N18" s="8" t="inlineStr"/>
+      <c r="N18" s="10" t="inlineStr"/>
     </row>
     <row r="19">
-      <c r="A19" s="5" t="inlineStr">
+      <c r="A19" s="7" t="inlineStr">
         <is>
           <t>신저가</t>
         </is>
       </c>
-      <c r="B19" s="7" t="inlineStr">
+      <c r="B19" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -15483,15 +15803,19 @@
         </is>
       </c>
       <c r="M19" t="inlineStr"/>
-      <c r="N19" s="8" t="inlineStr"/>
+      <c r="N19" s="10" t="inlineStr">
+        <is>
+          <t>완저우인터내셔널(돼지고기): 2분기 영업이익 부진을 이유로 목표가가 하향됐다.</t>
+        </is>
+      </c>
     </row>
     <row r="20">
-      <c r="A20" s="5" t="inlineStr">
+      <c r="A20" s="7" t="inlineStr">
         <is>
           <t>신저가</t>
         </is>
       </c>
-      <c r="B20" s="7" t="inlineStr">
+      <c r="B20" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -15537,15 +15861,15 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N20" s="8" t="inlineStr"/>
+      <c r="N20" s="10" t="inlineStr"/>
     </row>
     <row r="21">
-      <c r="A21" s="5" t="inlineStr">
+      <c r="A21" s="7" t="inlineStr">
         <is>
           <t>신저가</t>
         </is>
       </c>
-      <c r="B21" s="7" t="inlineStr">
+      <c r="B21" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -15591,15 +15915,15 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N21" s="8" t="inlineStr"/>
+      <c r="N21" s="10" t="inlineStr"/>
     </row>
     <row r="22">
-      <c r="A22" s="4" t="inlineStr">
+      <c r="A22" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
       </c>
-      <c r="B22" s="7" t="inlineStr">
+      <c r="B22" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -15637,15 +15961,15 @@
         </is>
       </c>
       <c r="M22" t="inlineStr"/>
-      <c r="N22" s="8" t="inlineStr"/>
+      <c r="N22" s="10" t="inlineStr"/>
     </row>
     <row r="23">
-      <c r="A23" s="5" t="inlineStr">
+      <c r="A23" s="7" t="inlineStr">
         <is>
           <t>신저가</t>
         </is>
       </c>
-      <c r="B23" s="7" t="inlineStr">
+      <c r="B23" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -15691,15 +16015,19 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N23" s="8" t="inlineStr"/>
+      <c r="N23" s="10" t="inlineStr">
+        <is>
+          <t>중국남방항공(항공사): 상반기 적자 확대와 항공유 비용 상승이 확인돼 매도됐다.</t>
+        </is>
+      </c>
     </row>
     <row r="24">
-      <c r="A24" s="5" t="inlineStr">
+      <c r="A24" s="7" t="inlineStr">
         <is>
           <t>신저가</t>
         </is>
       </c>
-      <c r="B24" s="7" t="inlineStr">
+      <c r="B24" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -15743,15 +16071,19 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N24" s="8" t="inlineStr"/>
+      <c r="N24" s="10" t="inlineStr">
+        <is>
+          <t>중국동방항공(항공사): 상반기 적자 확대와 항공유 비용 상승이 확인돼 매도됐다.</t>
+        </is>
+      </c>
     </row>
     <row r="25">
-      <c r="A25" s="5" t="inlineStr">
+      <c r="A25" s="7" t="inlineStr">
         <is>
           <t>신저가</t>
         </is>
       </c>
-      <c r="B25" s="7" t="inlineStr">
+      <c r="B25" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -15797,15 +16129,15 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N25" s="8" t="inlineStr"/>
+      <c r="N25" s="10" t="inlineStr"/>
     </row>
     <row r="26">
-      <c r="A26" s="5" t="inlineStr">
+      <c r="A26" s="7" t="inlineStr">
         <is>
           <t>신저가</t>
         </is>
       </c>
-      <c r="B26" s="7" t="inlineStr">
+      <c r="B26" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -15849,7 +16181,7 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N26" s="8" t="inlineStr"/>
+      <c r="N26" s="10" t="inlineStr"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:N26"/>
@@ -15955,12 +16287,12 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="4" t="inlineStr">
+      <c r="A2" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
       </c>
-      <c r="B2" s="7" t="inlineStr">
+      <c r="B2" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -16008,10 +16340,10 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N2" s="8" t="inlineStr"/>
+      <c r="N2" s="10" t="inlineStr"/>
     </row>
     <row r="3">
-      <c r="A3" s="4" t="inlineStr">
+      <c r="A3" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -16056,19 +16388,19 @@
         </is>
       </c>
       <c r="M3" t="inlineStr"/>
-      <c r="N3" s="8" t="inlineStr">
+      <c r="N3" s="10" t="inlineStr">
         <is>
           <t>(전일) 페트로차이나(석유·가스): 중간실적 공시와 쿤룬캐피털 증자 참여 발표</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="4" t="inlineStr">
+      <c r="A4" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
       </c>
-      <c r="B4" s="7" t="inlineStr">
+      <c r="B4" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -16116,10 +16448,14 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N4" s="8" t="inlineStr"/>
+      <c r="N4" s="10" t="inlineStr">
+        <is>
+          <t>중국은행(국유은행): 반기 순익 성장과 고배당 자금 유입으로 사상 최고가를 경신했다.</t>
+        </is>
+      </c>
     </row>
     <row r="5">
-      <c r="A5" s="4" t="inlineStr">
+      <c r="A5" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -16164,19 +16500,19 @@
         </is>
       </c>
       <c r="M5" t="inlineStr"/>
-      <c r="N5" s="8" t="inlineStr">
+      <c r="N5" s="10" t="inlineStr">
         <is>
           <t>(전일) 시노펙(정유·석화): 상반기 순이익 19% 증가·정제마진 개선 재평가</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="4" t="inlineStr">
+      <c r="A6" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
       </c>
-      <c r="B6" s="7" t="inlineStr">
+      <c r="B6" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -16222,15 +16558,15 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N6" s="8" t="inlineStr"/>
+      <c r="N6" s="10" t="inlineStr"/>
     </row>
     <row r="7">
-      <c r="A7" s="4" t="inlineStr">
+      <c r="A7" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
       </c>
-      <c r="B7" s="7" t="inlineStr">
+      <c r="B7" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -16274,10 +16610,14 @@
         </is>
       </c>
       <c r="M7" t="inlineStr"/>
-      <c r="N7" s="8" t="inlineStr"/>
+      <c r="N7" s="10" t="inlineStr">
+        <is>
+          <t>중국우정저축은행(국유은행): 반기 순익 성장과 배당 확대 기대가 신고가를 이끌었다.</t>
+        </is>
+      </c>
     </row>
     <row r="8">
-      <c r="A8" s="5" t="inlineStr">
+      <c r="A8" s="7" t="inlineStr">
         <is>
           <t>신저가</t>
         </is>
@@ -16326,19 +16666,19 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N8" s="8" t="inlineStr">
+      <c r="N8" s="10" t="inlineStr">
         <is>
           <t>(전일) 유니트리(휴머노이드 로봇): 상장 급등 뒤 실적 대비 고평가 부담으로 조정 지속</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="4" t="inlineStr">
+      <c r="A9" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
       </c>
-      <c r="B9" s="7" t="inlineStr">
+      <c r="B9" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -16382,15 +16722,15 @@
         </is>
       </c>
       <c r="M9" t="inlineStr"/>
-      <c r="N9" s="8" t="inlineStr"/>
+      <c r="N9" s="10" t="inlineStr"/>
     </row>
     <row r="10">
-      <c r="A10" s="4" t="inlineStr">
+      <c r="A10" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
       </c>
-      <c r="B10" s="7" t="inlineStr">
+      <c r="B10" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -16438,10 +16778,10 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N10" s="8" t="inlineStr"/>
+      <c r="N10" s="10" t="inlineStr"/>
     </row>
     <row r="11">
-      <c r="A11" s="4" t="inlineStr">
+      <c r="A11" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -16488,19 +16828,19 @@
         </is>
       </c>
       <c r="M11" t="inlineStr"/>
-      <c r="N11" s="8" t="inlineStr">
+      <c r="N11" s="10" t="inlineStr">
         <is>
           <t>(전일) 무위안푸드(양돈): 특별한 회사 뉴스 없음(공급·돈가 기대 영향 추정)</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="5" t="inlineStr">
+      <c r="A12" s="7" t="inlineStr">
         <is>
           <t>신저가</t>
         </is>
       </c>
-      <c r="B12" s="7" t="inlineStr">
+      <c r="B12" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -16546,10 +16886,14 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N12" s="8" t="inlineStr"/>
+      <c r="N12" s="10" t="inlineStr">
+        <is>
+          <t>선그로우(태양광·저장장치): 상반기 매출 29%, 순이익 32% 감소가 매도를 불렀다.</t>
+        </is>
+      </c>
     </row>
     <row r="13">
-      <c r="A13" s="4" t="inlineStr">
+      <c r="A13" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -16598,19 +16942,19 @@
         </is>
       </c>
       <c r="M13" t="inlineStr"/>
-      <c r="N13" s="8" t="inlineStr">
+      <c r="N13" s="10" t="inlineStr">
         <is>
           <t>(전일) 마인드레이(의료기기): 특별한 회사 뉴스 없음(의료기기 수급 영향 추정)</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="4" t="inlineStr">
+      <c r="A14" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
       </c>
-      <c r="B14" s="7" t="inlineStr">
+      <c r="B14" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -16656,15 +17000,19 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N14" s="8" t="inlineStr"/>
+      <c r="N14" s="10" t="inlineStr">
+        <is>
+          <t>쑹파(조선업 편입 상장사): 특별한 당일 뉴스 없이 자산재편 기대가 이어진 것으로 추정한다.</t>
+        </is>
+      </c>
     </row>
     <row r="15">
-      <c r="A15" s="4" t="inlineStr">
+      <c r="A15" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
       </c>
-      <c r="B15" s="7" t="inlineStr">
+      <c r="B15" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -16706,15 +17054,15 @@
         </is>
       </c>
       <c r="M15" t="inlineStr"/>
-      <c r="N15" s="8" t="inlineStr"/>
+      <c r="N15" s="10" t="inlineStr"/>
     </row>
     <row r="16">
-      <c r="A16" s="4" t="inlineStr">
+      <c r="A16" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
       </c>
-      <c r="B16" s="7" t="inlineStr">
+      <c r="B16" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -16756,15 +17104,15 @@
         </is>
       </c>
       <c r="M16" t="inlineStr"/>
-      <c r="N16" s="8" t="inlineStr"/>
+      <c r="N16" s="10" t="inlineStr"/>
     </row>
     <row r="17">
-      <c r="A17" s="4" t="inlineStr">
+      <c r="A17" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
       </c>
-      <c r="B17" s="7" t="inlineStr">
+      <c r="B17" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -16806,15 +17154,15 @@
         </is>
       </c>
       <c r="M17" t="inlineStr"/>
-      <c r="N17" s="8" t="inlineStr"/>
+      <c r="N17" s="10" t="inlineStr"/>
     </row>
     <row r="18">
-      <c r="A18" s="4" t="inlineStr">
+      <c r="A18" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
       </c>
-      <c r="B18" s="7" t="inlineStr">
+      <c r="B18" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -16856,15 +17204,15 @@
         </is>
       </c>
       <c r="M18" t="inlineStr"/>
-      <c r="N18" s="8" t="inlineStr"/>
+      <c r="N18" s="10" t="inlineStr"/>
     </row>
     <row r="19">
-      <c r="A19" s="5" t="inlineStr">
+      <c r="A19" s="7" t="inlineStr">
         <is>
           <t>신저가</t>
         </is>
       </c>
-      <c r="B19" s="7" t="inlineStr">
+      <c r="B19" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -16908,15 +17256,19 @@
         </is>
       </c>
       <c r="M19" t="inlineStr"/>
-      <c r="N19" s="8" t="inlineStr"/>
+      <c r="N19" s="10" t="inlineStr">
+        <is>
+          <t>쓰위안일렉트릭(전력기기): 미국 전력설비 제한정책 우려가 이어진 것으로 추정한다.</t>
+        </is>
+      </c>
     </row>
     <row r="20">
-      <c r="A20" s="4" t="inlineStr">
+      <c r="A20" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
       </c>
-      <c r="B20" s="7" t="inlineStr">
+      <c r="B20" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -16960,10 +17312,14 @@
         </is>
       </c>
       <c r="M20" t="inlineStr"/>
-      <c r="N20" s="8" t="inlineStr"/>
+      <c r="N20" s="10" t="inlineStr">
+        <is>
+          <t>베이징은행(지역은행): 반기 이익 성장과 순이자마진 안정 기대가 재평가를 이끌었다.</t>
+        </is>
+      </c>
     </row>
     <row r="21">
-      <c r="A21" s="5" t="inlineStr">
+      <c r="A21" s="7" t="inlineStr">
         <is>
           <t>신저가</t>
         </is>
@@ -17016,19 +17372,19 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N21" s="8" t="inlineStr">
+      <c r="N21" s="10" t="inlineStr">
         <is>
           <t>(전일) 화샤은행(은행): 2026년 중간배당 미실시 발표 뒤 급락</t>
         </is>
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="4" t="inlineStr">
+      <c r="A22" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
       </c>
-      <c r="B22" s="7" t="inlineStr">
+      <c r="B22" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -17070,15 +17426,15 @@
         </is>
       </c>
       <c r="M22" t="inlineStr"/>
-      <c r="N22" s="8" t="inlineStr"/>
+      <c r="N22" s="10" t="inlineStr"/>
     </row>
     <row r="23">
-      <c r="A23" s="5" t="inlineStr">
+      <c r="A23" s="7" t="inlineStr">
         <is>
           <t>신저가</t>
         </is>
       </c>
-      <c r="B23" s="7" t="inlineStr">
+      <c r="B23" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -17126,15 +17482,19 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N23" s="8" t="inlineStr"/>
+      <c r="N23" s="10" t="inlineStr">
+        <is>
+          <t>쉬공기계(건설기계): 매출은 늘었지만 순이익 감소와 환손실 확대가 부담이었다.</t>
+        </is>
+      </c>
     </row>
     <row r="24">
-      <c r="A24" s="4" t="inlineStr">
+      <c r="A24" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
       </c>
-      <c r="B24" s="7" t="inlineStr">
+      <c r="B24" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -17176,15 +17536,15 @@
         </is>
       </c>
       <c r="M24" t="inlineStr"/>
-      <c r="N24" s="8" t="inlineStr"/>
+      <c r="N24" s="10" t="inlineStr"/>
     </row>
     <row r="25">
-      <c r="A25" s="5" t="inlineStr">
+      <c r="A25" s="7" t="inlineStr">
         <is>
           <t>신저가</t>
         </is>
       </c>
-      <c r="B25" s="7" t="inlineStr">
+      <c r="B25" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -17226,15 +17586,19 @@
         </is>
       </c>
       <c r="M25" t="inlineStr"/>
-      <c r="N25" s="8" t="inlineStr"/>
+      <c r="N25" s="10" t="inlineStr">
+        <is>
+          <t>룽위안전력(풍력발전): 상반기 매출 6%, 순이익 29% 감소가 부담이었다.</t>
+        </is>
+      </c>
     </row>
     <row r="26">
-      <c r="A26" s="5" t="inlineStr">
+      <c r="A26" s="7" t="inlineStr">
         <is>
           <t>신저가</t>
         </is>
       </c>
-      <c r="B26" s="7" t="inlineStr">
+      <c r="B26" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -17280,15 +17644,19 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N26" s="8" t="inlineStr"/>
+      <c r="N26" s="10" t="inlineStr">
+        <is>
+          <t>세레스(전기차): 특별한 뉴스 없음. 신에너지차 약세와 자금유출 흐름으로 추정한다.</t>
+        </is>
+      </c>
     </row>
     <row r="27">
-      <c r="A27" s="4" t="inlineStr">
+      <c r="A27" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
       </c>
-      <c r="B27" s="7" t="inlineStr">
+      <c r="B27" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -17334,7 +17702,11 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N27" s="8" t="inlineStr"/>
+      <c r="N27" s="10" t="inlineStr">
+        <is>
+          <t>레이트론(적외선 센서): 위성통신 기술 진전과 우주산업 정책 기대가 매수를 불렀다.</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:N27"/>
